--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="2581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4944" uniqueCount="2581">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19172,9 +19172,6 @@
       </c>
       <c r="D287" t="s">
         <v>1086</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1271</v>
       </c>
       <c r="F287" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4944" uniqueCount="2581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="2581">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19172,6 +19172,9 @@
       </c>
       <c r="D287" t="s">
         <v>1086</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1271</v>
       </c>
       <c r="F287" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -4087,6 +4087,9 @@
     <t>ORÇAMENTO</t>
   </si>
   <si>
+    <t>BIOLOGIA,URBANISMO</t>
+  </si>
+  <si>
     <t>MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
@@ -4130,9 +4133,6 @@
   </si>
   <si>
     <t>ECONOMICIDADE OBRAS,ENGENHARIA CIVIL</t>
-  </si>
-  <si>
-    <t>BIOLOGIA,URBANISMO</t>
   </si>
   <si>
     <t>EDIFICAÇÕES</t>
@@ -10815,7 +10815,7 @@
         <v>1341</v>
       </c>
       <c r="H36" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="I36" t="s">
         <v>1420</v>
@@ -11007,7 +11007,7 @@
         <v>1341</v>
       </c>
       <c r="H42" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="I42" t="s">
         <v>1406</v>
@@ -11141,7 +11141,7 @@
         <v>1341</v>
       </c>
       <c r="H46" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I46" t="s">
         <v>1405</v>
@@ -11173,7 +11173,7 @@
         <v>1341</v>
       </c>
       <c r="H47" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="I47" t="s">
         <v>1429</v>
@@ -11307,7 +11307,7 @@
         <v>1341</v>
       </c>
       <c r="H51" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I51" t="s">
         <v>1431</v>
@@ -11371,7 +11371,7 @@
         <v>1344</v>
       </c>
       <c r="H53" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="I53" t="s">
         <v>1433</v>
@@ -11601,7 +11601,7 @@
         <v>1343</v>
       </c>
       <c r="H60" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I60" t="s">
         <v>1438</v>
@@ -11633,7 +11633,7 @@
         <v>1341</v>
       </c>
       <c r="H61" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I61" t="s">
         <v>1423</v>
@@ -11700,7 +11700,7 @@
         <v>1341</v>
       </c>
       <c r="H63" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="I63" t="s">
         <v>1396</v>
@@ -11959,7 +11959,7 @@
         <v>1341</v>
       </c>
       <c r="H71" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I71" t="s">
         <v>1442</v>
@@ -11994,7 +11994,7 @@
         <v>1341</v>
       </c>
       <c r="H72" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I72" t="s">
         <v>1443</v>
@@ -12026,7 +12026,7 @@
         <v>1342</v>
       </c>
       <c r="H73" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I73" t="s">
         <v>1429</v>
@@ -12396,7 +12396,7 @@
         <v>1341</v>
       </c>
       <c r="H84" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I84" t="s">
         <v>1442</v>
@@ -12463,7 +12463,7 @@
         <v>1341</v>
       </c>
       <c r="H86" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I86" t="s">
         <v>1449</v>
@@ -12530,7 +12530,7 @@
         <v>1341</v>
       </c>
       <c r="H88" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I88" t="s">
         <v>1442</v>
@@ -12603,7 +12603,7 @@
         <v>1343</v>
       </c>
       <c r="H90" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="I90" t="s">
         <v>1403</v>
@@ -12903,7 +12903,7 @@
         <v>1341</v>
       </c>
       <c r="H99" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I99" t="s">
         <v>1442</v>
@@ -13101,7 +13101,7 @@
         <v>1341</v>
       </c>
       <c r="H105" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I105" t="s">
         <v>1453</v>
@@ -13343,7 +13343,7 @@
         <v>1341</v>
       </c>
       <c r="H112" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="I112" t="s">
         <v>1458</v>
@@ -13471,7 +13471,7 @@
         <v>1341</v>
       </c>
       <c r="H116" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="I116" t="s">
         <v>1460</v>
@@ -13503,7 +13503,7 @@
         <v>1341</v>
       </c>
       <c r="H117" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="I117" t="s">
         <v>1397</v>
@@ -13701,7 +13701,7 @@
         <v>1341</v>
       </c>
       <c r="H123" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I123" t="s">
         <v>1462</v>
@@ -13733,7 +13733,7 @@
         <v>1341</v>
       </c>
       <c r="H124" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="I124" t="s">
         <v>1403</v>
@@ -13829,7 +13829,7 @@
         <v>1341</v>
       </c>
       <c r="H127" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="I127" t="s">
         <v>1441</v>
@@ -13861,7 +13861,7 @@
         <v>1342</v>
       </c>
       <c r="H128" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="I128" t="s">
         <v>1463</v>
@@ -13989,7 +13989,7 @@
         <v>1341</v>
       </c>
       <c r="H132" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I132" t="s">
         <v>1423</v>
@@ -14085,7 +14085,7 @@
         <v>1341</v>
       </c>
       <c r="H135" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I135" t="s">
         <v>1465</v>
@@ -14219,7 +14219,7 @@
         <v>1341</v>
       </c>
       <c r="H139" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="I139" t="s">
         <v>1420</v>
@@ -14353,7 +14353,7 @@
         <v>1342</v>
       </c>
       <c r="H143" t="s">
-        <v>1372</v>
+        <v>1357</v>
       </c>
       <c r="I143" t="s">
         <v>1397</v>
@@ -14455,7 +14455,7 @@
         <v>1341</v>
       </c>
       <c r="H146" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I146" t="s">
         <v>1460</v>
@@ -14630,7 +14630,7 @@
         <v>1343</v>
       </c>
       <c r="H151" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="I151" t="s">
         <v>1473</v>
@@ -14697,7 +14697,7 @@
         <v>1341</v>
       </c>
       <c r="H153" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I153" t="s">
         <v>1471</v>
@@ -14863,7 +14863,7 @@
         <v>1341</v>
       </c>
       <c r="H158" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I158" t="s">
         <v>1476</v>
@@ -15000,7 +15000,7 @@
         <v>1341</v>
       </c>
       <c r="H162" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I162" t="s">
         <v>1478</v>
@@ -15064,7 +15064,7 @@
         <v>1341</v>
       </c>
       <c r="H164" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I164" t="s">
         <v>1409</v>
@@ -15254,7 +15254,7 @@
         <v>1341</v>
       </c>
       <c r="H169" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I169" t="s">
         <v>1427</v>
@@ -15330,7 +15330,7 @@
         <v>1341</v>
       </c>
       <c r="H171" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I171" t="s">
         <v>1397</v>
@@ -15726,7 +15726,7 @@
         <v>1341</v>
       </c>
       <c r="H183" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="I183" t="s">
         <v>1465</v>
@@ -15962,7 +15962,7 @@
         <v>1342</v>
       </c>
       <c r="H190" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I190" t="s">
         <v>1478</v>
@@ -16419,7 +16419,7 @@
         <v>1341</v>
       </c>
       <c r="H204" t="s">
-        <v>1372</v>
+        <v>1357</v>
       </c>
       <c r="I204" t="s">
         <v>1438</v>
@@ -16661,7 +16661,7 @@
         <v>1342</v>
       </c>
       <c r="H211" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I211" t="s">
         <v>1400</v>
@@ -17159,7 +17159,7 @@
         <v>1342</v>
       </c>
       <c r="H226" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I226" t="s">
         <v>1494</v>
@@ -18091,7 +18091,7 @@
         <v>1341</v>
       </c>
       <c r="H254" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I254" t="s">
         <v>1483</v>
@@ -18123,7 +18123,7 @@
         <v>1342</v>
       </c>
       <c r="H255" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I255" t="s">
         <v>1466</v>
@@ -18193,7 +18193,7 @@
         <v>1341</v>
       </c>
       <c r="H257" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="I257" t="s">
         <v>1451</v>
@@ -19672,7 +19672,7 @@
         <v>1341</v>
       </c>
       <c r="H302" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="I302" t="s">
         <v>1481</v>
@@ -19748,7 +19748,7 @@
         <v>1341</v>
       </c>
       <c r="H304" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I304" t="s">
         <v>1507</v>
@@ -20141,7 +20141,7 @@
         <v>1341</v>
       </c>
       <c r="H316" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I316" t="s">
         <v>1471</v>
@@ -20307,7 +20307,7 @@
         <v>1341</v>
       </c>
       <c r="H321" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I321" t="s">
         <v>1442</v>
@@ -20473,7 +20473,7 @@
         <v>1341</v>
       </c>
       <c r="H326" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I326" t="s">
         <v>1449</v>
@@ -20639,7 +20639,7 @@
         <v>1341</v>
       </c>
       <c r="H331" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I331" t="s">
         <v>1442</v>
@@ -21096,7 +21096,7 @@
         <v>1341</v>
       </c>
       <c r="H345" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I345" t="s">
         <v>1449</v>
@@ -21553,7 +21553,7 @@
         <v>1341</v>
       </c>
       <c r="H359" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="I359" t="s">
         <v>1396</v>
@@ -21591,7 +21591,7 @@
         <v>1341</v>
       </c>
       <c r="H360" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="I360" t="s">
         <v>1397</v>
@@ -21655,7 +21655,7 @@
         <v>1341</v>
       </c>
       <c r="H362" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I362" t="s">
         <v>1447</v>
@@ -21859,7 +21859,7 @@
         <v>1341</v>
       </c>
       <c r="H368" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I368" t="s">
         <v>1516</v>
@@ -22098,7 +22098,7 @@
         <v>1341</v>
       </c>
       <c r="H375" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I375" t="s">
         <v>1519</v>
@@ -22459,7 +22459,7 @@
         <v>1341</v>
       </c>
       <c r="H386" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I386" t="s">
         <v>1485</v>
@@ -22491,7 +22491,7 @@
         <v>1341</v>
       </c>
       <c r="H387" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="I387" t="s">
         <v>1431</v>
@@ -22692,7 +22692,7 @@
         <v>1341</v>
       </c>
       <c r="H393" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I393" t="s">
         <v>1449</v>
@@ -22788,7 +22788,7 @@
         <v>1342</v>
       </c>
       <c r="H396" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I396" t="s">
         <v>1400</v>
@@ -22858,7 +22858,7 @@
         <v>1343</v>
       </c>
       <c r="H398" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="I398" t="s">
         <v>1473</v>
@@ -23100,7 +23100,7 @@
         <v>1341</v>
       </c>
       <c r="H405" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="I405" t="s">
         <v>1427</v>
@@ -23365,7 +23365,7 @@
         <v>1341</v>
       </c>
       <c r="H413" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I413" t="s">
         <v>1523</v>
@@ -23633,7 +23633,7 @@
         <v>1341</v>
       </c>
       <c r="H421" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I421" t="s">
         <v>1449</v>
@@ -24839,7 +24839,7 @@
         <v>1341</v>
       </c>
       <c r="H457" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I457" t="s">
         <v>1483</v>
@@ -25343,7 +25343,7 @@
         <v>1341</v>
       </c>
       <c r="H472" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I472" t="s">
         <v>1471</v>
@@ -25375,7 +25375,7 @@
         <v>1341</v>
       </c>
       <c r="H473" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="I473" t="s">
         <v>1433</v>
@@ -25506,7 +25506,7 @@
         <v>1341</v>
       </c>
       <c r="H477" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I477" t="s">
         <v>1396</v>
@@ -25538,7 +25538,7 @@
         <v>1342</v>
       </c>
       <c r="H478" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="I478" t="s">
         <v>1396</v>
@@ -25602,7 +25602,7 @@
         <v>1341</v>
       </c>
       <c r="H480" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="I480" t="s">
         <v>1519</v>
@@ -25771,7 +25771,7 @@
         <v>1341</v>
       </c>
       <c r="H485" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="I485" t="s">
         <v>1471</v>
@@ -26252,7 +26252,7 @@
         <v>1341</v>
       </c>
       <c r="H499" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I499" t="s">
         <v>1427</v>
@@ -26686,7 +26686,7 @@
         <v>1341</v>
       </c>
       <c r="H512" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="I512" t="s">
         <v>1438</v>
@@ -27085,7 +27085,7 @@
         <v>1341</v>
       </c>
       <c r="H524" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="I524" t="s">
         <v>1427</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4927" uniqueCount="2573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4926" uniqueCount="2573">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19116,9 +19116,6 @@
       </c>
       <c r="D286" t="s">
         <v>1082</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1267</v>
       </c>
       <c r="F286" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4926" uniqueCount="2573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4927" uniqueCount="2573">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19117,6 +19117,9 @@
       <c r="D286" t="s">
         <v>1082</v>
       </c>
+      <c r="E286" t="s">
+        <v>1267</v>
+      </c>
       <c r="F286" s="2">
         <v>45771</v>
       </c>
@@ -20277,7 +20280,7 @@
         <v>1163</v>
       </c>
       <c r="F321" s="2">
-        <v>45708</v>
+        <v>46079</v>
       </c>
       <c r="G321" t="s">
         <v>1337</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="2571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4920" uniqueCount="2571">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19135,6 +19135,9 @@
       </c>
       <c r="D287" t="s">
         <v>1080</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1266</v>
       </c>
       <c r="F287" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4920" uniqueCount="2571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="2571">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19135,9 +19135,6 @@
       </c>
       <c r="D287" t="s">
         <v>1080</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1266</v>
       </c>
       <c r="F287" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4910" uniqueCount="2567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="2567">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19114,6 +19114,9 @@
       </c>
       <c r="D287" t="s">
         <v>1078</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1264</v>
       </c>
       <c r="F287" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="2567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4910" uniqueCount="2567">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -19114,9 +19114,6 @@
       </c>
       <c r="D287" t="s">
         <v>1078</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1264</v>
       </c>
       <c r="F287" s="2">
         <v>45771</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -4636,6 +4636,9 @@
     <t>FENOMENOS DE ENERGIA E INFORMAÇÃO</t>
   </si>
   <si>
+    <t>AVALIAÇÃO DE IMÓVEIS</t>
+  </si>
+  <si>
     <t>FENOMENOS DE ENERGIA E INFORMAÇÃO,MOBILIDADE E TRANSPORTE</t>
   </si>
   <si>
@@ -4709,9 +4712,6 @@
   </si>
   <si>
     <t>MOBILIDADE E TRANSPORTE,VALORAÇÃO DANOS AMBIENTAIS</t>
-  </si>
-  <si>
-    <t>AVALIAÇÃO DE IMÓVEIS</t>
   </si>
   <si>
     <t>BIOLOGIA,GEOLOGIA</t>
@@ -13215,7 +13215,7 @@
         <v>1525</v>
       </c>
       <c r="H69" t="s">
-        <v>1529</v>
+        <v>1540</v>
       </c>
       <c r="I69" t="s">
         <v>1627</v>
@@ -13413,7 +13413,7 @@
         <v>1528</v>
       </c>
       <c r="H75" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I75" t="s">
         <v>1632</v>
@@ -14042,7 +14042,7 @@
         <v>1525</v>
       </c>
       <c r="H94" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="I94" t="s">
         <v>1640</v>
@@ -14246,7 +14246,7 @@
         <v>1525</v>
       </c>
       <c r="H100" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I100" t="s">
         <v>1612</v>
@@ -14278,7 +14278,7 @@
         <v>1525</v>
       </c>
       <c r="H101" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="I101" t="s">
         <v>1636</v>
@@ -14552,7 +14552,7 @@
         <v>1525</v>
       </c>
       <c r="H109" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="I109" t="s">
         <v>1580</v>
@@ -14756,7 +14756,7 @@
         <v>1525</v>
       </c>
       <c r="H115" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="I115" t="s">
         <v>1609</v>
@@ -15379,7 +15379,7 @@
         <v>1525</v>
       </c>
       <c r="H134" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="I134" t="s">
         <v>1653</v>
@@ -15417,7 +15417,7 @@
         <v>1525</v>
       </c>
       <c r="H135" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="I135" t="s">
         <v>1632</v>
@@ -15493,7 +15493,7 @@
         <v>1525</v>
       </c>
       <c r="H137" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="I137" t="s">
         <v>1654</v>
@@ -15621,7 +15621,7 @@
         <v>1525</v>
       </c>
       <c r="H141" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="I141" t="s">
         <v>1656</v>
@@ -15723,7 +15723,7 @@
         <v>1525</v>
       </c>
       <c r="H144" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="I144" t="s">
         <v>1606</v>
@@ -15915,7 +15915,7 @@
         <v>1525</v>
       </c>
       <c r="H150" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I150" t="s">
         <v>1657</v>
@@ -15947,7 +15947,7 @@
         <v>1525</v>
       </c>
       <c r="H151" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="I151" t="s">
         <v>1585</v>
@@ -16468,7 +16468,7 @@
         <v>1525</v>
       </c>
       <c r="H167" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="I167" t="s">
         <v>1606</v>
@@ -16666,7 +16666,7 @@
         <v>1526</v>
       </c>
       <c r="H173" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="I173" t="s">
         <v>1578</v>
@@ -16768,7 +16768,7 @@
         <v>1525</v>
       </c>
       <c r="H176" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I176" t="s">
         <v>1656</v>
@@ -17473,7 +17473,7 @@
         <v>1525</v>
       </c>
       <c r="H197" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I197" t="s">
         <v>1593</v>
@@ -17549,7 +17549,7 @@
         <v>1525</v>
       </c>
       <c r="H199" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="I199" t="s">
         <v>1674</v>
@@ -18467,7 +18467,7 @@
         <v>1525</v>
       </c>
       <c r="H226" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I226" t="s">
         <v>1681</v>
@@ -19172,7 +19172,7 @@
         <v>1526</v>
       </c>
       <c r="H247" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="I247" t="s">
         <v>1686</v>
@@ -19405,7 +19405,7 @@
         <v>1525</v>
       </c>
       <c r="H254" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="I254" t="s">
         <v>1615</v>
@@ -19638,7 +19638,7 @@
         <v>1525</v>
       </c>
       <c r="H261" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="I261" t="s">
         <v>1671</v>
@@ -19708,7 +19708,7 @@
         <v>1525</v>
       </c>
       <c r="H263" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="I263" t="s">
         <v>1633</v>
@@ -19804,7 +19804,7 @@
         <v>1527</v>
       </c>
       <c r="H266" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="I266" t="s">
         <v>1591</v>
@@ -20215,7 +20215,7 @@
         <v>1525</v>
       </c>
       <c r="H278" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="I278" t="s">
         <v>1620</v>
@@ -20736,7 +20736,7 @@
         <v>1525</v>
       </c>
       <c r="H294" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="I294" t="s">
         <v>1581</v>
@@ -20806,7 +20806,7 @@
         <v>1525</v>
       </c>
       <c r="H296" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="I296" t="s">
         <v>1678</v>
@@ -21170,7 +21170,7 @@
         <v>1526</v>
       </c>
       <c r="H307" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I307" t="s">
         <v>1592</v>
@@ -21828,7 +21828,7 @@
         <v>1525</v>
       </c>
       <c r="H327" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="I327" t="s">
         <v>1581</v>
@@ -21866,7 +21866,7 @@
         <v>1525</v>
       </c>
       <c r="H328" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="I328" t="s">
         <v>1699</v>
@@ -22198,7 +22198,7 @@
         <v>1525</v>
       </c>
       <c r="H338" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I338" t="s">
         <v>1701</v>
@@ -22332,7 +22332,7 @@
         <v>1525</v>
       </c>
       <c r="H342" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="I342" t="s">
         <v>1661</v>
@@ -22504,7 +22504,7 @@
         <v>1525</v>
       </c>
       <c r="H347" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I347" t="s">
         <v>1703</v>
@@ -22862,7 +22862,7 @@
         <v>1525</v>
       </c>
       <c r="H358" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I358" t="s">
         <v>1632</v>
@@ -23124,7 +23124,7 @@
         <v>1525</v>
       </c>
       <c r="H366" t="s">
-        <v>1565</v>
+        <v>1540</v>
       </c>
       <c r="I366" t="s">
         <v>1615</v>
@@ -23357,7 +23357,7 @@
         <v>1525</v>
       </c>
       <c r="H373" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="I373" t="s">
         <v>1614</v>
@@ -23555,7 +23555,7 @@
         <v>1525</v>
       </c>
       <c r="H379" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="I379" t="s">
         <v>1636</v>
@@ -23654,7 +23654,7 @@
         <v>1525</v>
       </c>
       <c r="H382" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="I382" t="s">
         <v>1707</v>
@@ -24006,7 +24006,7 @@
         <v>1525</v>
       </c>
       <c r="H393" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I393" t="s">
         <v>1702</v>
@@ -24335,7 +24335,7 @@
         <v>1525</v>
       </c>
       <c r="H403" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="I403" t="s">
         <v>1713</v>
@@ -25206,7 +25206,7 @@
         <v>1525</v>
       </c>
       <c r="H429" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="I429" t="s">
         <v>1678</v>
@@ -25244,7 +25244,7 @@
         <v>1525</v>
       </c>
       <c r="H430" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I430" t="s">
         <v>1691</v>
@@ -25509,7 +25509,7 @@
         <v>1525</v>
       </c>
       <c r="H438" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="I438" t="s">
         <v>1659</v>
@@ -26042,7 +26042,7 @@
         <v>1525</v>
       </c>
       <c r="H454" t="s">
-        <v>1565</v>
+        <v>1540</v>
       </c>
       <c r="I454" t="s">
         <v>1656</v>
@@ -26619,7 +26619,7 @@
         <v>1525</v>
       </c>
       <c r="H471" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="I471" t="s">
         <v>1645</v>
@@ -27254,7 +27254,7 @@
         <v>1527</v>
       </c>
       <c r="H490" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="I490" t="s">
         <v>1723</v>
@@ -27554,7 +27554,7 @@
         <v>1525</v>
       </c>
       <c r="H499" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I499" t="s">
         <v>1689</v>
@@ -27918,7 +27918,7 @@
         <v>1525</v>
       </c>
       <c r="H510" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="I510" t="s">
         <v>1685</v>
@@ -28256,7 +28256,7 @@
         <v>1525</v>
       </c>
       <c r="H520" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I520" t="s">
         <v>1678</v>
@@ -28632,7 +28632,7 @@
         <v>1525</v>
       </c>
       <c r="H531" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="I531" t="s">
         <v>1713</v>
@@ -29057,7 +29057,7 @@
         <v>1525</v>
       </c>
       <c r="H544" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="I544" t="s">
         <v>1691</v>
@@ -29541,7 +29541,7 @@
         <v>1528</v>
       </c>
       <c r="H558" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="I558" t="s">
         <v>1581</v>
@@ -30109,7 +30109,7 @@
         <v>1525</v>
       </c>
       <c r="H575" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="I575" t="s">
         <v>1585</v>
@@ -30415,7 +30415,7 @@
         <v>1528</v>
       </c>
       <c r="H584" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="I584" t="s">
         <v>1623</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14311,7 +14311,7 @@
         <v>1525</v>
       </c>
       <c r="H102" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="I102" t="s">
         <v>1643</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -12681,7 +12681,7 @@
         <v>45908</v>
       </c>
       <c r="G34" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="H34" t="s">
         <v>1612</v>
@@ -13953,7 +13953,7 @@
         <v>45994</v>
       </c>
       <c r="G73" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="H73" t="s">
         <v>1631</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -31170,7 +31170,7 @@
         <v>1623</v>
       </c>
       <c r="H585" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="I585" t="s">
         <v>1713</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14337,7 +14337,7 @@
         <v>1623</v>
       </c>
       <c r="H81" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="I81" t="s">
         <v>1740</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -22316,7 +22316,7 @@
         <v>1623</v>
       </c>
       <c r="H319" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="I319" t="s">
         <v>1730</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -4924,6 +4924,9 @@
     <t>###   SEM TEMA   ###</t>
   </si>
   <si>
+    <t>MEDICINA LEGAL</t>
+  </si>
+  <si>
     <t>URBANISMO</t>
   </si>
   <si>
@@ -4931,9 +4934,6 @@
   </si>
   <si>
     <t>FARMÁCIA,SAÚDE</t>
-  </si>
-  <si>
-    <t>MEDICINA LEGAL</t>
   </si>
   <si>
     <t>PATRIMÔNIO HISTÓRICO E CULTURAL</t>
@@ -12020,7 +12020,7 @@
         <v>1627</v>
       </c>
       <c r="H10" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="I10" t="s">
         <v>1692</v>
@@ -12058,7 +12058,7 @@
         <v>1630</v>
       </c>
       <c r="H11" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I11" t="s">
         <v>1693</v>
@@ -12186,7 +12186,7 @@
         <v>1628</v>
       </c>
       <c r="H15" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="I15" t="s">
         <v>1695</v>
@@ -12288,7 +12288,7 @@
         <v>1627</v>
       </c>
       <c r="H18" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="I18" t="s">
         <v>1698</v>
@@ -12326,7 +12326,7 @@
         <v>1627</v>
       </c>
       <c r="H19" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I19" t="s">
         <v>1699</v>
@@ -12524,7 +12524,7 @@
         <v>1627</v>
       </c>
       <c r="H25" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I25" t="s">
         <v>1705</v>
@@ -12559,7 +12559,7 @@
         <v>1627</v>
       </c>
       <c r="H26" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I26" t="s">
         <v>1706</v>
@@ -14355,7 +14355,7 @@
         <v>1627</v>
       </c>
       <c r="H81" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I81" t="s">
         <v>1744</v>
@@ -15363,7 +15363,7 @@
         <v>1627</v>
       </c>
       <c r="H111" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I111" t="s">
         <v>1756</v>
@@ -15640,7 +15640,7 @@
         <v>1628</v>
       </c>
       <c r="H119" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I119" t="s">
         <v>1710</v>
@@ -15879,7 +15879,7 @@
         <v>1627</v>
       </c>
       <c r="H126" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I126" t="s">
         <v>1760</v>
@@ -16109,7 +16109,7 @@
         <v>1629</v>
       </c>
       <c r="H133" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I133" t="s">
         <v>1762</v>
@@ -16505,7 +16505,7 @@
         <v>1627</v>
       </c>
       <c r="H145" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I145" t="s">
         <v>1766</v>
@@ -16543,7 +16543,7 @@
         <v>1627</v>
       </c>
       <c r="H146" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I146" t="s">
         <v>1745</v>
@@ -17789,7 +17789,7 @@
         <v>1627</v>
       </c>
       <c r="H184" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I184" t="s">
         <v>1775</v>
@@ -19127,7 +19127,7 @@
         <v>1627</v>
       </c>
       <c r="H223" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I223" t="s">
         <v>1790</v>
@@ -19488,7 +19488,7 @@
         <v>1629</v>
       </c>
       <c r="H234" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I234" t="s">
         <v>1698</v>
@@ -20400,7 +20400,7 @@
         <v>1628</v>
       </c>
       <c r="H261" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I261" t="s">
         <v>1799</v>
@@ -20930,7 +20930,7 @@
         <v>1627</v>
       </c>
       <c r="H277" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I277" t="s">
         <v>1804</v>
@@ -21303,7 +21303,7 @@
         <v>1627</v>
       </c>
       <c r="H288" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I288" t="s">
         <v>1734</v>
@@ -21990,7 +21990,7 @@
         <v>1627</v>
       </c>
       <c r="H309" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I309" t="s">
         <v>1810</v>
@@ -22200,7 +22200,7 @@
         <v>1627</v>
       </c>
       <c r="H315" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="I315" t="s">
         <v>1698</v>
@@ -22334,7 +22334,7 @@
         <v>1627</v>
       </c>
       <c r="H319" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I319" t="s">
         <v>1734</v>
@@ -23936,7 +23936,7 @@
         <v>1627</v>
       </c>
       <c r="H367" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I367" t="s">
         <v>1773</v>
@@ -25153,7 +25153,7 @@
         <v>1627</v>
       </c>
       <c r="H404" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I404" t="s">
         <v>1822</v>
@@ -26976,7 +26976,7 @@
         <v>1627</v>
       </c>
       <c r="H459" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="I459" t="s">
         <v>1698</v>
@@ -27509,7 +27509,7 @@
         <v>1627</v>
       </c>
       <c r="H475" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I475" t="s">
         <v>1691</v>
@@ -28086,7 +28086,7 @@
         <v>1627</v>
       </c>
       <c r="H492" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I492" t="s">
         <v>1712</v>
@@ -28928,7 +28928,7 @@
         <v>1627</v>
       </c>
       <c r="H517" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I517" t="s">
         <v>1805</v>
@@ -29583,7 +29583,7 @@
         <v>1627</v>
       </c>
       <c r="H537" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I537" t="s">
         <v>1738</v>
@@ -30396,7 +30396,7 @@
         <v>1627</v>
       </c>
       <c r="H561" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I561" t="s">
         <v>1839</v>
@@ -31016,7 +31016,7 @@
         <v>1628</v>
       </c>
       <c r="H580" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="I580" t="s">
         <v>1695</v>
@@ -31226,7 +31226,7 @@
         <v>1627</v>
       </c>
       <c r="H586" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I586" t="s">
         <v>1717</v>
@@ -32126,7 +32126,7 @@
         <v>1627</v>
       </c>
       <c r="H613" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I613" t="s">
         <v>1693</v>
@@ -32298,7 +32298,7 @@
         <v>1628</v>
       </c>
       <c r="H618" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="I618" t="s">
         <v>1842</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -28644,7 +28644,7 @@
         <v>1625</v>
       </c>
       <c r="H509" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="I509" t="s">
         <v>1715</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -30078,7 +30078,7 @@
         <v>1576</v>
       </c>
       <c r="F546" s="2">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="G546" t="s">
         <v>1655</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -26243,7 +26243,7 @@
         <v>1662</v>
       </c>
       <c r="H430" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="I430" t="s">
         <v>1754</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -4546,6 +4546,9 @@
     <t>19/03/2026</t>
   </si>
   <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
     <t>03/09/2025</t>
   </si>
   <si>
@@ -4690,7 +4693,7 @@
     <t>15/06/2025</t>
   </si>
   <si>
-    <t>07/11/2025</t>
+    <t>06/05/2026</t>
   </si>
   <si>
     <t>16/04/2025</t>
@@ -4784,9 +4787,6 @@
   </si>
   <si>
     <t>21/11/2024</t>
-  </si>
-  <si>
-    <t>06/05/2026</t>
   </si>
   <si>
     <t>21/10/2024</t>
@@ -12297,7 +12297,7 @@
         <v>1354</v>
       </c>
       <c r="E11" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="F11" s="2">
         <v>45922</v>
@@ -12524,7 +12524,7 @@
         <v>1329</v>
       </c>
       <c r="D18" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="E18" t="s">
         <v>1653</v>
@@ -12667,7 +12667,7 @@
         <v>1608</v>
       </c>
       <c r="E22" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F22" s="2">
         <v>46125</v>
@@ -12798,7 +12798,7 @@
         <v>1337</v>
       </c>
       <c r="D26" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F26" s="2">
         <v>45889</v>
@@ -13997,7 +13997,7 @@
         <v>1441</v>
       </c>
       <c r="E63" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F63" s="2">
         <v>46112</v>
@@ -14661,10 +14661,10 @@
         <v>1385</v>
       </c>
       <c r="D83" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="E83" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="F83" s="2">
         <v>45690</v>
@@ -15124,7 +15124,7 @@
         <v>1393</v>
       </c>
       <c r="D97" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="F97" s="2">
         <v>45972</v>
@@ -15599,10 +15599,10 @@
         <v>1401</v>
       </c>
       <c r="D111" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E111" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F111" s="2">
         <v>46113</v>
@@ -15637,7 +15637,7 @@
         <v>1402</v>
       </c>
       <c r="D112" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F112" s="2">
         <v>46009</v>
@@ -15876,10 +15876,10 @@
         <v>1405</v>
       </c>
       <c r="D119" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="E119" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="F119" s="2">
         <v>46127</v>
@@ -16080,7 +16080,7 @@
         <v>1411</v>
       </c>
       <c r="D125" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E125" t="s">
         <v>1656</v>
@@ -16386,7 +16386,7 @@
         <v>1414</v>
       </c>
       <c r="E134" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F134" s="2">
         <v>45727</v>
@@ -16590,7 +16590,7 @@
         <v>1608</v>
       </c>
       <c r="E140" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F140" s="2">
         <v>46126</v>
@@ -17900,7 +17900,7 @@
         <v>1444</v>
       </c>
       <c r="D180" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="E180" t="s">
         <v>1606</v>
@@ -18541,7 +18541,7 @@
         <v>1356</v>
       </c>
       <c r="D199" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F199" s="2">
         <v>45972</v>
@@ -18905,10 +18905,10 @@
         <v>1434</v>
       </c>
       <c r="D210" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="E210" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F210" s="2">
         <v>45869</v>
@@ -19220,7 +19220,7 @@
         <v>1622</v>
       </c>
       <c r="E219" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F219" s="2">
         <v>45838</v>
@@ -19296,7 +19296,7 @@
         <v>1623</v>
       </c>
       <c r="E221" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F221" s="2">
         <v>46009</v>
@@ -20059,10 +20059,10 @@
         <v>1480</v>
       </c>
       <c r="D244" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="E244" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F244" s="2">
         <v>45860</v>
@@ -21399,7 +21399,7 @@
         <v>1393</v>
       </c>
       <c r="E284" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F284" s="2">
         <v>45919</v>
@@ -21804,7 +21804,7 @@
         <v>1631</v>
       </c>
       <c r="E296" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F296" s="2">
         <v>45952</v>
@@ -21874,7 +21874,7 @@
         <v>1632</v>
       </c>
       <c r="E298" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F298" s="2">
         <v>45818</v>
@@ -22040,10 +22040,10 @@
         <v>964</v>
       </c>
       <c r="C303" t="s">
-        <v>1316</v>
+        <v>1510</v>
       </c>
       <c r="F303" s="2">
-        <v>45994</v>
+        <v>46154</v>
       </c>
       <c r="G303" t="s">
         <v>1666</v>
@@ -22104,7 +22104,7 @@
         <v>966</v>
       </c>
       <c r="C305" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="F305" s="2">
         <v>45994</v>
@@ -22136,7 +22136,7 @@
         <v>967</v>
       </c>
       <c r="C306" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="F306" s="2">
         <v>46044</v>
@@ -22203,7 +22203,7 @@
         <v>969</v>
       </c>
       <c r="C308" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F308" s="2">
         <v>45965</v>
@@ -22363,7 +22363,7 @@
         <v>974</v>
       </c>
       <c r="C313" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F313" s="2">
         <v>46118</v>
@@ -22459,7 +22459,7 @@
         <v>977</v>
       </c>
       <c r="C316" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F316" s="2">
         <v>45754</v>
@@ -22491,7 +22491,7 @@
         <v>978</v>
       </c>
       <c r="C317" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F317" s="2">
         <v>46050</v>
@@ -22593,7 +22593,7 @@
         <v>981</v>
       </c>
       <c r="C320" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="F320" s="2">
         <v>45883</v>
@@ -22625,7 +22625,7 @@
         <v>982</v>
       </c>
       <c r="C321" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="D321" t="s">
         <v>1451</v>
@@ -22663,7 +22663,7 @@
         <v>983</v>
       </c>
       <c r="C322" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="F322" s="2">
         <v>46043</v>
@@ -22698,10 +22698,10 @@
         <v>1378</v>
       </c>
       <c r="D323" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="E323" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F323" s="2">
         <v>45937</v>
@@ -22733,7 +22733,7 @@
         <v>985</v>
       </c>
       <c r="C324" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F324" s="2">
         <v>45887</v>
@@ -22765,7 +22765,7 @@
         <v>986</v>
       </c>
       <c r="C325" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="D325" t="s">
         <v>1636</v>
@@ -22835,7 +22835,7 @@
         <v>988</v>
       </c>
       <c r="C327" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="F327" s="2">
         <v>46129</v>
@@ -22899,7 +22899,7 @@
         <v>990</v>
       </c>
       <c r="C329" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="F329" s="2">
         <v>46149</v>
@@ -22963,7 +22963,7 @@
         <v>992</v>
       </c>
       <c r="C331" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="F331" s="2">
         <v>45799</v>
@@ -22995,7 +22995,7 @@
         <v>993</v>
       </c>
       <c r="C332" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F332" s="2">
         <v>46118</v>
@@ -23155,13 +23155,13 @@
         <v>998</v>
       </c>
       <c r="C337" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D337" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="E337" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F337" s="2">
         <v>45972</v>
@@ -23193,7 +23193,7 @@
         <v>999</v>
       </c>
       <c r="C338" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D338" t="s">
         <v>1637</v>
@@ -23231,7 +23231,7 @@
         <v>1000</v>
       </c>
       <c r="C339" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="F339" s="2">
         <v>45680</v>
@@ -23263,7 +23263,7 @@
         <v>1001</v>
       </c>
       <c r="C340" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="D340" t="s">
         <v>1353</v>
@@ -23333,7 +23333,7 @@
         <v>1003</v>
       </c>
       <c r="C342" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F342" s="2">
         <v>46149</v>
@@ -23365,7 +23365,7 @@
         <v>1004</v>
       </c>
       <c r="C343" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F343" s="2">
         <v>45818</v>
@@ -23429,13 +23429,13 @@
         <v>1006</v>
       </c>
       <c r="C345" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D345" t="s">
         <v>1608</v>
       </c>
       <c r="E345" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F345" s="2">
         <v>46112</v>
@@ -23563,7 +23563,7 @@
         <v>1010</v>
       </c>
       <c r="C349" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F349" s="2">
         <v>46010</v>
@@ -23595,7 +23595,7 @@
         <v>1011</v>
       </c>
       <c r="C350" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F350" s="2">
         <v>46149</v>
@@ -23627,7 +23627,7 @@
         <v>1012</v>
       </c>
       <c r="C351" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F351" s="2">
         <v>45812</v>
@@ -23691,7 +23691,7 @@
         <v>1014</v>
       </c>
       <c r="C353" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F353" s="2">
         <v>45811</v>
@@ -23755,7 +23755,7 @@
         <v>1016</v>
       </c>
       <c r="C355" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F355" s="2">
         <v>45883</v>
@@ -23787,7 +23787,7 @@
         <v>1017</v>
       </c>
       <c r="C356" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="F356" s="2">
         <v>45846</v>
@@ -23883,7 +23883,7 @@
         <v>1020</v>
       </c>
       <c r="C359" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F359" s="2">
         <v>45870</v>
@@ -23915,7 +23915,7 @@
         <v>1021</v>
       </c>
       <c r="C360" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="F360" s="2">
         <v>45751</v>
@@ -23947,7 +23947,7 @@
         <v>1022</v>
       </c>
       <c r="C361" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="D361" t="s">
         <v>1638</v>
@@ -24029,7 +24029,7 @@
         <v>1350</v>
       </c>
       <c r="E363" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F363" s="2">
         <v>45771</v>
@@ -24093,7 +24093,7 @@
         <v>1026</v>
       </c>
       <c r="C365" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F365" s="2">
         <v>45728</v>
@@ -24157,13 +24157,13 @@
         <v>1028</v>
       </c>
       <c r="C367" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D367" t="s">
         <v>1639</v>
       </c>
       <c r="E367" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F367" s="2">
         <v>46139</v>
@@ -24259,7 +24259,7 @@
         <v>1031</v>
       </c>
       <c r="C370" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F370" s="2">
         <v>46092</v>
@@ -24294,10 +24294,10 @@
         <v>1457</v>
       </c>
       <c r="D371" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="E371" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="F371" s="2">
         <v>46091</v>
@@ -24329,7 +24329,7 @@
         <v>1033</v>
       </c>
       <c r="C372" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F372" s="2">
         <v>46035</v>
@@ -24399,7 +24399,7 @@
         <v>1035</v>
       </c>
       <c r="C374" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="F374" s="2">
         <v>45659</v>
@@ -24431,7 +24431,7 @@
         <v>1036</v>
       </c>
       <c r="C375" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F375" s="2">
         <v>45891</v>
@@ -24495,7 +24495,7 @@
         <v>1038</v>
       </c>
       <c r="C377" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="F377" s="2">
         <v>45728</v>
@@ -24527,7 +24527,7 @@
         <v>1039</v>
       </c>
       <c r="C378" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="D378" t="s">
         <v>1338</v>
@@ -24629,7 +24629,7 @@
         <v>1042</v>
       </c>
       <c r="C381" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="F381" s="2">
         <v>46048</v>
@@ -24664,7 +24664,7 @@
         <v>1391</v>
       </c>
       <c r="D382" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="E382" t="s">
         <v>1403</v>
@@ -24737,7 +24737,7 @@
         <v>1045</v>
       </c>
       <c r="C384" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F384" s="2">
         <v>46044</v>
@@ -24769,7 +24769,7 @@
         <v>1046</v>
       </c>
       <c r="C385" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F385" s="2">
         <v>45868</v>
@@ -24833,7 +24833,7 @@
         <v>1048</v>
       </c>
       <c r="C387" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="F387" s="2">
         <v>46149</v>
@@ -24929,7 +24929,7 @@
         <v>1051</v>
       </c>
       <c r="C390" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F390" s="2">
         <v>46092</v>
@@ -25057,7 +25057,7 @@
         <v>1055</v>
       </c>
       <c r="C394" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="F394" s="2">
         <v>46149</v>
@@ -25121,7 +25121,7 @@
         <v>1057</v>
       </c>
       <c r="C396" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="D396" t="s">
         <v>1641</v>
@@ -25159,7 +25159,7 @@
         <v>1058</v>
       </c>
       <c r="C397" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="F397" s="2">
         <v>45877</v>
@@ -25191,7 +25191,7 @@
         <v>1059</v>
       </c>
       <c r="C398" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D398" t="s">
         <v>1642</v>
@@ -25226,7 +25226,7 @@
         <v>1060</v>
       </c>
       <c r="C399" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F399" s="2">
         <v>46118</v>
@@ -25290,7 +25290,7 @@
         <v>1062</v>
       </c>
       <c r="C401" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F401" s="2">
         <v>45993</v>
@@ -25389,7 +25389,7 @@
         <v>1065</v>
       </c>
       <c r="C404" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="F404" s="2">
         <v>46120</v>
@@ -25421,7 +25421,7 @@
         <v>1066</v>
       </c>
       <c r="C405" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="D405" t="s">
         <v>1643</v>
@@ -25488,7 +25488,7 @@
         <v>1068</v>
       </c>
       <c r="C407" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="F407" s="2">
         <v>45853</v>
@@ -25552,7 +25552,7 @@
         <v>1070</v>
       </c>
       <c r="C409" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="F409" s="2">
         <v>45852</v>
@@ -25651,7 +25651,7 @@
         <v>1073</v>
       </c>
       <c r="C412" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="F412" s="2">
         <v>46035</v>
@@ -25683,10 +25683,10 @@
         <v>1074</v>
       </c>
       <c r="C413" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="F413" s="2">
-        <v>46044</v>
+        <v>46154</v>
       </c>
       <c r="G413" t="s">
         <v>1666</v>
@@ -25753,7 +25753,7 @@
         <v>1076</v>
       </c>
       <c r="C415" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="F415" s="2">
         <v>45946</v>
@@ -25913,7 +25913,7 @@
         <v>1081</v>
       </c>
       <c r="C420" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D420" t="s">
         <v>1644</v>
@@ -25951,7 +25951,7 @@
         <v>1082</v>
       </c>
       <c r="C421" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="F421" s="2">
         <v>45825</v>
@@ -26018,7 +26018,7 @@
         <v>1320</v>
       </c>
       <c r="D423" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F423" s="2">
         <v>45952</v>
@@ -26242,7 +26242,7 @@
         <v>1091</v>
       </c>
       <c r="C430" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F430" s="2">
         <v>46112</v>
@@ -26274,7 +26274,7 @@
         <v>1092</v>
       </c>
       <c r="C431" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F431" s="2">
         <v>45680</v>
@@ -26370,7 +26370,7 @@
         <v>1095</v>
       </c>
       <c r="C434" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F434" s="2">
         <v>45714</v>
@@ -26402,7 +26402,7 @@
         <v>1096</v>
       </c>
       <c r="C435" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F435" s="2">
         <v>45671</v>
@@ -26504,7 +26504,7 @@
         <v>1415</v>
       </c>
       <c r="E438" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F438" s="2">
         <v>45929</v>
@@ -26536,7 +26536,7 @@
         <v>1100</v>
       </c>
       <c r="C439" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="F439" s="2">
         <v>45799</v>
@@ -26699,7 +26699,7 @@
         <v>1427</v>
       </c>
       <c r="D444" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F444" s="2">
         <v>45812</v>
@@ -26763,7 +26763,7 @@
         <v>1107</v>
       </c>
       <c r="C446" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="F446" s="2">
         <v>45994</v>
@@ -26859,7 +26859,7 @@
         <v>1110</v>
       </c>
       <c r="C449" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="F449" s="2">
         <v>45673</v>
@@ -26891,7 +26891,7 @@
         <v>1111</v>
       </c>
       <c r="C450" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F450" s="2">
         <v>45919</v>
@@ -27019,7 +27019,7 @@
         <v>1115</v>
       </c>
       <c r="C454" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="D454" t="s">
         <v>1470</v>
@@ -27095,7 +27095,7 @@
         <v>1117</v>
       </c>
       <c r="C456" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F456" s="2">
         <v>45989</v>
@@ -27127,7 +27127,7 @@
         <v>1118</v>
       </c>
       <c r="C457" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D457" t="s">
         <v>1639</v>
@@ -27200,7 +27200,7 @@
         <v>1363</v>
       </c>
       <c r="E459" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F459" s="2">
         <v>45924</v>
@@ -27296,7 +27296,7 @@
         <v>1123</v>
       </c>
       <c r="C462" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="D462" t="s">
         <v>1488</v>
@@ -27337,7 +27337,7 @@
         <v>1394</v>
       </c>
       <c r="D463" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="E463" t="s">
         <v>1347</v>
@@ -27404,7 +27404,7 @@
         <v>1126</v>
       </c>
       <c r="C465" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="F465" s="2">
         <v>45693</v>
@@ -27436,7 +27436,7 @@
         <v>1127</v>
       </c>
       <c r="C466" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F466" s="2">
         <v>45735</v>
@@ -27468,7 +27468,7 @@
         <v>1128</v>
       </c>
       <c r="C467" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F467" s="2">
         <v>46028</v>
@@ -27503,10 +27503,10 @@
         <v>1339</v>
       </c>
       <c r="D468" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="E468" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F468" s="2">
         <v>46118</v>
@@ -27538,7 +27538,7 @@
         <v>1130</v>
       </c>
       <c r="C469" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F469" s="2">
         <v>45812</v>
@@ -27605,7 +27605,7 @@
         <v>1132</v>
       </c>
       <c r="C471" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F471" s="2">
         <v>46148</v>
@@ -27637,7 +27637,7 @@
         <v>1133</v>
       </c>
       <c r="C472" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F472" s="2">
         <v>46044</v>
@@ -27742,10 +27742,10 @@
         <v>1428</v>
       </c>
       <c r="D475" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="E475" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F475" s="2">
         <v>45811</v>
@@ -27777,7 +27777,7 @@
         <v>1137</v>
       </c>
       <c r="C476" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F476" s="2">
         <v>45897</v>
@@ -27841,7 +27841,7 @@
         <v>1139</v>
       </c>
       <c r="C478" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F478" s="2">
         <v>45754</v>
@@ -27905,7 +27905,7 @@
         <v>1141</v>
       </c>
       <c r="C480" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="D480" t="s">
         <v>1645</v>
@@ -28042,7 +28042,7 @@
         <v>1145</v>
       </c>
       <c r="C484" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F484" s="2">
         <v>45995</v>
@@ -28240,7 +28240,7 @@
         <v>1621</v>
       </c>
       <c r="E490" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F490" s="2">
         <v>45992</v>
@@ -28272,7 +28272,7 @@
         <v>1152</v>
       </c>
       <c r="C491" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F491" s="2">
         <v>46010</v>
@@ -28304,7 +28304,7 @@
         <v>1153</v>
       </c>
       <c r="C492" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D492" t="s">
         <v>1392</v>
@@ -28339,7 +28339,7 @@
         <v>1154</v>
       </c>
       <c r="C493" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="F493" s="2">
         <v>45849</v>
@@ -28435,7 +28435,7 @@
         <v>1157</v>
       </c>
       <c r="C496" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F496" s="2">
         <v>45811</v>
@@ -28543,7 +28543,7 @@
         <v>1160</v>
       </c>
       <c r="C499" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F499" s="2">
         <v>45684</v>
@@ -28575,7 +28575,7 @@
         <v>1161</v>
       </c>
       <c r="C500" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="F500" s="2">
         <v>46092</v>
@@ -28607,7 +28607,7 @@
         <v>1162</v>
       </c>
       <c r="C501" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="D501" t="s">
         <v>1647</v>
@@ -28782,7 +28782,7 @@
         <v>1344</v>
       </c>
       <c r="D506" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="E506" t="s">
         <v>1477</v>
@@ -28817,7 +28817,7 @@
         <v>1168</v>
       </c>
       <c r="C507" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F507" s="2">
         <v>45722</v>
@@ -28945,7 +28945,7 @@
         <v>1172</v>
       </c>
       <c r="C511" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F511" s="2">
         <v>45994</v>
@@ -29012,7 +29012,7 @@
         <v>1174</v>
       </c>
       <c r="C513" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D513" t="s">
         <v>1478</v>
@@ -29050,7 +29050,7 @@
         <v>1175</v>
       </c>
       <c r="C514" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F514" s="2">
         <v>45679</v>
@@ -29085,10 +29085,10 @@
         <v>1448</v>
       </c>
       <c r="D515" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="E515" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F515" s="2">
         <v>45915</v>
@@ -29420,7 +29420,7 @@
         <v>1186</v>
       </c>
       <c r="C525" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F525" s="2">
         <v>45824</v>
@@ -29519,7 +29519,7 @@
         <v>1189</v>
       </c>
       <c r="C528" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F528" s="2">
         <v>46093</v>
@@ -29551,13 +29551,13 @@
         <v>1190</v>
       </c>
       <c r="C529" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="D529" t="s">
         <v>1473</v>
       </c>
       <c r="E529" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F529" s="2">
         <v>45750</v>
@@ -29621,7 +29621,7 @@
         <v>1192</v>
       </c>
       <c r="C531" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F531" s="2">
         <v>45946</v>
@@ -29653,7 +29653,7 @@
         <v>1193</v>
       </c>
       <c r="C532" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F532" s="2">
         <v>45751</v>
@@ -29781,7 +29781,7 @@
         <v>1197</v>
       </c>
       <c r="C536" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="F536" s="2">
         <v>45994</v>
@@ -29851,7 +29851,7 @@
         <v>1199</v>
       </c>
       <c r="C538" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F538" s="2">
         <v>46049</v>
@@ -29979,7 +29979,7 @@
         <v>1203</v>
       </c>
       <c r="C542" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F542" s="2">
         <v>45722</v>
@@ -30011,7 +30011,7 @@
         <v>1204</v>
       </c>
       <c r="C543" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="F543" s="2">
         <v>45994</v>
@@ -30043,7 +30043,7 @@
         <v>1205</v>
       </c>
       <c r="C544" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="D544" t="s">
         <v>1405</v>
@@ -30081,7 +30081,7 @@
         <v>1206</v>
       </c>
       <c r="C545" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F545" s="2">
         <v>46127</v>
@@ -30113,7 +30113,7 @@
         <v>1207</v>
       </c>
       <c r="C546" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="F546" s="2">
         <v>45730</v>
@@ -30148,7 +30148,7 @@
         <v>1376</v>
       </c>
       <c r="D547" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F547" s="2">
         <v>45709</v>
@@ -30404,7 +30404,7 @@
         <v>1216</v>
       </c>
       <c r="C555" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="D555" t="s">
         <v>1649</v>
@@ -30503,7 +30503,7 @@
         <v>1219</v>
       </c>
       <c r="C558" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="D558" t="s">
         <v>1650</v>
@@ -30541,7 +30541,7 @@
         <v>1220</v>
       </c>
       <c r="C559" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F559" s="2">
         <v>45751</v>
@@ -30637,7 +30637,7 @@
         <v>1223</v>
       </c>
       <c r="C562" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="F562" s="2">
         <v>45684</v>
@@ -30733,7 +30733,7 @@
         <v>1226</v>
       </c>
       <c r="C565" t="s">
-        <v>1590</v>
+        <v>1559</v>
       </c>
       <c r="F565" s="2">
         <v>46150</v>
@@ -30978,10 +30978,10 @@
         <v>1448</v>
       </c>
       <c r="D572" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="E572" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F572" s="2">
         <v>45992</v>
@@ -31115,7 +31115,7 @@
         <v>1237</v>
       </c>
       <c r="C576" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F576" s="2">
         <v>45751</v>
@@ -31153,7 +31153,7 @@
         <v>1623</v>
       </c>
       <c r="E577" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F577" s="2">
         <v>45946</v>
@@ -31185,7 +31185,7 @@
         <v>1239</v>
       </c>
       <c r="C578" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F578" s="2">
         <v>45888</v>
@@ -31281,13 +31281,13 @@
         <v>1242</v>
       </c>
       <c r="C581" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D581" t="s">
         <v>1507</v>
       </c>
       <c r="E581" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F581" s="2">
         <v>45894</v>
@@ -31319,7 +31319,7 @@
         <v>1243</v>
       </c>
       <c r="C582" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F582" s="2">
         <v>46010</v>
@@ -31450,7 +31450,7 @@
         <v>1247</v>
       </c>
       <c r="C586" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F586" s="2">
         <v>46112</v>
@@ -31482,7 +31482,7 @@
         <v>1248</v>
       </c>
       <c r="C587" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F587" s="2">
         <v>45735</v>
@@ -31546,7 +31546,7 @@
         <v>1250</v>
       </c>
       <c r="C589" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F589" s="2">
         <v>45715</v>
@@ -31980,7 +31980,7 @@
         <v>1350</v>
       </c>
       <c r="D602" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F602" s="2">
         <v>45870</v>
@@ -32076,7 +32076,7 @@
         <v>1266</v>
       </c>
       <c r="C605" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="F605" s="2">
         <v>46118</v>
@@ -32175,10 +32175,10 @@
         <v>1598</v>
       </c>
       <c r="D608" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="E608" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="F608" s="2">
         <v>45946</v>
@@ -32216,7 +32216,7 @@
         <v>1349</v>
       </c>
       <c r="E609" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F609" s="2">
         <v>45975</v>
@@ -32280,7 +32280,7 @@
         <v>1272</v>
       </c>
       <c r="C611" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F611" s="2">
         <v>46092</v>
@@ -32350,7 +32350,7 @@
         <v>1358</v>
       </c>
       <c r="E613" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F613" s="2">
         <v>45704</v>
@@ -32516,7 +32516,7 @@
         <v>1279</v>
       </c>
       <c r="C618" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F618" s="2">
         <v>45811</v>
@@ -32586,7 +32586,7 @@
         <v>1391</v>
       </c>
       <c r="E620" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F620" s="2">
         <v>46045</v>
@@ -32650,7 +32650,7 @@
         <v>1283</v>
       </c>
       <c r="C622" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F622" s="2">
         <v>45925</v>
@@ -32714,7 +32714,7 @@
         <v>1285</v>
       </c>
       <c r="C624" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="F624" s="2">
         <v>46091</v>
@@ -32810,7 +32810,7 @@
         <v>1288</v>
       </c>
       <c r="C627" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="F627" s="2">
         <v>46118</v>
@@ -33256,7 +33256,7 @@
         <v>1325</v>
       </c>
       <c r="E640" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="F640" s="2">
         <v>46125</v>
@@ -33326,7 +33326,7 @@
         <v>1303</v>
       </c>
       <c r="C642" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F642" s="2">
         <v>45938</v>
@@ -33428,7 +33428,7 @@
         <v>1306</v>
       </c>
       <c r="C645" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F645" s="2">
         <v>45740</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14682,7 +14682,7 @@
         <v>1674</v>
       </c>
       <c r="H82" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="I82" t="s">
         <v>1793</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -13634,7 +13634,7 @@
         <v>1706</v>
       </c>
       <c r="H44" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="I44" t="s">
         <v>1800</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -4273,7 +4273,7 @@
     <t>27/02/2025</t>
   </si>
   <si>
-    <t>08/05/2026</t>
+    <t>15/06/2026</t>
   </si>
   <si>
     <t>21/05/2025</t>
@@ -13533,7 +13533,7 @@
         <v>1419</v>
       </c>
       <c r="F26" s="2">
-        <v>46169</v>
+        <v>46190</v>
       </c>
       <c r="G26" t="s">
         <v>1776</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -33965,7 +33965,7 @@
         <v>1852</v>
       </c>
       <c r="H622" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="I622" t="s">
         <v>1918</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -15345,7 +15345,7 @@
         <v>1845</v>
       </c>
       <c r="H67" t="s">
-        <v>1853</v>
+        <v>1863</v>
       </c>
       <c r="I67" t="s">
         <v>1951</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -33831,10 +33831,10 @@
         <v>1350</v>
       </c>
       <c r="C619" t="s">
-        <v>1613</v>
+        <v>1732</v>
       </c>
       <c r="F619" s="2">
-        <v>46149</v>
+        <v>46211</v>
       </c>
       <c r="G619" t="s">
         <v>1845</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -22998,7 +22998,7 @@
         <v>1908</v>
       </c>
       <c r="H282" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="I282" t="s">
         <v>2063</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7113" uniqueCount="3633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7115" uniqueCount="3633">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -1027,6 +1027,9 @@
     <t>20.22.0001.0054369.2025-45</t>
   </si>
   <si>
+    <t>20.22.0001.0080581.2025-33</t>
+  </si>
+  <si>
     <t>20.22.0001.0052553.2026-89</t>
   </si>
   <si>
@@ -1771,6 +1774,9 @@
     <t>20.22.0001.0038464.2025-61</t>
   </si>
   <si>
+    <t>20.22.0001.0024156.2026-23</t>
+  </si>
+  <si>
     <t>20.22.0001.0072427.2024-04</t>
   </si>
   <si>
@@ -1876,9 +1882,6 @@
     <t>20.22.0001.0090296.2025-16</t>
   </si>
   <si>
-    <t>20.22.0001.0015609.2025-32</t>
-  </si>
-  <si>
     <t>20.22.0001.0041662.2025-45</t>
   </si>
   <si>
@@ -1900,9 +1903,6 @@
     <t>20.22.0001.0087530.2024-11</t>
   </si>
   <si>
-    <t>20.22.0001.0050560.2025-68</t>
-  </si>
-  <si>
     <t>20.22.0001.0072069.2025-64</t>
   </si>
   <si>
@@ -3271,6 +3271,9 @@
     <t>2025.0965</t>
   </si>
   <si>
+    <t>2025.1451</t>
+  </si>
+  <si>
     <t>2026.0873</t>
   </si>
   <si>
@@ -4015,6 +4018,9 @@
     <t>2025.0649</t>
   </si>
   <si>
+    <t>2026.0413</t>
+  </si>
+  <si>
     <t>2024.0638</t>
   </si>
   <si>
@@ -4120,9 +4126,6 @@
     <t>2025.1644</t>
   </si>
   <si>
-    <t>2025.0242</t>
-  </si>
-  <si>
     <t>2025.0721</t>
   </si>
   <si>
@@ -4142,9 +4145,6 @@
   </si>
   <si>
     <t>2024.0883</t>
-  </si>
-  <si>
-    <t>2025.0907</t>
   </si>
   <si>
     <t>2025.1320</t>
@@ -8400,6 +8400,11 @@
   </si>
   <si>
     <t>"solicitem-se os préstimo ao GATE para elaboração de análise técnica, de modo a esclarecer a eventual ocorrência  de sobrepreço/e ou superfaturamento"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trata-se de Inquérito Civil que apura "Celebração de termos de renovação contratual entre o Município e a COMDEP, entre os anos 2001 e 2008, sem apresentação do orçamento detalhado em planilhas que expressem a composição de todos os custos unitários, contrariando o comando do art,7º§ 2º,ll da lei 8666/93. Possível violação ao princípio da economicidade. Dano ao erário"; 
+Assim, sirvo-me do presente para solicitar análise técnica ao GATE, para que seja feita análise da economicidade dos valores atualmente contratados pelo Município de Petrópolis junto à COMDEP.
+</t>
   </si>
   <si>
     <t>Considerando os elementos constantes dos autos, a realização de reunião
@@ -10002,6 +10007,11 @@
     <t>Solicito análise da proposta de honorários do perito judicial no Processo 0023904-09.2022.8.19.0023, index 247, apontando eventuais inconsistências.</t>
   </si>
   <si>
+    <t>Solicita-se ao GATE a realização de análise técnica da contratação em questão
+com a empresa UNIÃO, com o objetivo de apurar a eventual ocorrência de
+superfaturamento ou sobrepreço, devendo verificar se os preços contratados e pagos foram condizentes com os valores de mercado, e se houve sobrepreço e/ou superfaturamento; se os valores pagos correspondem aos serviços efetivamente prestados, se os serviços prestados foram de acordo com a previsão contratual, analisar se o os serviços previstos no contrato com a KAWA e com a Angeloc possuíam identidade com os serviços contratados com a UNIÃO, com o fim de verificar se houve sobreposição de serviços e pagamentos, entre outros pontos que entender relevantes.</t>
+  </si>
+  <si>
     <t>Solicitamos os bons préstimos do GATE para realizar análise técnica sobre os cinco contratos de maior valor informados (Contratos nº 37/2020, 67/2020, 66/2020, 54/2020 e 53/2020), avaliando se os preços acertados foram compatíveis com aqueles praticados no mercado no contexto da pandemia 
 do COVID-19.</t>
   </si>
@@ -10191,9 +10201,6 @@
 7. Demais considerações reputadas relevantes pelos Ilustres Peritos.</t>
   </si>
   <si>
-    <t>A realização de perícia médica com a finalidade de responder se a morte da vítima JOSÉ VICTOR DE SOUSA GERMANO foi causada por comportamento negligente, imperito ou imprudente da investigada LHYVIA ANDRADE DA SILVA.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Considerando o relato da idosa em situação de sofrimento psíquico, e diante da
 necessidade de garantir que sua manifestação seja acolhida com responsabilidade e em conformidade com os princípios de proteção integral e
 dignidade da pessoa humana, solicita-se a avaliação psiquiátrica por parte GATE deste Ministério Público. </t>
@@ -10224,9 +10231,6 @@
   </si>
   <si>
     <t>Dra. Cristina Monteiro  determina a remessa dos documentos remetidos pelo SESC ao GATE/MPRJ (índex 03448505), solicitando a complementação da IT 771/2024</t>
-  </si>
-  <si>
-    <t>Trata-se de instaurado para apurar notícia de fato sobre possível sobrepreço/superfaturamento na contratação de empresa especializada para execução dos serviços de construção de Pórtico em Monnerat, segundo distrito do Município de Duas Barras/RJ, via certame licitatório na modalidade Carta Convite nº 28/2022, pela Secretaria Municipal de Obras de Duas Barras (Secretário Municipal Marco Antônio Barcelos Júnior). Para tanto, solicita-se que este Ilmo. GATE responda os presentes quesitos que oportunizarão o Parquet a ter conhecimento se houve ou não sobrepreço/superfaturamento: 1) Os preços praticados correspondem aos valores de mercado? 2) Os serviços executados correspondem aos contratados (análise quantitativa e qualitativa)? 3) Os valores pagos estão compatíveis com os contratados? 4) Foi verificado sobrepreço no contrato celebrado? 5) Foi verificado superfaturamento no pagamento dos serviços executados, correspondentes ao contrato celebrado? 6) Se resta constatado dano ao erário, informando, em caso positivo, o seu montante. 7) Quando da análise para responder aos quesitos acima, foram verificadas outras irregularidades? 8) Maiores esclarecimentos a critério da equipe técnica.</t>
   </si>
   <si>
     <t>Solicito ao GATE, em complementação à IT 0784/2018, a produção de nova informação técnica com análise contábil dos documentos que instruíram a contestação do Município de Rio Bonito no Processo 0000696-92.2020.8.19.0046.</t>
@@ -11959,6 +11963,9 @@
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5043462&amp;id_documento=5043463</t>
   </si>
   <si>
+    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5415330&amp;id_documento=5415331</t>
+  </si>
+  <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=6348519&amp;id_documento=6348520</t>
   </si>
   <si>
@@ -12703,6 +12710,9 @@
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4823555&amp;id_documento=4823556</t>
   </si>
   <si>
+    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5934632&amp;id_documento=5934633</t>
+  </si>
+  <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4131587&amp;id_documento=4131588</t>
   </si>
   <si>
@@ -12808,9 +12818,6 @@
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5562345&amp;id_documento=5562346</t>
   </si>
   <si>
-    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4524516&amp;id_documento=4524517</t>
-  </si>
-  <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4867615&amp;id_documento=4867616</t>
   </si>
   <si>
@@ -12830,9 +12837,6 @@
   </si>
   <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4315098&amp;id_documento=4315099</t>
-  </si>
-  <si>
-    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4987780&amp;id_documento=4987781</t>
   </si>
   <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5292635&amp;id_documento=5292636</t>
@@ -24529,19 +24533,25 @@
         <v>1085</v>
       </c>
       <c r="C327" t="s">
-        <v>1726</v>
+        <v>1685</v>
+      </c>
+      <c r="D327" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E327" t="s">
+        <v>1861</v>
       </c>
       <c r="F327" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="G327" t="s">
         <v>1914</v>
       </c>
       <c r="H327" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I327" t="s">
-        <v>1974</v>
+        <v>2018</v>
       </c>
       <c r="J327" t="s">
         <v>2140</v>
@@ -24561,19 +24571,19 @@
         <v>1086</v>
       </c>
       <c r="C328" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="F328" s="2">
-        <v>46043</v>
+        <v>46231</v>
       </c>
       <c r="G328" t="s">
         <v>1914</v>
       </c>
       <c r="H328" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I328" t="s">
-        <v>2046</v>
+        <v>1974</v>
       </c>
       <c r="J328" t="s">
         <v>2140</v>
@@ -24593,22 +24603,22 @@
         <v>1087</v>
       </c>
       <c r="C329" t="s">
-        <v>1522</v>
+        <v>1727</v>
       </c>
       <c r="F329" s="2">
-        <v>45849</v>
+        <v>46043</v>
       </c>
       <c r="G329" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H329" t="s">
         <v>1921</v>
       </c>
       <c r="I329" t="s">
-        <v>2059</v>
+        <v>2046</v>
       </c>
       <c r="J329" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K329" t="s">
         <v>2466</v>
@@ -24625,22 +24635,22 @@
         <v>1088</v>
       </c>
       <c r="C330" t="s">
-        <v>1589</v>
+        <v>1522</v>
       </c>
       <c r="F330" s="2">
-        <v>46196</v>
+        <v>45849</v>
       </c>
       <c r="G330" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H330" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I330" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
       <c r="J330" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K330" t="s">
         <v>2467</v>
@@ -24657,19 +24667,19 @@
         <v>1089</v>
       </c>
       <c r="C331" t="s">
-        <v>1665</v>
+        <v>1589</v>
       </c>
       <c r="F331" s="2">
-        <v>45704</v>
+        <v>46196</v>
       </c>
       <c r="G331" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H331" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="I331" t="s">
-        <v>2011</v>
+        <v>2055</v>
       </c>
       <c r="J331" t="s">
         <v>2140</v>
@@ -24689,19 +24699,19 @@
         <v>1090</v>
       </c>
       <c r="C332" t="s">
-        <v>1609</v>
+        <v>1665</v>
       </c>
       <c r="F332" s="2">
-        <v>45777</v>
+        <v>45704</v>
       </c>
       <c r="G332" t="s">
         <v>1915</v>
       </c>
       <c r="H332" t="s">
-        <v>1941</v>
+        <v>1919</v>
       </c>
       <c r="I332" t="s">
-        <v>2093</v>
+        <v>2011</v>
       </c>
       <c r="J332" t="s">
         <v>2140</v>
@@ -24721,25 +24731,19 @@
         <v>1091</v>
       </c>
       <c r="C333" t="s">
-        <v>1662</v>
-      </c>
-      <c r="D333" t="s">
-        <v>1600</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1749</v>
+        <v>1609</v>
       </c>
       <c r="F333" s="2">
-        <v>45919</v>
+        <v>45777</v>
       </c>
       <c r="G333" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H333" t="s">
-        <v>1958</v>
+        <v>1941</v>
       </c>
       <c r="I333" t="s">
-        <v>2074</v>
+        <v>2093</v>
       </c>
       <c r="J333" t="s">
         <v>2140</v>
@@ -24759,19 +24763,25 @@
         <v>1092</v>
       </c>
       <c r="C334" t="s">
-        <v>1728</v>
+        <v>1662</v>
+      </c>
+      <c r="D334" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1749</v>
       </c>
       <c r="F334" s="2">
-        <v>46185</v>
+        <v>45919</v>
       </c>
       <c r="G334" t="s">
         <v>1914</v>
       </c>
       <c r="H334" t="s">
-        <v>1921</v>
+        <v>1958</v>
       </c>
       <c r="I334" t="s">
-        <v>1976</v>
+        <v>2074</v>
       </c>
       <c r="J334" t="s">
         <v>2140</v>
@@ -24791,19 +24801,19 @@
         <v>1093</v>
       </c>
       <c r="C335" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="F335" s="2">
-        <v>45826</v>
+        <v>46185</v>
       </c>
       <c r="G335" t="s">
         <v>1914</v>
       </c>
       <c r="H335" t="s">
-        <v>1928</v>
+        <v>1921</v>
       </c>
       <c r="I335" t="s">
-        <v>2094</v>
+        <v>1976</v>
       </c>
       <c r="J335" t="s">
         <v>2140</v>
@@ -24823,28 +24833,22 @@
         <v>1094</v>
       </c>
       <c r="C336" t="s">
-        <v>1521</v>
-      </c>
-      <c r="D336" t="s">
-        <v>1534</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1534</v>
+        <v>1729</v>
       </c>
       <c r="F336" s="2">
-        <v>45995</v>
+        <v>45826</v>
       </c>
       <c r="G336" t="s">
         <v>1914</v>
       </c>
       <c r="H336" t="s">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="I336" t="s">
-        <v>2036</v>
+        <v>2094</v>
       </c>
       <c r="J336" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K336" t="s">
         <v>2473</v>
@@ -24861,19 +24865,25 @@
         <v>1095</v>
       </c>
       <c r="C337" t="s">
-        <v>1539</v>
+        <v>1521</v>
+      </c>
+      <c r="D337" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1534</v>
       </c>
       <c r="F337" s="2">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="G337" t="s">
         <v>1914</v>
       </c>
       <c r="H337" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I337" t="s">
-        <v>2059</v>
+        <v>2036</v>
       </c>
       <c r="J337" t="s">
         <v>2141</v>
@@ -24893,19 +24903,19 @@
         <v>1096</v>
       </c>
       <c r="C338" t="s">
-        <v>1730</v>
+        <v>1539</v>
       </c>
       <c r="F338" s="2">
-        <v>45835</v>
+        <v>45994</v>
       </c>
       <c r="G338" t="s">
         <v>1914</v>
       </c>
       <c r="H338" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I338" t="s">
-        <v>1985</v>
+        <v>2059</v>
       </c>
       <c r="J338" t="s">
         <v>2141</v>
@@ -24925,22 +24935,22 @@
         <v>1097</v>
       </c>
       <c r="C339" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="F339" s="2">
-        <v>46126</v>
+        <v>45835</v>
       </c>
       <c r="G339" t="s">
         <v>1914</v>
       </c>
       <c r="H339" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I339" t="s">
-        <v>2027</v>
+        <v>1985</v>
       </c>
       <c r="J339" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K339" t="s">
         <v>2476</v>
@@ -24957,10 +24967,10 @@
         <v>1098</v>
       </c>
       <c r="C340" t="s">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="F340" s="2">
-        <v>46198</v>
+        <v>46126</v>
       </c>
       <c r="G340" t="s">
         <v>1914</v>
@@ -24969,7 +24979,7 @@
         <v>1922</v>
       </c>
       <c r="I340" t="s">
-        <v>2000</v>
+        <v>2027</v>
       </c>
       <c r="J340" t="s">
         <v>2140</v>
@@ -24989,22 +24999,19 @@
         <v>1099</v>
       </c>
       <c r="C341" t="s">
-        <v>1732</v>
-      </c>
-      <c r="D341" t="s">
-        <v>1873</v>
+        <v>1731</v>
       </c>
       <c r="F341" s="2">
-        <v>45698</v>
+        <v>46198</v>
       </c>
       <c r="G341" t="s">
         <v>1914</v>
       </c>
       <c r="H341" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="I341" t="s">
-        <v>2089</v>
+        <v>2000</v>
       </c>
       <c r="J341" t="s">
         <v>2140</v>
@@ -25024,28 +25031,25 @@
         <v>1100</v>
       </c>
       <c r="C342" t="s">
-        <v>1645</v>
+        <v>1732</v>
       </c>
       <c r="D342" t="s">
-        <v>1712</v>
-      </c>
-      <c r="E342" t="s">
-        <v>1712</v>
+        <v>1873</v>
       </c>
       <c r="F342" s="2">
-        <v>46048</v>
+        <v>45698</v>
       </c>
       <c r="G342" t="s">
         <v>1914</v>
       </c>
       <c r="H342" t="s">
-        <v>1941</v>
+        <v>1919</v>
       </c>
       <c r="I342" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
       <c r="J342" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K342" t="s">
         <v>2479</v>
@@ -25062,22 +25066,28 @@
         <v>1101</v>
       </c>
       <c r="C343" t="s">
-        <v>1514</v>
+        <v>1645</v>
+      </c>
+      <c r="D343" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1712</v>
       </c>
       <c r="F343" s="2">
-        <v>46091</v>
+        <v>46048</v>
       </c>
       <c r="G343" t="s">
         <v>1914</v>
       </c>
       <c r="H343" t="s">
-        <v>1922</v>
+        <v>1941</v>
       </c>
       <c r="I343" t="s">
-        <v>2008</v>
+        <v>2095</v>
       </c>
       <c r="J343" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K343" t="s">
         <v>2480</v>
@@ -25094,10 +25104,10 @@
         <v>1102</v>
       </c>
       <c r="C344" t="s">
-        <v>1693</v>
+        <v>1514</v>
       </c>
       <c r="F344" s="2">
-        <v>46183</v>
+        <v>46091</v>
       </c>
       <c r="G344" t="s">
         <v>1914</v>
@@ -25106,10 +25116,10 @@
         <v>1922</v>
       </c>
       <c r="I344" t="s">
-        <v>2032</v>
+        <v>2008</v>
       </c>
       <c r="J344" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K344" t="s">
         <v>2481</v>
@@ -25126,22 +25136,22 @@
         <v>1103</v>
       </c>
       <c r="C345" t="s">
-        <v>1517</v>
+        <v>1693</v>
       </c>
       <c r="F345" s="2">
-        <v>45775</v>
+        <v>46183</v>
       </c>
       <c r="G345" t="s">
         <v>1914</v>
       </c>
       <c r="H345" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I345" t="s">
-        <v>1981</v>
+        <v>2032</v>
       </c>
       <c r="J345" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K345" t="s">
         <v>2482</v>
@@ -25158,19 +25168,19 @@
         <v>1104</v>
       </c>
       <c r="C346" t="s">
-        <v>1572</v>
+        <v>1517</v>
       </c>
       <c r="F346" s="2">
-        <v>45728</v>
+        <v>45775</v>
       </c>
       <c r="G346" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H346" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I346" t="s">
-        <v>2096</v>
+        <v>1981</v>
       </c>
       <c r="J346" t="s">
         <v>2140</v>
@@ -25190,19 +25200,19 @@
         <v>1105</v>
       </c>
       <c r="C347" t="s">
-        <v>1733</v>
+        <v>1572</v>
       </c>
       <c r="F347" s="2">
-        <v>46055</v>
+        <v>45728</v>
       </c>
       <c r="G347" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H347" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I347" t="s">
-        <v>2060</v>
+        <v>2096</v>
       </c>
       <c r="J347" t="s">
         <v>2140</v>
@@ -25222,25 +25232,19 @@
         <v>1106</v>
       </c>
       <c r="C348" t="s">
-        <v>1734</v>
-      </c>
-      <c r="D348" t="s">
-        <v>1874</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1822</v>
+        <v>1733</v>
       </c>
       <c r="F348" s="2">
-        <v>45952</v>
+        <v>46055</v>
       </c>
       <c r="G348" t="s">
         <v>1914</v>
       </c>
       <c r="H348" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="I348" t="s">
-        <v>2025</v>
+        <v>2060</v>
       </c>
       <c r="J348" t="s">
         <v>2140</v>
@@ -25260,25 +25264,25 @@
         <v>1107</v>
       </c>
       <c r="C349" t="s">
-        <v>1602</v>
+        <v>1734</v>
       </c>
       <c r="D349" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="E349" t="s">
-        <v>1776</v>
+        <v>1822</v>
       </c>
       <c r="F349" s="2">
-        <v>45818</v>
+        <v>45952</v>
       </c>
       <c r="G349" t="s">
         <v>1914</v>
       </c>
       <c r="H349" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
       <c r="I349" t="s">
-        <v>2097</v>
+        <v>2025</v>
       </c>
       <c r="J349" t="s">
         <v>2140</v>
@@ -25298,10 +25302,16 @@
         <v>1108</v>
       </c>
       <c r="C350" t="s">
-        <v>1735</v>
+        <v>1602</v>
+      </c>
+      <c r="D350" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1776</v>
       </c>
       <c r="F350" s="2">
-        <v>45994</v>
+        <v>45818</v>
       </c>
       <c r="G350" t="s">
         <v>1914</v>
@@ -25310,10 +25320,10 @@
         <v>1921</v>
       </c>
       <c r="I350" t="s">
-        <v>2000</v>
+        <v>2097</v>
       </c>
       <c r="J350" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K350" t="s">
         <v>2487</v>
@@ -25330,22 +25340,22 @@
         <v>1109</v>
       </c>
       <c r="C351" t="s">
-        <v>1715</v>
+        <v>1735</v>
       </c>
       <c r="F351" s="2">
-        <v>46217</v>
+        <v>45994</v>
       </c>
       <c r="G351" t="s">
         <v>1914</v>
       </c>
       <c r="H351" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I351" t="s">
-        <v>2070</v>
+        <v>2000</v>
       </c>
       <c r="J351" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K351" t="s">
         <v>2488</v>
@@ -25362,28 +25372,22 @@
         <v>1110</v>
       </c>
       <c r="C352" t="s">
-        <v>1736</v>
-      </c>
-      <c r="D352" t="s">
-        <v>1876</v>
-      </c>
-      <c r="E352" t="s">
-        <v>1876</v>
+        <v>1715</v>
       </c>
       <c r="F352" s="2">
-        <v>45922</v>
+        <v>46217</v>
       </c>
       <c r="G352" t="s">
         <v>1914</v>
       </c>
       <c r="H352" t="s">
-        <v>1946</v>
+        <v>1922</v>
       </c>
       <c r="I352" t="s">
-        <v>2024</v>
+        <v>2070</v>
       </c>
       <c r="J352" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K352" t="s">
         <v>2489</v>
@@ -25400,19 +25404,25 @@
         <v>1111</v>
       </c>
       <c r="C353" t="s">
-        <v>1737</v>
+        <v>1736</v>
+      </c>
+      <c r="D353" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1876</v>
       </c>
       <c r="F353" s="2">
-        <v>46113</v>
+        <v>45922</v>
       </c>
       <c r="G353" t="s">
         <v>1914</v>
       </c>
       <c r="H353" t="s">
-        <v>1922</v>
+        <v>1946</v>
       </c>
       <c r="I353" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="J353" t="s">
         <v>2141</v>
@@ -25432,7 +25442,7 @@
         <v>1112</v>
       </c>
       <c r="C354" t="s">
-        <v>1635</v>
+        <v>1737</v>
       </c>
       <c r="F354" s="2">
         <v>46113</v>
@@ -25441,13 +25451,13 @@
         <v>1914</v>
       </c>
       <c r="H354" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I354" t="s">
-        <v>2011</v>
+        <v>2027</v>
       </c>
       <c r="J354" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K354" t="s">
         <v>2491</v>
@@ -25464,10 +25474,10 @@
         <v>1113</v>
       </c>
       <c r="C355" t="s">
-        <v>1738</v>
+        <v>1635</v>
       </c>
       <c r="F355" s="2">
-        <v>46218</v>
+        <v>46113</v>
       </c>
       <c r="G355" t="s">
         <v>1914</v>
@@ -25476,7 +25486,7 @@
         <v>1921</v>
       </c>
       <c r="I355" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="J355" t="s">
         <v>2140</v>
@@ -25496,19 +25506,19 @@
         <v>1114</v>
       </c>
       <c r="C356" t="s">
-        <v>1633</v>
+        <v>1738</v>
       </c>
       <c r="F356" s="2">
-        <v>45799</v>
+        <v>46218</v>
       </c>
       <c r="G356" t="s">
         <v>1914</v>
       </c>
       <c r="H356" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="I356" t="s">
-        <v>2032</v>
+        <v>2009</v>
       </c>
       <c r="J356" t="s">
         <v>2140</v>
@@ -25528,19 +25538,19 @@
         <v>1115</v>
       </c>
       <c r="C357" t="s">
-        <v>1739</v>
+        <v>1633</v>
       </c>
       <c r="F357" s="2">
-        <v>45994</v>
+        <v>45799</v>
       </c>
       <c r="G357" t="s">
         <v>1914</v>
       </c>
       <c r="H357" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I357" t="s">
-        <v>1986</v>
+        <v>2032</v>
       </c>
       <c r="J357" t="s">
         <v>2140</v>
@@ -25560,22 +25570,22 @@
         <v>1116</v>
       </c>
       <c r="C358" t="s">
-        <v>1513</v>
+        <v>1739</v>
       </c>
       <c r="F358" s="2">
-        <v>46205</v>
+        <v>45994</v>
       </c>
       <c r="G358" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H358" t="s">
-        <v>1938</v>
+        <v>1922</v>
       </c>
       <c r="I358" t="s">
-        <v>2018</v>
+        <v>1986</v>
       </c>
       <c r="J358" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K358" t="s">
         <v>2495</v>
@@ -25592,22 +25602,19 @@
         <v>1117</v>
       </c>
       <c r="C359" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D359" t="s">
-        <v>1877</v>
+        <v>1513</v>
       </c>
       <c r="F359" s="2">
-        <v>45733</v>
+        <v>46205</v>
       </c>
       <c r="G359" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H359" t="s">
-        <v>1924</v>
+        <v>1938</v>
       </c>
       <c r="I359" t="s">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="J359" t="s">
         <v>2141</v>
@@ -25627,22 +25634,25 @@
         <v>1118</v>
       </c>
       <c r="C360" t="s">
-        <v>1740</v>
+        <v>1560</v>
+      </c>
+      <c r="D360" t="s">
+        <v>1877</v>
       </c>
       <c r="F360" s="2">
-        <v>45965</v>
+        <v>45733</v>
       </c>
       <c r="G360" t="s">
         <v>1914</v>
       </c>
       <c r="H360" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I360" t="s">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="J360" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K360" t="s">
         <v>2497</v>
@@ -25659,19 +25669,19 @@
         <v>1119</v>
       </c>
       <c r="C361" t="s">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="F361" s="2">
-        <v>45853</v>
+        <v>45965</v>
       </c>
       <c r="G361" t="s">
         <v>1914</v>
       </c>
       <c r="H361" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I361" t="s">
-        <v>2074</v>
+        <v>2007</v>
       </c>
       <c r="J361" t="s">
         <v>2140</v>
@@ -25691,19 +25701,19 @@
         <v>1120</v>
       </c>
       <c r="C362" t="s">
-        <v>1550</v>
+        <v>1730</v>
       </c>
       <c r="F362" s="2">
-        <v>45840</v>
+        <v>45853</v>
       </c>
       <c r="G362" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H362" t="s">
         <v>1924</v>
       </c>
       <c r="I362" t="s">
-        <v>2098</v>
+        <v>2074</v>
       </c>
       <c r="J362" t="s">
         <v>2140</v>
@@ -25723,19 +25733,19 @@
         <v>1121</v>
       </c>
       <c r="C363" t="s">
-        <v>1531</v>
+        <v>1550</v>
       </c>
       <c r="F363" s="2">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="G363" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H363" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I363" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="J363" t="s">
         <v>2140</v>
@@ -25755,19 +25765,19 @@
         <v>1122</v>
       </c>
       <c r="C364" t="s">
-        <v>1613</v>
+        <v>1531</v>
       </c>
       <c r="F364" s="2">
-        <v>45992</v>
+        <v>45838</v>
       </c>
       <c r="G364" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H364" t="s">
         <v>1921</v>
       </c>
       <c r="I364" t="s">
-        <v>2055</v>
+        <v>2099</v>
       </c>
       <c r="J364" t="s">
         <v>2140</v>
@@ -25787,19 +25797,19 @@
         <v>1123</v>
       </c>
       <c r="C365" t="s">
-        <v>1741</v>
+        <v>1613</v>
       </c>
       <c r="F365" s="2">
-        <v>46118</v>
+        <v>45992</v>
       </c>
       <c r="G365" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H365" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I365" t="s">
-        <v>2018</v>
+        <v>2055</v>
       </c>
       <c r="J365" t="s">
         <v>2140</v>
@@ -25819,19 +25829,19 @@
         <v>1124</v>
       </c>
       <c r="C366" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="F366" s="2">
-        <v>46168</v>
+        <v>46118</v>
       </c>
       <c r="G366" t="s">
         <v>1914</v>
       </c>
       <c r="H366" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I366" t="s">
-        <v>1974</v>
+        <v>2018</v>
       </c>
       <c r="J366" t="s">
         <v>2140</v>
@@ -25851,22 +25861,22 @@
         <v>1125</v>
       </c>
       <c r="C367" t="s">
-        <v>1737</v>
+        <v>1742</v>
       </c>
       <c r="F367" s="2">
-        <v>46118</v>
+        <v>46168</v>
       </c>
       <c r="G367" t="s">
         <v>1914</v>
       </c>
       <c r="H367" t="s">
-        <v>1950</v>
+        <v>1921</v>
       </c>
       <c r="I367" t="s">
-        <v>2060</v>
+        <v>1974</v>
       </c>
       <c r="J367" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K367" t="s">
         <v>2504</v>
@@ -25883,22 +25893,22 @@
         <v>1126</v>
       </c>
       <c r="C368" t="s">
-        <v>1743</v>
+        <v>1737</v>
       </c>
       <c r="F368" s="2">
-        <v>45754</v>
+        <v>46118</v>
       </c>
       <c r="G368" t="s">
         <v>1914</v>
       </c>
       <c r="H368" t="s">
-        <v>1922</v>
+        <v>1950</v>
       </c>
       <c r="I368" t="s">
-        <v>1980</v>
+        <v>2060</v>
       </c>
       <c r="J368" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K368" t="s">
         <v>2505</v>
@@ -25915,19 +25925,19 @@
         <v>1127</v>
       </c>
       <c r="C369" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="F369" s="2">
-        <v>46050</v>
+        <v>45754</v>
       </c>
       <c r="G369" t="s">
         <v>1914</v>
       </c>
       <c r="H369" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="I369" t="s">
-        <v>2100</v>
+        <v>1980</v>
       </c>
       <c r="J369" t="s">
         <v>2140</v>
@@ -25947,25 +25957,19 @@
         <v>1128</v>
       </c>
       <c r="C370" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D370" t="s">
-        <v>1717</v>
-      </c>
-      <c r="E370" t="s">
-        <v>1657</v>
+        <v>1744</v>
       </c>
       <c r="F370" s="2">
-        <v>46113</v>
+        <v>46050</v>
       </c>
       <c r="G370" t="s">
         <v>1914</v>
       </c>
       <c r="H370" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
       <c r="I370" t="s">
-        <v>2011</v>
+        <v>2100</v>
       </c>
       <c r="J370" t="s">
         <v>2140</v>
@@ -25985,22 +25989,28 @@
         <v>1129</v>
       </c>
       <c r="C371" t="s">
-        <v>1526</v>
+        <v>1636</v>
+      </c>
+      <c r="D371" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E371" t="s">
+        <v>1657</v>
       </c>
       <c r="F371" s="2">
-        <v>45761</v>
+        <v>46113</v>
       </c>
       <c r="G371" t="s">
         <v>1914</v>
       </c>
       <c r="H371" t="s">
-        <v>1941</v>
+        <v>1921</v>
       </c>
       <c r="I371" t="s">
-        <v>1990</v>
+        <v>2011</v>
       </c>
       <c r="J371" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K371" t="s">
         <v>2508</v>
@@ -26017,22 +26027,22 @@
         <v>1130</v>
       </c>
       <c r="C372" t="s">
-        <v>1745</v>
+        <v>1526</v>
       </c>
       <c r="F372" s="2">
-        <v>45883</v>
+        <v>45761</v>
       </c>
       <c r="G372" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H372" t="s">
-        <v>1936</v>
+        <v>1941</v>
       </c>
       <c r="I372" t="s">
-        <v>2062</v>
+        <v>1990</v>
       </c>
       <c r="J372" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K372" t="s">
         <v>2509</v>
@@ -26049,25 +26059,19 @@
         <v>1131</v>
       </c>
       <c r="C373" t="s">
-        <v>1558</v>
-      </c>
-      <c r="D373" t="s">
-        <v>1789</v>
-      </c>
-      <c r="E373" t="s">
-        <v>1907</v>
+        <v>1745</v>
       </c>
       <c r="F373" s="2">
-        <v>46211</v>
+        <v>45883</v>
       </c>
       <c r="G373" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H373" t="s">
-        <v>1923</v>
+        <v>1936</v>
       </c>
       <c r="I373" t="s">
-        <v>2018</v>
+        <v>2062</v>
       </c>
       <c r="J373" t="s">
         <v>2140</v>
@@ -26087,16 +26091,16 @@
         <v>1132</v>
       </c>
       <c r="C374" t="s">
-        <v>1746</v>
+        <v>1558</v>
       </c>
       <c r="D374" t="s">
-        <v>1665</v>
+        <v>1789</v>
       </c>
       <c r="E374" t="s">
-        <v>1899</v>
+        <v>1907</v>
       </c>
       <c r="F374" s="2">
-        <v>45705</v>
+        <v>46211</v>
       </c>
       <c r="G374" t="s">
         <v>1914</v>
@@ -26105,7 +26109,7 @@
         <v>1923</v>
       </c>
       <c r="I374" t="s">
-        <v>1978</v>
+        <v>2018</v>
       </c>
       <c r="J374" t="s">
         <v>2140</v>
@@ -26125,25 +26129,25 @@
         <v>1133</v>
       </c>
       <c r="C375" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="D375" t="s">
-        <v>1675</v>
+        <v>1665</v>
       </c>
       <c r="E375" t="s">
-        <v>1850</v>
+        <v>1899</v>
       </c>
       <c r="F375" s="2">
-        <v>46170</v>
+        <v>45705</v>
       </c>
       <c r="G375" t="s">
         <v>1914</v>
       </c>
       <c r="H375" t="s">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="I375" t="s">
-        <v>2101</v>
+        <v>1978</v>
       </c>
       <c r="J375" t="s">
         <v>2140</v>
@@ -26163,19 +26167,25 @@
         <v>1134</v>
       </c>
       <c r="C376" t="s">
-        <v>1748</v>
+        <v>1747</v>
+      </c>
+      <c r="D376" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E376" t="s">
+        <v>1850</v>
       </c>
       <c r="F376" s="2">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="G376" t="s">
         <v>1914</v>
       </c>
       <c r="H376" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="I376" t="s">
-        <v>2021</v>
+        <v>2101</v>
       </c>
       <c r="J376" t="s">
         <v>2140</v>
@@ -26195,25 +26205,19 @@
         <v>1135</v>
       </c>
       <c r="C377" t="s">
-        <v>1582</v>
-      </c>
-      <c r="D377" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E377" t="s">
-        <v>1604</v>
+        <v>1748</v>
       </c>
       <c r="F377" s="2">
-        <v>45937</v>
+        <v>46168</v>
       </c>
       <c r="G377" t="s">
         <v>1914</v>
       </c>
       <c r="H377" t="s">
-        <v>1927</v>
+        <v>1934</v>
       </c>
       <c r="I377" t="s">
-        <v>1990</v>
+        <v>2021</v>
       </c>
       <c r="J377" t="s">
         <v>2140</v>
@@ -26233,19 +26237,25 @@
         <v>1136</v>
       </c>
       <c r="C378" t="s">
-        <v>1605</v>
+        <v>1582</v>
+      </c>
+      <c r="D378" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E378" t="s">
+        <v>1604</v>
       </c>
       <c r="F378" s="2">
-        <v>46191</v>
+        <v>45937</v>
       </c>
       <c r="G378" t="s">
         <v>1914</v>
       </c>
       <c r="H378" t="s">
-        <v>1922</v>
+        <v>1927</v>
       </c>
       <c r="I378" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="J378" t="s">
         <v>2140</v>
@@ -26265,19 +26275,19 @@
         <v>1137</v>
       </c>
       <c r="C379" t="s">
-        <v>1749</v>
+        <v>1605</v>
       </c>
       <c r="F379" s="2">
-        <v>45887</v>
+        <v>46191</v>
       </c>
       <c r="G379" t="s">
         <v>1914</v>
       </c>
       <c r="H379" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I379" t="s">
-        <v>2102</v>
+        <v>1995</v>
       </c>
       <c r="J379" t="s">
         <v>2140</v>
@@ -26297,25 +26307,19 @@
         <v>1138</v>
       </c>
       <c r="C380" t="s">
-        <v>1750</v>
-      </c>
-      <c r="D380" t="s">
-        <v>1878</v>
-      </c>
-      <c r="E380" t="s">
-        <v>1878</v>
+        <v>1749</v>
       </c>
       <c r="F380" s="2">
-        <v>45734</v>
+        <v>45887</v>
       </c>
       <c r="G380" t="s">
         <v>1914</v>
       </c>
       <c r="H380" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="I380" t="s">
-        <v>2057</v>
+        <v>2102</v>
       </c>
       <c r="J380" t="s">
         <v>2140</v>
@@ -26335,25 +26339,25 @@
         <v>1139</v>
       </c>
       <c r="C381" t="s">
-        <v>1654</v>
+        <v>1750</v>
       </c>
       <c r="D381" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="E381" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="F381" s="2">
-        <v>46188</v>
+        <v>45734</v>
       </c>
       <c r="G381" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H381" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="I381" t="s">
-        <v>2041</v>
+        <v>2057</v>
       </c>
       <c r="J381" t="s">
         <v>2140</v>
@@ -26373,22 +26377,25 @@
         <v>1140</v>
       </c>
       <c r="C382" t="s">
-        <v>1597</v>
+        <v>1654</v>
       </c>
       <c r="D382" t="s">
-        <v>1530</v>
+        <v>1879</v>
+      </c>
+      <c r="E382" t="s">
+        <v>1879</v>
       </c>
       <c r="F382" s="2">
-        <v>46211</v>
+        <v>46188</v>
       </c>
       <c r="G382" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H382" t="s">
-        <v>1930</v>
+        <v>1922</v>
       </c>
       <c r="I382" t="s">
-        <v>2103</v>
+        <v>2041</v>
       </c>
       <c r="J382" t="s">
         <v>2140</v>
@@ -26408,19 +26415,22 @@
         <v>1141</v>
       </c>
       <c r="C383" t="s">
-        <v>1549</v>
+        <v>1597</v>
+      </c>
+      <c r="D383" t="s">
+        <v>1530</v>
       </c>
       <c r="F383" s="2">
-        <v>45938</v>
+        <v>46211</v>
       </c>
       <c r="G383" t="s">
         <v>1914</v>
       </c>
       <c r="H383" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="I383" t="s">
-        <v>2021</v>
+        <v>2103</v>
       </c>
       <c r="J383" t="s">
         <v>2140</v>
@@ -26440,19 +26450,19 @@
         <v>1142</v>
       </c>
       <c r="C384" t="s">
-        <v>1751</v>
+        <v>1549</v>
       </c>
       <c r="F384" s="2">
-        <v>46129</v>
+        <v>45938</v>
       </c>
       <c r="G384" t="s">
         <v>1914</v>
       </c>
       <c r="H384" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="I384" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="J384" t="s">
         <v>2140</v>
@@ -26472,19 +26482,19 @@
         <v>1143</v>
       </c>
       <c r="C385" t="s">
-        <v>1603</v>
+        <v>1751</v>
       </c>
       <c r="F385" s="2">
-        <v>46043</v>
+        <v>46129</v>
       </c>
       <c r="G385" t="s">
         <v>1914</v>
       </c>
       <c r="H385" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
       <c r="I385" t="s">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="J385" t="s">
         <v>2140</v>
@@ -26504,19 +26514,19 @@
         <v>1144</v>
       </c>
       <c r="C386" t="s">
-        <v>1752</v>
+        <v>1603</v>
       </c>
       <c r="F386" s="2">
-        <v>46161</v>
+        <v>46043</v>
       </c>
       <c r="G386" t="s">
         <v>1914</v>
       </c>
       <c r="H386" t="s">
-        <v>1949</v>
+        <v>1921</v>
       </c>
       <c r="I386" t="s">
-        <v>2059</v>
+        <v>2011</v>
       </c>
       <c r="J386" t="s">
         <v>2140</v>
@@ -26536,19 +26546,19 @@
         <v>1145</v>
       </c>
       <c r="C387" t="s">
-        <v>1713</v>
+        <v>1752</v>
       </c>
       <c r="F387" s="2">
-        <v>46050</v>
+        <v>46161</v>
       </c>
       <c r="G387" t="s">
         <v>1914</v>
       </c>
       <c r="H387" t="s">
-        <v>1924</v>
+        <v>1949</v>
       </c>
       <c r="I387" t="s">
-        <v>2075</v>
+        <v>2059</v>
       </c>
       <c r="J387" t="s">
         <v>2140</v>
@@ -26568,19 +26578,19 @@
         <v>1146</v>
       </c>
       <c r="C388" t="s">
-        <v>1753</v>
+        <v>1713</v>
       </c>
       <c r="F388" s="2">
-        <v>45799</v>
+        <v>46050</v>
       </c>
       <c r="G388" t="s">
         <v>1914</v>
       </c>
       <c r="H388" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I388" t="s">
-        <v>1978</v>
+        <v>2075</v>
       </c>
       <c r="J388" t="s">
         <v>2140</v>
@@ -26600,19 +26610,19 @@
         <v>1147</v>
       </c>
       <c r="C389" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="F389" s="2">
-        <v>46185</v>
+        <v>45799</v>
       </c>
       <c r="G389" t="s">
         <v>1914</v>
       </c>
       <c r="H389" t="s">
-        <v>1956</v>
+        <v>1922</v>
       </c>
       <c r="I389" t="s">
-        <v>2027</v>
+        <v>1978</v>
       </c>
       <c r="J389" t="s">
         <v>2140</v>
@@ -26632,19 +26642,19 @@
         <v>1148</v>
       </c>
       <c r="C390" t="s">
-        <v>1585</v>
+        <v>1754</v>
       </c>
       <c r="F390" s="2">
-        <v>45693</v>
+        <v>46185</v>
       </c>
       <c r="G390" t="s">
         <v>1914</v>
       </c>
       <c r="H390" t="s">
-        <v>1922</v>
+        <v>1956</v>
       </c>
       <c r="I390" t="s">
-        <v>2070</v>
+        <v>2027</v>
       </c>
       <c r="J390" t="s">
         <v>2140</v>
@@ -26664,19 +26674,19 @@
         <v>1149</v>
       </c>
       <c r="C391" t="s">
-        <v>1700</v>
+        <v>1585</v>
       </c>
       <c r="F391" s="2">
-        <v>46044</v>
+        <v>45693</v>
       </c>
       <c r="G391" t="s">
         <v>1914</v>
       </c>
       <c r="H391" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I391" t="s">
-        <v>1976</v>
+        <v>2070</v>
       </c>
       <c r="J391" t="s">
         <v>2140</v>
@@ -26696,22 +26706,22 @@
         <v>1150</v>
       </c>
       <c r="C392" t="s">
-        <v>1603</v>
+        <v>1700</v>
       </c>
       <c r="F392" s="2">
-        <v>45835</v>
+        <v>46044</v>
       </c>
       <c r="G392" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H392" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I392" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="J392" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K392" t="s">
         <v>2529</v>
@@ -26728,25 +26738,19 @@
         <v>1151</v>
       </c>
       <c r="C393" t="s">
-        <v>1755</v>
-      </c>
-      <c r="D393" t="s">
-        <v>1788</v>
-      </c>
-      <c r="E393" t="s">
-        <v>1788</v>
+        <v>1603</v>
       </c>
       <c r="F393" s="2">
-        <v>45972</v>
+        <v>45835</v>
       </c>
       <c r="G393" t="s">
         <v>1915</v>
       </c>
       <c r="H393" t="s">
-        <v>1959</v>
+        <v>1922</v>
       </c>
       <c r="I393" t="s">
-        <v>1987</v>
+        <v>1978</v>
       </c>
       <c r="J393" t="s">
         <v>2141</v>
@@ -26766,28 +26770,28 @@
         <v>1152</v>
       </c>
       <c r="C394" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="D394" t="s">
-        <v>1880</v>
+        <v>1788</v>
       </c>
       <c r="E394" t="s">
-        <v>1880</v>
+        <v>1788</v>
       </c>
       <c r="F394" s="2">
-        <v>45777</v>
+        <v>45972</v>
       </c>
       <c r="G394" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H394" t="s">
-        <v>1922</v>
+        <v>1959</v>
       </c>
       <c r="I394" t="s">
-        <v>1994</v>
+        <v>1987</v>
       </c>
       <c r="J394" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K394" t="s">
         <v>2531</v>
@@ -26804,22 +26808,28 @@
         <v>1153</v>
       </c>
       <c r="C395" t="s">
-        <v>1757</v>
+        <v>1756</v>
+      </c>
+      <c r="D395" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E395" t="s">
+        <v>1880</v>
       </c>
       <c r="F395" s="2">
-        <v>45680</v>
+        <v>45777</v>
       </c>
       <c r="G395" t="s">
         <v>1914</v>
       </c>
       <c r="H395" t="s">
-        <v>1960</v>
+        <v>1922</v>
       </c>
       <c r="I395" t="s">
-        <v>2029</v>
+        <v>1994</v>
       </c>
       <c r="J395" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K395" t="s">
         <v>2532</v>
@@ -26836,28 +26846,22 @@
         <v>1154</v>
       </c>
       <c r="C396" t="s">
-        <v>1753</v>
-      </c>
-      <c r="D396" t="s">
-        <v>1551</v>
-      </c>
-      <c r="E396" t="s">
-        <v>1692</v>
+        <v>1757</v>
       </c>
       <c r="F396" s="2">
-        <v>45791</v>
+        <v>45680</v>
       </c>
       <c r="G396" t="s">
         <v>1914</v>
       </c>
       <c r="H396" t="s">
-        <v>1922</v>
+        <v>1960</v>
       </c>
       <c r="I396" t="s">
-        <v>2080</v>
+        <v>2029</v>
       </c>
       <c r="J396" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K396" t="s">
         <v>2533</v>
@@ -26874,10 +26878,16 @@
         <v>1155</v>
       </c>
       <c r="C397" t="s">
-        <v>1643</v>
+        <v>1753</v>
+      </c>
+      <c r="D397" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E397" t="s">
+        <v>1692</v>
       </c>
       <c r="F397" s="2">
-        <v>45993</v>
+        <v>45791</v>
       </c>
       <c r="G397" t="s">
         <v>1914</v>
@@ -26886,7 +26896,7 @@
         <v>1922</v>
       </c>
       <c r="I397" t="s">
-        <v>2009</v>
+        <v>2080</v>
       </c>
       <c r="J397" t="s">
         <v>2140</v>
@@ -26906,19 +26916,19 @@
         <v>1156</v>
       </c>
       <c r="C398" t="s">
-        <v>1758</v>
+        <v>1643</v>
       </c>
       <c r="F398" s="2">
-        <v>46149</v>
+        <v>45993</v>
       </c>
       <c r="G398" t="s">
         <v>1914</v>
       </c>
       <c r="H398" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I398" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="J398" t="s">
         <v>2140</v>
@@ -26938,10 +26948,10 @@
         <v>1157</v>
       </c>
       <c r="C399" t="s">
-        <v>1743</v>
+        <v>1758</v>
       </c>
       <c r="F399" s="2">
-        <v>45818</v>
+        <v>46149</v>
       </c>
       <c r="G399" t="s">
         <v>1914</v>
@@ -26950,7 +26960,7 @@
         <v>1921</v>
       </c>
       <c r="I399" t="s">
-        <v>1977</v>
+        <v>2011</v>
       </c>
       <c r="J399" t="s">
         <v>2140</v>
@@ -26970,19 +26980,19 @@
         <v>1158</v>
       </c>
       <c r="C400" t="s">
-        <v>1554</v>
+        <v>1743</v>
       </c>
       <c r="F400" s="2">
-        <v>46118</v>
+        <v>45818</v>
       </c>
       <c r="G400" t="s">
         <v>1914</v>
       </c>
       <c r="H400" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I400" t="s">
-        <v>2017</v>
+        <v>1977</v>
       </c>
       <c r="J400" t="s">
         <v>2140</v>
@@ -27002,19 +27012,19 @@
         <v>1159</v>
       </c>
       <c r="C401" t="s">
-        <v>1759</v>
+        <v>1554</v>
       </c>
       <c r="F401" s="2">
-        <v>46225</v>
+        <v>46118</v>
       </c>
       <c r="G401" t="s">
         <v>1914</v>
       </c>
       <c r="H401" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I401" t="s">
-        <v>1974</v>
+        <v>2017</v>
       </c>
       <c r="J401" t="s">
         <v>2140</v>
@@ -27034,22 +27044,16 @@
         <v>1160</v>
       </c>
       <c r="C402" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D402" t="s">
         <v>1759</v>
       </c>
-      <c r="E402" t="s">
-        <v>1828</v>
-      </c>
       <c r="F402" s="2">
-        <v>46112</v>
+        <v>46225</v>
       </c>
       <c r="G402" t="s">
         <v>1914</v>
       </c>
       <c r="H402" t="s">
-        <v>1930</v>
+        <v>1922</v>
       </c>
       <c r="I402" t="s">
         <v>1974</v>
@@ -27072,19 +27076,25 @@
         <v>1161</v>
       </c>
       <c r="C403" t="s">
-        <v>1602</v>
+        <v>1760</v>
+      </c>
+      <c r="D403" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E403" t="s">
+        <v>1828</v>
       </c>
       <c r="F403" s="2">
-        <v>45789</v>
+        <v>46112</v>
       </c>
       <c r="G403" t="s">
         <v>1914</v>
       </c>
       <c r="H403" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="I403" t="s">
-        <v>2010</v>
+        <v>1974</v>
       </c>
       <c r="J403" t="s">
         <v>2140</v>
@@ -27104,22 +27114,22 @@
         <v>1162</v>
       </c>
       <c r="C404" t="s">
-        <v>1691</v>
+        <v>1602</v>
       </c>
       <c r="F404" s="2">
-        <v>45692</v>
+        <v>45789</v>
       </c>
       <c r="G404" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H404" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I404" t="s">
-        <v>1995</v>
+        <v>2010</v>
       </c>
       <c r="J404" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K404" t="s">
         <v>2541</v>
@@ -27136,25 +27146,22 @@
         <v>1163</v>
       </c>
       <c r="C405" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D405" t="s">
-        <v>1509</v>
+        <v>1691</v>
       </c>
       <c r="F405" s="2">
-        <v>46205</v>
+        <v>45692</v>
       </c>
       <c r="G405" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H405" t="s">
-        <v>1931</v>
+        <v>1924</v>
       </c>
       <c r="I405" t="s">
-        <v>1974</v>
+        <v>1995</v>
       </c>
       <c r="J405" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K405" t="s">
         <v>2542</v>
@@ -27171,19 +27178,22 @@
         <v>1164</v>
       </c>
       <c r="C406" t="s">
-        <v>1586</v>
+        <v>1761</v>
+      </c>
+      <c r="D406" t="s">
+        <v>1509</v>
       </c>
       <c r="F406" s="2">
-        <v>45888</v>
+        <v>46205</v>
       </c>
       <c r="G406" t="s">
         <v>1914</v>
       </c>
       <c r="H406" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="I406" t="s">
-        <v>2009</v>
+        <v>1974</v>
       </c>
       <c r="J406" t="s">
         <v>2140</v>
@@ -27203,19 +27213,19 @@
         <v>1165</v>
       </c>
       <c r="C407" t="s">
-        <v>1762</v>
+        <v>1586</v>
       </c>
       <c r="F407" s="2">
-        <v>46010</v>
+        <v>45888</v>
       </c>
       <c r="G407" t="s">
         <v>1914</v>
       </c>
       <c r="H407" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I407" t="s">
-        <v>1995</v>
+        <v>2009</v>
       </c>
       <c r="J407" t="s">
         <v>2140</v>
@@ -27235,19 +27245,19 @@
         <v>1166</v>
       </c>
       <c r="C408" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="F408" s="2">
-        <v>46149</v>
+        <v>46010</v>
       </c>
       <c r="G408" t="s">
         <v>1914</v>
       </c>
       <c r="H408" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I408" t="s">
-        <v>2011</v>
+        <v>1995</v>
       </c>
       <c r="J408" t="s">
         <v>2140</v>
@@ -27267,10 +27277,10 @@
         <v>1167</v>
       </c>
       <c r="C409" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="F409" s="2">
-        <v>45812</v>
+        <v>46149</v>
       </c>
       <c r="G409" t="s">
         <v>1914</v>
@@ -27279,7 +27289,7 @@
         <v>1921</v>
       </c>
       <c r="I409" t="s">
-        <v>1986</v>
+        <v>2011</v>
       </c>
       <c r="J409" t="s">
         <v>2140</v>
@@ -27299,19 +27309,19 @@
         <v>1168</v>
       </c>
       <c r="C410" t="s">
-        <v>1566</v>
+        <v>1763</v>
       </c>
       <c r="F410" s="2">
-        <v>45994</v>
+        <v>45812</v>
       </c>
       <c r="G410" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H410" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I410" t="s">
-        <v>1992</v>
+        <v>1986</v>
       </c>
       <c r="J410" t="s">
         <v>2140</v>
@@ -27331,19 +27341,19 @@
         <v>1169</v>
       </c>
       <c r="C411" t="s">
-        <v>1764</v>
+        <v>1566</v>
       </c>
       <c r="F411" s="2">
-        <v>45811</v>
+        <v>45994</v>
       </c>
       <c r="G411" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H411" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I411" t="s">
-        <v>2052</v>
+        <v>1992</v>
       </c>
       <c r="J411" t="s">
         <v>2140</v>
@@ -27363,10 +27373,10 @@
         <v>1170</v>
       </c>
       <c r="C412" t="s">
-        <v>1564</v>
+        <v>1764</v>
       </c>
       <c r="F412" s="2">
-        <v>45699</v>
+        <v>45811</v>
       </c>
       <c r="G412" t="s">
         <v>1914</v>
@@ -27375,7 +27385,7 @@
         <v>1924</v>
       </c>
       <c r="I412" t="s">
-        <v>2104</v>
+        <v>2052</v>
       </c>
       <c r="J412" t="s">
         <v>2140</v>
@@ -27395,22 +27405,22 @@
         <v>1171</v>
       </c>
       <c r="C413" t="s">
-        <v>1765</v>
+        <v>1564</v>
       </c>
       <c r="F413" s="2">
-        <v>45883</v>
+        <v>45699</v>
       </c>
       <c r="G413" t="s">
         <v>1914</v>
       </c>
       <c r="H413" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I413" t="s">
-        <v>2020</v>
+        <v>2104</v>
       </c>
       <c r="J413" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K413" t="s">
         <v>2550</v>
@@ -27427,22 +27437,22 @@
         <v>1172</v>
       </c>
       <c r="C414" t="s">
-        <v>1683</v>
+        <v>1765</v>
       </c>
       <c r="F414" s="2">
-        <v>46155</v>
+        <v>45883</v>
       </c>
       <c r="G414" t="s">
         <v>1914</v>
       </c>
       <c r="H414" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I414" t="s">
-        <v>2072</v>
+        <v>2020</v>
       </c>
       <c r="J414" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K414" t="s">
         <v>2551</v>
@@ -27459,19 +27469,19 @@
         <v>1173</v>
       </c>
       <c r="C415" t="s">
-        <v>1556</v>
+        <v>1683</v>
       </c>
       <c r="F415" s="2">
-        <v>46175</v>
+        <v>46155</v>
       </c>
       <c r="G415" t="s">
         <v>1914</v>
       </c>
       <c r="H415" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I415" t="s">
-        <v>1992</v>
+        <v>2072</v>
       </c>
       <c r="J415" t="s">
         <v>2140</v>
@@ -27491,19 +27501,19 @@
         <v>1174</v>
       </c>
       <c r="C416" t="s">
-        <v>1711</v>
+        <v>1556</v>
       </c>
       <c r="F416" s="2">
-        <v>45923</v>
+        <v>46175</v>
       </c>
       <c r="G416" t="s">
         <v>1914</v>
       </c>
       <c r="H416" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I416" t="s">
-        <v>2041</v>
+        <v>1992</v>
       </c>
       <c r="J416" t="s">
         <v>2140</v>
@@ -27523,22 +27533,22 @@
         <v>1175</v>
       </c>
       <c r="C417" t="s">
-        <v>1766</v>
+        <v>1711</v>
       </c>
       <c r="F417" s="2">
-        <v>45870</v>
+        <v>45923</v>
       </c>
       <c r="G417" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H417" t="s">
         <v>1924</v>
       </c>
       <c r="I417" t="s">
-        <v>2074</v>
+        <v>2041</v>
       </c>
       <c r="J417" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K417" t="s">
         <v>2554</v>
@@ -27555,22 +27565,22 @@
         <v>1176</v>
       </c>
       <c r="C418" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="F418" s="2">
-        <v>45751</v>
+        <v>45870</v>
       </c>
       <c r="G418" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="H418" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I418" t="s">
-        <v>2009</v>
+        <v>2074</v>
       </c>
       <c r="J418" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K418" t="s">
         <v>2555</v>
@@ -27587,28 +27597,22 @@
         <v>1177</v>
       </c>
       <c r="C419" t="s">
-        <v>1768</v>
-      </c>
-      <c r="D419" t="s">
-        <v>1879</v>
-      </c>
-      <c r="E419" t="s">
-        <v>1879</v>
+        <v>1767</v>
       </c>
       <c r="F419" s="2">
-        <v>46127</v>
+        <v>45751</v>
       </c>
       <c r="G419" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H419" t="s">
-        <v>1959</v>
+        <v>1922</v>
       </c>
       <c r="I419" t="s">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="J419" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K419" t="s">
         <v>2556</v>
@@ -27625,28 +27629,28 @@
         <v>1178</v>
       </c>
       <c r="C420" t="s">
-        <v>1688</v>
+        <v>1768</v>
       </c>
       <c r="D420" t="s">
-        <v>1600</v>
+        <v>1879</v>
       </c>
       <c r="E420" t="s">
-        <v>1656</v>
+        <v>1879</v>
       </c>
       <c r="F420" s="2">
-        <v>46083</v>
+        <v>46127</v>
       </c>
       <c r="G420" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H420" t="s">
-        <v>1931</v>
+        <v>1959</v>
       </c>
       <c r="I420" t="s">
-        <v>1978</v>
+        <v>2024</v>
       </c>
       <c r="J420" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K420" t="s">
         <v>2557</v>
@@ -27663,25 +27667,25 @@
         <v>1179</v>
       </c>
       <c r="C421" t="s">
-        <v>1580</v>
+        <v>1688</v>
       </c>
       <c r="D421" t="s">
-        <v>1548</v>
+        <v>1600</v>
       </c>
       <c r="E421" t="s">
-        <v>1826</v>
+        <v>1656</v>
       </c>
       <c r="F421" s="2">
-        <v>45771</v>
+        <v>46083</v>
       </c>
       <c r="G421" t="s">
         <v>1914</v>
       </c>
       <c r="H421" t="s">
-        <v>1961</v>
+        <v>1931</v>
       </c>
       <c r="I421" t="s">
-        <v>2105</v>
+        <v>1978</v>
       </c>
       <c r="J421" t="s">
         <v>2140</v>
@@ -27701,22 +27705,28 @@
         <v>1180</v>
       </c>
       <c r="C422" t="s">
-        <v>1516</v>
+        <v>1580</v>
+      </c>
+      <c r="D422" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E422" t="s">
+        <v>1826</v>
       </c>
       <c r="F422" s="2">
-        <v>45705</v>
+        <v>45771</v>
       </c>
       <c r="G422" t="s">
         <v>1914</v>
       </c>
       <c r="H422" t="s">
-        <v>1921</v>
+        <v>1961</v>
       </c>
       <c r="I422" t="s">
-        <v>2020</v>
+        <v>2105</v>
       </c>
       <c r="J422" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K422" t="s">
         <v>2559</v>
@@ -27733,19 +27743,19 @@
         <v>1181</v>
       </c>
       <c r="C423" t="s">
-        <v>1769</v>
+        <v>1516</v>
       </c>
       <c r="F423" s="2">
-        <v>45728</v>
+        <v>45705</v>
       </c>
       <c r="G423" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H423" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I423" t="s">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="J423" t="s">
         <v>2141</v>
@@ -27765,22 +27775,22 @@
         <v>1182</v>
       </c>
       <c r="C424" t="s">
-        <v>1596</v>
+        <v>1769</v>
       </c>
       <c r="F424" s="2">
-        <v>45805</v>
+        <v>45728</v>
       </c>
       <c r="G424" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H424" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I424" t="s">
-        <v>2075</v>
+        <v>2009</v>
       </c>
       <c r="J424" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K424" t="s">
         <v>2561</v>
@@ -27797,25 +27807,19 @@
         <v>1183</v>
       </c>
       <c r="C425" t="s">
-        <v>1721</v>
-      </c>
-      <c r="D425" t="s">
-        <v>1881</v>
-      </c>
-      <c r="E425" t="s">
-        <v>1518</v>
+        <v>1596</v>
       </c>
       <c r="F425" s="2">
-        <v>46139</v>
+        <v>45805</v>
       </c>
       <c r="G425" t="s">
         <v>1914</v>
       </c>
       <c r="H425" t="s">
-        <v>1918</v>
+        <v>1924</v>
       </c>
       <c r="I425" t="s">
-        <v>1994</v>
+        <v>2075</v>
       </c>
       <c r="J425" t="s">
         <v>2140</v>
@@ -27835,19 +27839,25 @@
         <v>1184</v>
       </c>
       <c r="C426" t="s">
-        <v>1549</v>
+        <v>1721</v>
+      </c>
+      <c r="D426" t="s">
+        <v>1881</v>
+      </c>
+      <c r="E426" t="s">
+        <v>1518</v>
       </c>
       <c r="F426" s="2">
-        <v>46044</v>
+        <v>46139</v>
       </c>
       <c r="G426" t="s">
         <v>1914</v>
       </c>
       <c r="H426" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="I426" t="s">
-        <v>2019</v>
+        <v>1994</v>
       </c>
       <c r="J426" t="s">
         <v>2140</v>
@@ -27867,19 +27877,19 @@
         <v>1185</v>
       </c>
       <c r="C427" t="s">
-        <v>1577</v>
+        <v>1549</v>
       </c>
       <c r="F427" s="2">
-        <v>45834</v>
+        <v>46044</v>
       </c>
       <c r="G427" t="s">
         <v>1914</v>
       </c>
       <c r="H427" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I427" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J427" t="s">
         <v>2140</v>
@@ -27899,19 +27909,19 @@
         <v>1186</v>
       </c>
       <c r="C428" t="s">
-        <v>1770</v>
+        <v>1577</v>
       </c>
       <c r="F428" s="2">
-        <v>46196</v>
+        <v>45834</v>
       </c>
       <c r="G428" t="s">
         <v>1914</v>
       </c>
       <c r="H428" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I428" t="s">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="J428" t="s">
         <v>2140</v>
@@ -27931,25 +27941,19 @@
         <v>1187</v>
       </c>
       <c r="C429" t="s">
-        <v>1671</v>
-      </c>
-      <c r="D429" t="s">
-        <v>1760</v>
-      </c>
-      <c r="E429" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="F429" s="2">
-        <v>46091</v>
+        <v>46196</v>
       </c>
       <c r="G429" t="s">
         <v>1914</v>
       </c>
       <c r="H429" t="s">
-        <v>1938</v>
+        <v>1921</v>
       </c>
       <c r="I429" t="s">
-        <v>2106</v>
+        <v>2010</v>
       </c>
       <c r="J429" t="s">
         <v>2140</v>
@@ -27969,19 +27973,25 @@
         <v>1188</v>
       </c>
       <c r="C430" t="s">
-        <v>1525</v>
+        <v>1671</v>
+      </c>
+      <c r="D430" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E430" t="s">
+        <v>1760</v>
       </c>
       <c r="F430" s="2">
-        <v>46168</v>
+        <v>46091</v>
       </c>
       <c r="G430" t="s">
         <v>1914</v>
       </c>
       <c r="H430" t="s">
-        <v>1921</v>
+        <v>1938</v>
       </c>
       <c r="I430" t="s">
-        <v>2011</v>
+        <v>2106</v>
       </c>
       <c r="J430" t="s">
         <v>2140</v>
@@ -28001,19 +28011,19 @@
         <v>1189</v>
       </c>
       <c r="C431" t="s">
-        <v>1771</v>
+        <v>1525</v>
       </c>
       <c r="F431" s="2">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="G431" t="s">
         <v>1914</v>
       </c>
       <c r="H431" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I431" t="s">
-        <v>2027</v>
+        <v>2011</v>
       </c>
       <c r="J431" t="s">
         <v>2140</v>
@@ -28033,16 +28043,10 @@
         <v>1190</v>
       </c>
       <c r="C432" t="s">
-        <v>1630</v>
-      </c>
-      <c r="D432" t="s">
-        <v>1882</v>
-      </c>
-      <c r="E432" t="s">
-        <v>1882</v>
+        <v>1771</v>
       </c>
       <c r="F432" s="2">
-        <v>45754</v>
+        <v>46157</v>
       </c>
       <c r="G432" t="s">
         <v>1914</v>
@@ -28051,10 +28055,10 @@
         <v>1922</v>
       </c>
       <c r="I432" t="s">
-        <v>1978</v>
+        <v>2027</v>
       </c>
       <c r="J432" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K432" t="s">
         <v>2569</v>
@@ -28071,19 +28075,25 @@
         <v>1191</v>
       </c>
       <c r="C433" t="s">
-        <v>1772</v>
+        <v>1630</v>
+      </c>
+      <c r="D433" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E433" t="s">
+        <v>1882</v>
       </c>
       <c r="F433" s="2">
-        <v>45659</v>
+        <v>45754</v>
       </c>
       <c r="G433" t="s">
         <v>1914</v>
       </c>
       <c r="H433" t="s">
-        <v>1962</v>
+        <v>1922</v>
       </c>
       <c r="I433" t="s">
-        <v>2107</v>
+        <v>1978</v>
       </c>
       <c r="J433" t="s">
         <v>2141</v>
@@ -28103,22 +28113,22 @@
         <v>1192</v>
       </c>
       <c r="C434" t="s">
-        <v>1749</v>
+        <v>1772</v>
       </c>
       <c r="F434" s="2">
-        <v>45891</v>
+        <v>45659</v>
       </c>
       <c r="G434" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H434" t="s">
-        <v>1921</v>
+        <v>1962</v>
       </c>
       <c r="I434" t="s">
-        <v>2059</v>
+        <v>2107</v>
       </c>
       <c r="J434" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K434" t="s">
         <v>2571</v>
@@ -28135,19 +28145,19 @@
         <v>1193</v>
       </c>
       <c r="C435" t="s">
-        <v>1773</v>
+        <v>1749</v>
       </c>
       <c r="F435" s="2">
-        <v>46189</v>
+        <v>45891</v>
       </c>
       <c r="G435" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H435" t="s">
-        <v>1963</v>
+        <v>1921</v>
       </c>
       <c r="I435" t="s">
-        <v>2021</v>
+        <v>2059</v>
       </c>
       <c r="J435" t="s">
         <v>2140</v>
@@ -28167,19 +28177,19 @@
         <v>1194</v>
       </c>
       <c r="C436" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="F436" s="2">
-        <v>45728</v>
+        <v>46189</v>
       </c>
       <c r="G436" t="s">
         <v>1914</v>
       </c>
       <c r="H436" t="s">
-        <v>1921</v>
+        <v>1963</v>
       </c>
       <c r="I436" t="s">
-        <v>2108</v>
+        <v>2021</v>
       </c>
       <c r="J436" t="s">
         <v>2140</v>
@@ -28199,19 +28209,19 @@
         <v>1195</v>
       </c>
       <c r="C437" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="F437" s="2">
-        <v>46196</v>
+        <v>45728</v>
       </c>
       <c r="G437" t="s">
         <v>1914</v>
       </c>
       <c r="H437" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I437" t="s">
-        <v>2018</v>
+        <v>2108</v>
       </c>
       <c r="J437" t="s">
         <v>2140</v>
@@ -28231,28 +28241,22 @@
         <v>1196</v>
       </c>
       <c r="C438" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D438" t="s">
-        <v>1534</v>
-      </c>
-      <c r="E438" t="s">
-        <v>1908</v>
+        <v>1775</v>
       </c>
       <c r="F438" s="2">
-        <v>45831</v>
+        <v>46196</v>
       </c>
       <c r="G438" t="s">
         <v>1914</v>
       </c>
       <c r="H438" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="I438" t="s">
-        <v>2062</v>
+        <v>2018</v>
       </c>
       <c r="J438" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K438" t="s">
         <v>2575</v>
@@ -28269,22 +28273,28 @@
         <v>1197</v>
       </c>
       <c r="C439" t="s">
-        <v>1582</v>
+        <v>1776</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E439" t="s">
+        <v>1908</v>
       </c>
       <c r="F439" s="2">
-        <v>46044</v>
+        <v>45831</v>
       </c>
       <c r="G439" t="s">
         <v>1914</v>
       </c>
       <c r="H439" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="I439" t="s">
-        <v>1988</v>
+        <v>2062</v>
       </c>
       <c r="J439" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K439" t="s">
         <v>2576</v>
@@ -28301,19 +28311,19 @@
         <v>1198</v>
       </c>
       <c r="C440" t="s">
-        <v>1522</v>
+        <v>1582</v>
       </c>
       <c r="F440" s="2">
-        <v>45888</v>
+        <v>46044</v>
       </c>
       <c r="G440" t="s">
         <v>1914</v>
       </c>
       <c r="H440" t="s">
-        <v>1950</v>
+        <v>1922</v>
       </c>
       <c r="I440" t="s">
-        <v>2080</v>
+        <v>1988</v>
       </c>
       <c r="J440" t="s">
         <v>2140</v>
@@ -28333,19 +28343,19 @@
         <v>1199</v>
       </c>
       <c r="C441" t="s">
-        <v>1777</v>
+        <v>1522</v>
       </c>
       <c r="F441" s="2">
-        <v>46189</v>
+        <v>45888</v>
       </c>
       <c r="G441" t="s">
         <v>1914</v>
       </c>
       <c r="H441" t="s">
-        <v>1921</v>
+        <v>1950</v>
       </c>
       <c r="I441" t="s">
-        <v>2109</v>
+        <v>2080</v>
       </c>
       <c r="J441" t="s">
         <v>2140</v>
@@ -28365,22 +28375,22 @@
         <v>1200</v>
       </c>
       <c r="C442" t="s">
-        <v>1742</v>
+        <v>1777</v>
       </c>
       <c r="F442" s="2">
-        <v>46048</v>
+        <v>46189</v>
       </c>
       <c r="G442" t="s">
         <v>1914</v>
       </c>
       <c r="H442" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I442" t="s">
-        <v>2058</v>
+        <v>2109</v>
       </c>
       <c r="J442" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K442" t="s">
         <v>2579</v>
@@ -28397,28 +28407,22 @@
         <v>1201</v>
       </c>
       <c r="C443" t="s">
-        <v>1596</v>
-      </c>
-      <c r="D443" t="s">
-        <v>1883</v>
-      </c>
-      <c r="E443" t="s">
-        <v>1615</v>
+        <v>1742</v>
       </c>
       <c r="F443" s="2">
-        <v>45894</v>
+        <v>46048</v>
       </c>
       <c r="G443" t="s">
         <v>1914</v>
       </c>
       <c r="H443" t="s">
-        <v>1964</v>
+        <v>1924</v>
       </c>
       <c r="I443" t="s">
-        <v>2021</v>
+        <v>2058</v>
       </c>
       <c r="J443" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K443" t="s">
         <v>2580</v>
@@ -28435,25 +28439,25 @@
         <v>1202</v>
       </c>
       <c r="C444" t="s">
-        <v>1677</v>
+        <v>1596</v>
       </c>
       <c r="D444" t="s">
-        <v>1704</v>
+        <v>1883</v>
       </c>
       <c r="E444" t="s">
-        <v>1704</v>
+        <v>1615</v>
       </c>
       <c r="F444" s="2">
-        <v>45743</v>
+        <v>45894</v>
       </c>
       <c r="G444" t="s">
         <v>1914</v>
       </c>
       <c r="H444" t="s">
-        <v>1941</v>
+        <v>1964</v>
       </c>
       <c r="I444" t="s">
-        <v>2110</v>
+        <v>2021</v>
       </c>
       <c r="J444" t="s">
         <v>2140</v>
@@ -28473,19 +28477,25 @@
         <v>1203</v>
       </c>
       <c r="C445" t="s">
-        <v>1778</v>
+        <v>1677</v>
+      </c>
+      <c r="D445" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E445" t="s">
+        <v>1704</v>
       </c>
       <c r="F445" s="2">
-        <v>46044</v>
+        <v>45743</v>
       </c>
       <c r="G445" t="s">
         <v>1914</v>
       </c>
       <c r="H445" t="s">
-        <v>1922</v>
+        <v>1941</v>
       </c>
       <c r="I445" t="s">
-        <v>2000</v>
+        <v>2110</v>
       </c>
       <c r="J445" t="s">
         <v>2140</v>
@@ -28505,19 +28515,19 @@
         <v>1204</v>
       </c>
       <c r="C446" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="F446" s="2">
-        <v>45868</v>
+        <v>46044</v>
       </c>
       <c r="G446" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H446" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I446" t="s">
-        <v>2041</v>
+        <v>2000</v>
       </c>
       <c r="J446" t="s">
         <v>2140</v>
@@ -28537,19 +28547,19 @@
         <v>1205</v>
       </c>
       <c r="C447" t="s">
-        <v>1520</v>
+        <v>1779</v>
       </c>
       <c r="F447" s="2">
-        <v>46190</v>
+        <v>45868</v>
       </c>
       <c r="G447" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H447" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I447" t="s">
-        <v>2010</v>
+        <v>2041</v>
       </c>
       <c r="J447" t="s">
         <v>2140</v>
@@ -28569,10 +28579,10 @@
         <v>1206</v>
       </c>
       <c r="C448" t="s">
-        <v>1574</v>
+        <v>1520</v>
       </c>
       <c r="F448" s="2">
-        <v>46043</v>
+        <v>46190</v>
       </c>
       <c r="G448" t="s">
         <v>1914</v>
@@ -28581,7 +28591,7 @@
         <v>1922</v>
       </c>
       <c r="I448" t="s">
-        <v>1978</v>
+        <v>2010</v>
       </c>
       <c r="J448" t="s">
         <v>2140</v>
@@ -28601,10 +28611,10 @@
         <v>1207</v>
       </c>
       <c r="C449" t="s">
-        <v>1780</v>
+        <v>1574</v>
       </c>
       <c r="F449" s="2">
-        <v>46149</v>
+        <v>46043</v>
       </c>
       <c r="G449" t="s">
         <v>1914</v>
@@ -28613,7 +28623,7 @@
         <v>1922</v>
       </c>
       <c r="I449" t="s">
-        <v>2005</v>
+        <v>1978</v>
       </c>
       <c r="J449" t="s">
         <v>2140</v>
@@ -28633,22 +28643,22 @@
         <v>1208</v>
       </c>
       <c r="C450" t="s">
-        <v>1599</v>
+        <v>1780</v>
       </c>
       <c r="F450" s="2">
-        <v>45854</v>
+        <v>46149</v>
       </c>
       <c r="G450" t="s">
         <v>1914</v>
       </c>
       <c r="H450" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I450" t="s">
-        <v>2027</v>
+        <v>2005</v>
       </c>
       <c r="J450" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K450" t="s">
         <v>2587</v>
@@ -28665,19 +28675,19 @@
         <v>1209</v>
       </c>
       <c r="C451" t="s">
-        <v>1686</v>
+        <v>1599</v>
       </c>
       <c r="F451" s="2">
-        <v>45931</v>
+        <v>45854</v>
       </c>
       <c r="G451" t="s">
         <v>1914</v>
       </c>
       <c r="H451" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I451" t="s">
-        <v>2107</v>
+        <v>2027</v>
       </c>
       <c r="J451" t="s">
         <v>2141</v>
@@ -28697,10 +28707,10 @@
         <v>1210</v>
       </c>
       <c r="C452" t="s">
-        <v>1604</v>
+        <v>1686</v>
       </c>
       <c r="F452" s="2">
-        <v>46092</v>
+        <v>45931</v>
       </c>
       <c r="G452" t="s">
         <v>1914</v>
@@ -28709,10 +28719,10 @@
         <v>1924</v>
       </c>
       <c r="I452" t="s">
-        <v>2021</v>
+        <v>2107</v>
       </c>
       <c r="J452" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K452" t="s">
         <v>2589</v>
@@ -28729,10 +28739,10 @@
         <v>1211</v>
       </c>
       <c r="C453" t="s">
-        <v>1564</v>
+        <v>1604</v>
       </c>
       <c r="F453" s="2">
-        <v>45699</v>
+        <v>46092</v>
       </c>
       <c r="G453" t="s">
         <v>1914</v>
@@ -28741,7 +28751,7 @@
         <v>1924</v>
       </c>
       <c r="I453" t="s">
-        <v>1981</v>
+        <v>2021</v>
       </c>
       <c r="J453" t="s">
         <v>2140</v>
@@ -28761,19 +28771,19 @@
         <v>1212</v>
       </c>
       <c r="C454" t="s">
-        <v>1648</v>
+        <v>1564</v>
       </c>
       <c r="F454" s="2">
-        <v>45866</v>
+        <v>45699</v>
       </c>
       <c r="G454" t="s">
         <v>1914</v>
       </c>
       <c r="H454" t="s">
-        <v>1919</v>
+        <v>1924</v>
       </c>
       <c r="I454" t="s">
-        <v>2090</v>
+        <v>1981</v>
       </c>
       <c r="J454" t="s">
         <v>2140</v>
@@ -28793,19 +28803,19 @@
         <v>1213</v>
       </c>
       <c r="C455" t="s">
-        <v>1720</v>
+        <v>1648</v>
       </c>
       <c r="F455" s="2">
-        <v>46091</v>
+        <v>45866</v>
       </c>
       <c r="G455" t="s">
         <v>1914</v>
       </c>
       <c r="H455" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I455" t="s">
-        <v>2059</v>
+        <v>2090</v>
       </c>
       <c r="J455" t="s">
         <v>2140</v>
@@ -28825,19 +28835,19 @@
         <v>1214</v>
       </c>
       <c r="C456" t="s">
-        <v>1781</v>
+        <v>1720</v>
       </c>
       <c r="F456" s="2">
-        <v>46149</v>
+        <v>46091</v>
       </c>
       <c r="G456" t="s">
         <v>1914</v>
       </c>
       <c r="H456" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I456" t="s">
-        <v>1984</v>
+        <v>2059</v>
       </c>
       <c r="J456" t="s">
         <v>2140</v>
@@ -28857,19 +28867,19 @@
         <v>1215</v>
       </c>
       <c r="C457" t="s">
-        <v>1603</v>
+        <v>1781</v>
       </c>
       <c r="F457" s="2">
-        <v>45838</v>
+        <v>46149</v>
       </c>
       <c r="G457" t="s">
         <v>1914</v>
       </c>
       <c r="H457" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="I457" t="s">
-        <v>2111</v>
+        <v>1984</v>
       </c>
       <c r="J457" t="s">
         <v>2140</v>
@@ -28889,28 +28899,22 @@
         <v>1216</v>
       </c>
       <c r="C458" t="s">
-        <v>1782</v>
-      </c>
-      <c r="D458" t="s">
-        <v>1884</v>
-      </c>
-      <c r="E458" t="s">
-        <v>1884</v>
+        <v>1603</v>
       </c>
       <c r="F458" s="2">
-        <v>45699</v>
+        <v>45838</v>
       </c>
       <c r="G458" t="s">
         <v>1914</v>
       </c>
       <c r="H458" t="s">
-        <v>1965</v>
+        <v>1919</v>
       </c>
       <c r="I458" t="s">
-        <v>2034</v>
+        <v>2111</v>
       </c>
       <c r="J458" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K458" t="s">
         <v>2595</v>
@@ -28927,22 +28931,28 @@
         <v>1217</v>
       </c>
       <c r="C459" t="s">
-        <v>1737</v>
+        <v>1782</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1884</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1884</v>
       </c>
       <c r="F459" s="2">
-        <v>46175</v>
+        <v>45699</v>
       </c>
       <c r="G459" t="s">
         <v>1914</v>
       </c>
       <c r="H459" t="s">
-        <v>1922</v>
+        <v>1965</v>
       </c>
       <c r="I459" t="s">
-        <v>2027</v>
+        <v>2034</v>
       </c>
       <c r="J459" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K459" t="s">
         <v>2596</v>
@@ -28959,10 +28969,10 @@
         <v>1218</v>
       </c>
       <c r="C460" t="s">
-        <v>1783</v>
+        <v>1737</v>
       </c>
       <c r="F460" s="2">
-        <v>45877</v>
+        <v>46175</v>
       </c>
       <c r="G460" t="s">
         <v>1914</v>
@@ -28971,7 +28981,7 @@
         <v>1922</v>
       </c>
       <c r="I460" t="s">
-        <v>1977</v>
+        <v>2027</v>
       </c>
       <c r="J460" t="s">
         <v>2140</v>
@@ -28991,22 +29001,19 @@
         <v>1219</v>
       </c>
       <c r="C461" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D461" t="s">
-        <v>1689</v>
+        <v>1783</v>
       </c>
       <c r="F461" s="2">
-        <v>46154</v>
+        <v>45877</v>
       </c>
       <c r="G461" t="s">
         <v>1914</v>
       </c>
       <c r="H461" t="s">
-        <v>1938</v>
+        <v>1922</v>
       </c>
       <c r="I461" t="s">
-        <v>2013</v>
+        <v>1977</v>
       </c>
       <c r="J461" t="s">
         <v>2140</v>
@@ -29026,19 +29033,22 @@
         <v>1220</v>
       </c>
       <c r="C462" t="s">
-        <v>1785</v>
+        <v>1784</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1689</v>
       </c>
       <c r="F462" s="2">
-        <v>46118</v>
+        <v>46154</v>
       </c>
       <c r="G462" t="s">
         <v>1914</v>
       </c>
       <c r="H462" t="s">
-        <v>1923</v>
+        <v>1938</v>
       </c>
       <c r="I462" t="s">
-        <v>2112</v>
+        <v>2013</v>
       </c>
       <c r="J462" t="s">
         <v>2140</v>
@@ -29058,22 +29068,22 @@
         <v>1221</v>
       </c>
       <c r="C463" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="F463" s="2">
-        <v>46176</v>
+        <v>46118</v>
       </c>
       <c r="G463" t="s">
         <v>1914</v>
       </c>
       <c r="H463" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I463" t="s">
-        <v>2024</v>
+        <v>2112</v>
       </c>
       <c r="J463" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K463" t="s">
         <v>2600</v>
@@ -29090,22 +29100,22 @@
         <v>1222</v>
       </c>
       <c r="C464" t="s">
-        <v>1555</v>
+        <v>1786</v>
       </c>
       <c r="F464" s="2">
-        <v>46211</v>
+        <v>46176</v>
       </c>
       <c r="G464" t="s">
         <v>1914</v>
       </c>
       <c r="H464" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I464" t="s">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="J464" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K464" t="s">
         <v>2601</v>
@@ -29122,19 +29132,19 @@
         <v>1223</v>
       </c>
       <c r="C465" t="s">
-        <v>1787</v>
+        <v>1555</v>
       </c>
       <c r="F465" s="2">
-        <v>46198</v>
+        <v>46211</v>
       </c>
       <c r="G465" t="s">
         <v>1914</v>
       </c>
       <c r="H465" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I465" t="s">
-        <v>2113</v>
+        <v>2011</v>
       </c>
       <c r="J465" t="s">
         <v>2140</v>
@@ -29154,10 +29164,10 @@
         <v>1224</v>
       </c>
       <c r="C466" t="s">
-        <v>1665</v>
+        <v>1787</v>
       </c>
       <c r="F466" s="2">
-        <v>45793</v>
+        <v>46198</v>
       </c>
       <c r="G466" t="s">
         <v>1914</v>
@@ -29166,7 +29176,7 @@
         <v>1922</v>
       </c>
       <c r="I466" t="s">
-        <v>2070</v>
+        <v>2113</v>
       </c>
       <c r="J466" t="s">
         <v>2140</v>
@@ -29186,19 +29196,19 @@
         <v>1225</v>
       </c>
       <c r="C467" t="s">
-        <v>1788</v>
+        <v>1665</v>
       </c>
       <c r="F467" s="2">
-        <v>45993</v>
+        <v>45793</v>
       </c>
       <c r="G467" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H467" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I467" t="s">
-        <v>2096</v>
+        <v>2070</v>
       </c>
       <c r="J467" t="s">
         <v>2140</v>
@@ -29218,22 +29228,22 @@
         <v>1226</v>
       </c>
       <c r="C468" t="s">
-        <v>1599</v>
+        <v>1788</v>
       </c>
       <c r="F468" s="2">
-        <v>45854</v>
+        <v>45993</v>
       </c>
       <c r="G468" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="H468" t="s">
         <v>1921</v>
       </c>
       <c r="I468" t="s">
-        <v>2027</v>
+        <v>2096</v>
       </c>
       <c r="J468" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K468" t="s">
         <v>2605</v>
@@ -29250,25 +29260,22 @@
         <v>1227</v>
       </c>
       <c r="C469" t="s">
-        <v>1582</v>
-      </c>
-      <c r="D469" t="s">
-        <v>1613</v>
+        <v>1599</v>
       </c>
       <c r="F469" s="2">
-        <v>45972</v>
+        <v>45854</v>
       </c>
       <c r="G469" t="s">
         <v>1914</v>
       </c>
       <c r="H469" t="s">
-        <v>1943</v>
+        <v>1921</v>
       </c>
       <c r="I469" t="s">
-        <v>2066</v>
+        <v>2027</v>
       </c>
       <c r="J469" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K469" t="s">
         <v>2606</v>
@@ -29285,19 +29292,22 @@
         <v>1228</v>
       </c>
       <c r="C470" t="s">
-        <v>1789</v>
+        <v>1582</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1613</v>
       </c>
       <c r="F470" s="2">
-        <v>46211</v>
+        <v>45972</v>
       </c>
       <c r="G470" t="s">
         <v>1914</v>
       </c>
       <c r="H470" t="s">
-        <v>1919</v>
+        <v>1943</v>
       </c>
       <c r="I470" t="s">
-        <v>1974</v>
+        <v>2066</v>
       </c>
       <c r="J470" t="s">
         <v>2140</v>
@@ -29317,19 +29327,19 @@
         <v>1229</v>
       </c>
       <c r="C471" t="s">
-        <v>1536</v>
+        <v>1789</v>
       </c>
       <c r="F471" s="2">
-        <v>46168</v>
+        <v>46211</v>
       </c>
       <c r="G471" t="s">
         <v>1914</v>
       </c>
       <c r="H471" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I471" t="s">
-        <v>2114</v>
+        <v>1974</v>
       </c>
       <c r="J471" t="s">
         <v>2140</v>
@@ -29349,25 +29359,19 @@
         <v>1230</v>
       </c>
       <c r="C472" t="s">
-        <v>1759</v>
-      </c>
-      <c r="D472" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E472" t="s">
-        <v>1850</v>
+        <v>1536</v>
       </c>
       <c r="F472" s="2">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="G472" t="s">
         <v>1914</v>
       </c>
       <c r="H472" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I472" t="s">
-        <v>2016</v>
+        <v>2114</v>
       </c>
       <c r="J472" t="s">
         <v>2140</v>
@@ -29387,19 +29391,25 @@
         <v>1231</v>
       </c>
       <c r="C473" t="s">
-        <v>1610</v>
+        <v>1759</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1850</v>
       </c>
       <c r="F473" s="2">
-        <v>46120</v>
+        <v>46176</v>
       </c>
       <c r="G473" t="s">
         <v>1914</v>
       </c>
       <c r="H473" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I473" t="s">
-        <v>2033</v>
+        <v>2016</v>
       </c>
       <c r="J473" t="s">
         <v>2140</v>
@@ -29419,25 +29429,19 @@
         <v>1232</v>
       </c>
       <c r="C474" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D474" t="s">
-        <v>1879</v>
-      </c>
-      <c r="E474" t="s">
-        <v>1879</v>
+        <v>1610</v>
       </c>
       <c r="F474" s="2">
-        <v>46188</v>
+        <v>46120</v>
       </c>
       <c r="G474" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H474" t="s">
         <v>1922</v>
       </c>
       <c r="I474" t="s">
-        <v>2041</v>
+        <v>2033</v>
       </c>
       <c r="J474" t="s">
         <v>2140</v>
@@ -29457,25 +29461,28 @@
         <v>1233</v>
       </c>
       <c r="C475" t="s">
-        <v>1790</v>
+        <v>1654</v>
       </c>
       <c r="D475" t="s">
-        <v>1885</v>
+        <v>1879</v>
+      </c>
+      <c r="E475" t="s">
+        <v>1879</v>
       </c>
       <c r="F475" s="2">
-        <v>45853</v>
+        <v>46188</v>
       </c>
       <c r="G475" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H475" t="s">
-        <v>1929</v>
+        <v>1922</v>
       </c>
       <c r="I475" t="s">
-        <v>1976</v>
+        <v>2041</v>
       </c>
       <c r="J475" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K475" t="s">
         <v>2612</v>
@@ -29492,22 +29499,25 @@
         <v>1234</v>
       </c>
       <c r="C476" t="s">
-        <v>1674</v>
+        <v>1790</v>
+      </c>
+      <c r="D476" t="s">
+        <v>1885</v>
       </c>
       <c r="F476" s="2">
-        <v>46113</v>
+        <v>45853</v>
       </c>
       <c r="G476" t="s">
         <v>1914</v>
       </c>
       <c r="H476" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
       <c r="I476" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="J476" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K476" t="s">
         <v>2613</v>
@@ -29524,19 +29534,19 @@
         <v>1235</v>
       </c>
       <c r="C477" t="s">
-        <v>1783</v>
+        <v>1674</v>
       </c>
       <c r="F477" s="2">
-        <v>45853</v>
+        <v>46113</v>
       </c>
       <c r="G477" t="s">
         <v>1914</v>
       </c>
       <c r="H477" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I477" t="s">
-        <v>2114</v>
+        <v>1977</v>
       </c>
       <c r="J477" t="s">
         <v>2140</v>
@@ -29556,19 +29566,19 @@
         <v>1236</v>
       </c>
       <c r="C478" t="s">
-        <v>1708</v>
+        <v>1783</v>
       </c>
       <c r="F478" s="2">
-        <v>45699</v>
+        <v>45853</v>
       </c>
       <c r="G478" t="s">
         <v>1914</v>
       </c>
       <c r="H478" t="s">
-        <v>1918</v>
+        <v>1922</v>
       </c>
       <c r="I478" t="s">
-        <v>2011</v>
+        <v>2114</v>
       </c>
       <c r="J478" t="s">
         <v>2140</v>
@@ -29588,19 +29598,19 @@
         <v>1237</v>
       </c>
       <c r="C479" t="s">
-        <v>1791</v>
+        <v>1708</v>
       </c>
       <c r="F479" s="2">
-        <v>45852</v>
+        <v>45699</v>
       </c>
       <c r="G479" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H479" t="s">
         <v>1918</v>
       </c>
       <c r="I479" t="s">
-        <v>1983</v>
+        <v>2011</v>
       </c>
       <c r="J479" t="s">
         <v>2140</v>
@@ -29620,22 +29630,19 @@
         <v>1238</v>
       </c>
       <c r="C480" t="s">
-        <v>1733</v>
-      </c>
-      <c r="D480" t="s">
-        <v>1547</v>
+        <v>1791</v>
       </c>
       <c r="F480" s="2">
-        <v>45972</v>
+        <v>45852</v>
       </c>
       <c r="G480" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H480" t="s">
-        <v>1943</v>
+        <v>1918</v>
       </c>
       <c r="I480" t="s">
-        <v>2038</v>
+        <v>1983</v>
       </c>
       <c r="J480" t="s">
         <v>2140</v>
@@ -29655,19 +29662,22 @@
         <v>1239</v>
       </c>
       <c r="C481" t="s">
-        <v>1737</v>
+        <v>1733</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1547</v>
       </c>
       <c r="F481" s="2">
-        <v>46149</v>
+        <v>45972</v>
       </c>
       <c r="G481" t="s">
         <v>1914</v>
       </c>
       <c r="H481" t="s">
-        <v>1922</v>
+        <v>1943</v>
       </c>
       <c r="I481" t="s">
-        <v>1977</v>
+        <v>2038</v>
       </c>
       <c r="J481" t="s">
         <v>2140</v>
@@ -29687,19 +29697,19 @@
         <v>1240</v>
       </c>
       <c r="C482" t="s">
-        <v>1745</v>
+        <v>1737</v>
       </c>
       <c r="F482" s="2">
-        <v>46035</v>
+        <v>46149</v>
       </c>
       <c r="G482" t="s">
         <v>1914</v>
       </c>
       <c r="H482" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I482" t="s">
-        <v>2000</v>
+        <v>1977</v>
       </c>
       <c r="J482" t="s">
         <v>2140</v>
@@ -29719,19 +29729,19 @@
         <v>1241</v>
       </c>
       <c r="C483" t="s">
-        <v>1731</v>
+        <v>1745</v>
       </c>
       <c r="F483" s="2">
-        <v>46154</v>
+        <v>46035</v>
       </c>
       <c r="G483" t="s">
         <v>1914</v>
       </c>
       <c r="H483" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I483" t="s">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="J483" t="s">
         <v>2140</v>
@@ -29751,25 +29761,19 @@
         <v>1242</v>
       </c>
       <c r="C484" t="s">
-        <v>1577</v>
-      </c>
-      <c r="D484" t="s">
-        <v>1599</v>
-      </c>
-      <c r="E484" t="s">
-        <v>1698</v>
+        <v>1731</v>
       </c>
       <c r="F484" s="2">
-        <v>45985</v>
+        <v>46154</v>
       </c>
       <c r="G484" t="s">
         <v>1914</v>
       </c>
       <c r="H484" t="s">
-        <v>1943</v>
+        <v>1922</v>
       </c>
       <c r="I484" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="J484" t="s">
         <v>2140</v>
@@ -29789,22 +29793,28 @@
         <v>1243</v>
       </c>
       <c r="C485" t="s">
-        <v>1511</v>
+        <v>1577</v>
+      </c>
+      <c r="D485" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E485" t="s">
+        <v>1698</v>
       </c>
       <c r="F485" s="2">
-        <v>45758</v>
+        <v>45985</v>
       </c>
       <c r="G485" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H485" t="s">
-        <v>1923</v>
+        <v>1943</v>
       </c>
       <c r="I485" t="s">
-        <v>2112</v>
+        <v>2018</v>
       </c>
       <c r="J485" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K485" t="s">
         <v>2622</v>
@@ -29821,22 +29831,22 @@
         <v>1244</v>
       </c>
       <c r="C486" t="s">
-        <v>1536</v>
+        <v>1511</v>
       </c>
       <c r="F486" s="2">
-        <v>46064</v>
+        <v>45758</v>
       </c>
       <c r="G486" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="H486" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="I486" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="J486" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K486" t="s">
         <v>2623</v>
@@ -29853,19 +29863,19 @@
         <v>1245</v>
       </c>
       <c r="C487" t="s">
-        <v>1747</v>
+        <v>1536</v>
       </c>
       <c r="F487" s="2">
-        <v>46204</v>
+        <v>46064</v>
       </c>
       <c r="G487" t="s">
         <v>1914</v>
       </c>
       <c r="H487" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
       <c r="I487" t="s">
-        <v>2035</v>
+        <v>2115</v>
       </c>
       <c r="J487" t="s">
         <v>2140</v>
@@ -29885,28 +29895,22 @@
         <v>1246</v>
       </c>
       <c r="C488" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D488" t="s">
-        <v>1565</v>
-      </c>
-      <c r="E488" t="s">
-        <v>1565</v>
+        <v>1747</v>
       </c>
       <c r="F488" s="2">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="G488" t="s">
         <v>1914</v>
       </c>
       <c r="H488" t="s">
-        <v>1938</v>
+        <v>1921</v>
       </c>
       <c r="I488" t="s">
-        <v>2049</v>
+        <v>2035</v>
       </c>
       <c r="J488" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K488" t="s">
         <v>2625</v>
@@ -29923,22 +29927,28 @@
         <v>1247</v>
       </c>
       <c r="C489" t="s">
-        <v>1586</v>
+        <v>1792</v>
+      </c>
+      <c r="D489" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E489" t="s">
+        <v>1565</v>
       </c>
       <c r="F489" s="2">
-        <v>45849</v>
+        <v>46198</v>
       </c>
       <c r="G489" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H489" t="s">
-        <v>1921</v>
+        <v>1938</v>
       </c>
       <c r="I489" t="s">
-        <v>2009</v>
+        <v>2049</v>
       </c>
       <c r="J489" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K489" t="s">
         <v>2626</v>
@@ -29955,25 +29965,19 @@
         <v>1248</v>
       </c>
       <c r="C490" t="s">
-        <v>1743</v>
-      </c>
-      <c r="D490" t="s">
-        <v>1886</v>
-      </c>
-      <c r="E490" t="s">
-        <v>1886</v>
+        <v>1586</v>
       </c>
       <c r="F490" s="2">
-        <v>45775</v>
+        <v>45849</v>
       </c>
       <c r="G490" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H490" t="s">
-        <v>1943</v>
+        <v>1921</v>
       </c>
       <c r="I490" t="s">
-        <v>2038</v>
+        <v>2009</v>
       </c>
       <c r="J490" t="s">
         <v>2140</v>
@@ -29993,19 +29997,25 @@
         <v>1249</v>
       </c>
       <c r="C491" t="s">
-        <v>1793</v>
+        <v>1743</v>
+      </c>
+      <c r="D491" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E491" t="s">
+        <v>1886</v>
       </c>
       <c r="F491" s="2">
-        <v>45825</v>
+        <v>45775</v>
       </c>
       <c r="G491" t="s">
         <v>1914</v>
       </c>
       <c r="H491" t="s">
-        <v>1921</v>
+        <v>1943</v>
       </c>
       <c r="I491" t="s">
-        <v>1974</v>
+        <v>2038</v>
       </c>
       <c r="J491" t="s">
         <v>2140</v>
@@ -30025,10 +30035,10 @@
         <v>1250</v>
       </c>
       <c r="C492" t="s">
-        <v>1654</v>
+        <v>1793</v>
       </c>
       <c r="F492" s="2">
-        <v>46128</v>
+        <v>45825</v>
       </c>
       <c r="G492" t="s">
         <v>1914</v>
@@ -30037,7 +30047,7 @@
         <v>1921</v>
       </c>
       <c r="I492" t="s">
-        <v>2021</v>
+        <v>1974</v>
       </c>
       <c r="J492" t="s">
         <v>2140</v>
@@ -30057,22 +30067,19 @@
         <v>1251</v>
       </c>
       <c r="C493" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D493" t="s">
-        <v>1822</v>
+        <v>1654</v>
       </c>
       <c r="F493" s="2">
-        <v>45952</v>
+        <v>46128</v>
       </c>
       <c r="G493" t="s">
         <v>1914</v>
       </c>
       <c r="H493" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="I493" t="s">
-        <v>2112</v>
+        <v>2021</v>
       </c>
       <c r="J493" t="s">
         <v>2140</v>
@@ -30092,19 +30099,22 @@
         <v>1252</v>
       </c>
       <c r="C494" t="s">
-        <v>1707</v>
+        <v>1515</v>
+      </c>
+      <c r="D494" t="s">
+        <v>1822</v>
       </c>
       <c r="F494" s="2">
-        <v>45799</v>
+        <v>45952</v>
       </c>
       <c r="G494" t="s">
         <v>1914</v>
       </c>
       <c r="H494" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I494" t="s">
-        <v>1978</v>
+        <v>2112</v>
       </c>
       <c r="J494" t="s">
         <v>2140</v>
@@ -30124,16 +30134,10 @@
         <v>1253</v>
       </c>
       <c r="C495" t="s">
-        <v>1794</v>
-      </c>
-      <c r="D495" t="s">
-        <v>1513</v>
-      </c>
-      <c r="E495" t="s">
-        <v>1909</v>
+        <v>1707</v>
       </c>
       <c r="F495" s="2">
-        <v>46223</v>
+        <v>45799</v>
       </c>
       <c r="G495" t="s">
         <v>1914</v>
@@ -30142,7 +30146,7 @@
         <v>1922</v>
       </c>
       <c r="I495" t="s">
-        <v>2069</v>
+        <v>1978</v>
       </c>
       <c r="J495" t="s">
         <v>2140</v>
@@ -30162,19 +30166,25 @@
         <v>1254</v>
       </c>
       <c r="C496" t="s">
-        <v>1712</v>
+        <v>1794</v>
+      </c>
+      <c r="D496" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E496" t="s">
+        <v>1909</v>
       </c>
       <c r="F496" s="2">
-        <v>46010</v>
+        <v>46223</v>
       </c>
       <c r="G496" t="s">
         <v>1914</v>
       </c>
       <c r="H496" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I496" t="s">
-        <v>1999</v>
+        <v>2069</v>
       </c>
       <c r="J496" t="s">
         <v>2140</v>
@@ -30194,22 +30204,22 @@
         <v>1255</v>
       </c>
       <c r="C497" t="s">
-        <v>1795</v>
+        <v>1712</v>
       </c>
       <c r="F497" s="2">
-        <v>46167</v>
+        <v>46010</v>
       </c>
       <c r="G497" t="s">
         <v>1914</v>
       </c>
       <c r="H497" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I497" t="s">
-        <v>1978</v>
+        <v>1999</v>
       </c>
       <c r="J497" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K497" t="s">
         <v>2634</v>
@@ -30226,22 +30236,22 @@
         <v>1256</v>
       </c>
       <c r="C498" t="s">
-        <v>1628</v>
+        <v>1795</v>
       </c>
       <c r="F498" s="2">
-        <v>46010</v>
+        <v>46167</v>
       </c>
       <c r="G498" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H498" t="s">
         <v>1921</v>
       </c>
       <c r="I498" t="s">
-        <v>2032</v>
+        <v>1978</v>
       </c>
       <c r="J498" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K498" t="s">
         <v>2635</v>
@@ -30258,19 +30268,19 @@
         <v>1257</v>
       </c>
       <c r="C499" t="s">
-        <v>1538</v>
+        <v>1628</v>
       </c>
       <c r="F499" s="2">
-        <v>46184</v>
+        <v>46010</v>
       </c>
       <c r="G499" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H499" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I499" t="s">
-        <v>1981</v>
+        <v>2032</v>
       </c>
       <c r="J499" t="s">
         <v>2140</v>
@@ -30290,22 +30300,22 @@
         <v>1258</v>
       </c>
       <c r="C500" t="s">
-        <v>1623</v>
+        <v>1538</v>
       </c>
       <c r="F500" s="2">
-        <v>46034</v>
+        <v>46184</v>
       </c>
       <c r="G500" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H500" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I500" t="s">
-        <v>2116</v>
+        <v>1981</v>
       </c>
       <c r="J500" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K500" t="s">
         <v>2637</v>
@@ -30322,22 +30332,22 @@
         <v>1259</v>
       </c>
       <c r="C501" t="s">
-        <v>1574</v>
+        <v>1623</v>
       </c>
       <c r="F501" s="2">
-        <v>46001</v>
+        <v>46034</v>
       </c>
       <c r="G501" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H501" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="I501" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="J501" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K501" t="s">
         <v>2638</v>
@@ -30354,19 +30364,19 @@
         <v>1260</v>
       </c>
       <c r="C502" t="s">
-        <v>1741</v>
+        <v>1574</v>
       </c>
       <c r="F502" s="2">
-        <v>46112</v>
+        <v>46001</v>
       </c>
       <c r="G502" t="s">
         <v>1914</v>
       </c>
       <c r="H502" t="s">
-        <v>1924</v>
+        <v>1918</v>
       </c>
       <c r="I502" t="s">
-        <v>2012</v>
+        <v>2117</v>
       </c>
       <c r="J502" t="s">
         <v>2140</v>
@@ -30386,19 +30396,19 @@
         <v>1261</v>
       </c>
       <c r="C503" t="s">
-        <v>1796</v>
+        <v>1741</v>
       </c>
       <c r="F503" s="2">
-        <v>45680</v>
+        <v>46112</v>
       </c>
       <c r="G503" t="s">
         <v>1914</v>
       </c>
       <c r="H503" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I503" t="s">
-        <v>1978</v>
+        <v>2012</v>
       </c>
       <c r="J503" t="s">
         <v>2140</v>
@@ -30418,10 +30428,10 @@
         <v>1262</v>
       </c>
       <c r="C504" t="s">
-        <v>1599</v>
+        <v>1796</v>
       </c>
       <c r="F504" s="2">
-        <v>45994</v>
+        <v>45680</v>
       </c>
       <c r="G504" t="s">
         <v>1914</v>
@@ -30430,10 +30440,10 @@
         <v>1921</v>
       </c>
       <c r="I504" t="s">
-        <v>2027</v>
+        <v>1978</v>
       </c>
       <c r="J504" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K504" t="s">
         <v>2641</v>
@@ -30450,22 +30460,22 @@
         <v>1263</v>
       </c>
       <c r="C505" t="s">
-        <v>1765</v>
+        <v>1599</v>
       </c>
       <c r="F505" s="2">
-        <v>45714</v>
+        <v>45994</v>
       </c>
       <c r="G505" t="s">
         <v>1914</v>
       </c>
       <c r="H505" t="s">
-        <v>1962</v>
+        <v>1921</v>
       </c>
       <c r="I505" t="s">
-        <v>2108</v>
+        <v>2027</v>
       </c>
       <c r="J505" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K505" t="s">
         <v>2642</v>
@@ -30482,19 +30492,19 @@
         <v>1264</v>
       </c>
       <c r="C506" t="s">
-        <v>1797</v>
+        <v>1765</v>
       </c>
       <c r="F506" s="2">
-        <v>45671</v>
+        <v>45714</v>
       </c>
       <c r="G506" t="s">
         <v>1914</v>
       </c>
       <c r="H506" t="s">
-        <v>1921</v>
+        <v>1962</v>
       </c>
       <c r="I506" t="s">
-        <v>1977</v>
+        <v>2108</v>
       </c>
       <c r="J506" t="s">
         <v>2140</v>
@@ -30514,10 +30524,10 @@
         <v>1265</v>
       </c>
       <c r="C507" t="s">
-        <v>1528</v>
+        <v>1797</v>
       </c>
       <c r="F507" s="2">
-        <v>45992</v>
+        <v>45671</v>
       </c>
       <c r="G507" t="s">
         <v>1914</v>
@@ -30526,7 +30536,7 @@
         <v>1921</v>
       </c>
       <c r="I507" t="s">
-        <v>1992</v>
+        <v>1977</v>
       </c>
       <c r="J507" t="s">
         <v>2140</v>
@@ -30546,10 +30556,10 @@
         <v>1266</v>
       </c>
       <c r="C508" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="F508" s="2">
-        <v>45938</v>
+        <v>45992</v>
       </c>
       <c r="G508" t="s">
         <v>1914</v>
@@ -30558,7 +30568,7 @@
         <v>1921</v>
       </c>
       <c r="I508" t="s">
-        <v>1978</v>
+        <v>1992</v>
       </c>
       <c r="J508" t="s">
         <v>2140</v>
@@ -30578,25 +30588,19 @@
         <v>1267</v>
       </c>
       <c r="C509" t="s">
-        <v>1596</v>
-      </c>
-      <c r="D509" t="s">
-        <v>1627</v>
-      </c>
-      <c r="E509" t="s">
-        <v>1910</v>
+        <v>1524</v>
       </c>
       <c r="F509" s="2">
-        <v>45929</v>
+        <v>45938</v>
       </c>
       <c r="G509" t="s">
         <v>1914</v>
       </c>
       <c r="H509" t="s">
-        <v>1938</v>
+        <v>1921</v>
       </c>
       <c r="I509" t="s">
-        <v>2018</v>
+        <v>1978</v>
       </c>
       <c r="J509" t="s">
         <v>2140</v>
@@ -30616,19 +30620,25 @@
         <v>1268</v>
       </c>
       <c r="C510" t="s">
-        <v>1798</v>
+        <v>1596</v>
+      </c>
+      <c r="D510" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E510" t="s">
+        <v>1910</v>
       </c>
       <c r="F510" s="2">
-        <v>45799</v>
+        <v>45929</v>
       </c>
       <c r="G510" t="s">
         <v>1914</v>
       </c>
       <c r="H510" t="s">
-        <v>1919</v>
+        <v>1938</v>
       </c>
       <c r="I510" t="s">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="J510" t="s">
         <v>2140</v>
@@ -30648,19 +30658,19 @@
         <v>1269</v>
       </c>
       <c r="C511" t="s">
-        <v>1711</v>
+        <v>1798</v>
       </c>
       <c r="F511" s="2">
-        <v>45946</v>
+        <v>45799</v>
       </c>
       <c r="G511" t="s">
         <v>1914</v>
       </c>
       <c r="H511" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I511" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="J511" t="s">
         <v>2140</v>
@@ -30680,25 +30690,19 @@
         <v>1270</v>
       </c>
       <c r="C512" t="s">
-        <v>1780</v>
-      </c>
-      <c r="D512" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1850</v>
+        <v>1711</v>
       </c>
       <c r="F512" s="2">
-        <v>46175</v>
+        <v>45946</v>
       </c>
       <c r="G512" t="s">
         <v>1914</v>
       </c>
       <c r="H512" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I512" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="J512" t="s">
         <v>2140</v>
@@ -30718,19 +30722,25 @@
         <v>1271</v>
       </c>
       <c r="C513" t="s">
-        <v>1554</v>
+        <v>1780</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1850</v>
       </c>
       <c r="F513" s="2">
-        <v>46118</v>
+        <v>46175</v>
       </c>
       <c r="G513" t="s">
         <v>1914</v>
       </c>
       <c r="H513" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I513" t="s">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="J513" t="s">
         <v>2140</v>
@@ -30750,22 +30760,22 @@
         <v>1272</v>
       </c>
       <c r="C514" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="F514" s="2">
-        <v>45898</v>
+        <v>46118</v>
       </c>
       <c r="G514" t="s">
         <v>1914</v>
       </c>
       <c r="H514" t="s">
-        <v>1966</v>
+        <v>1924</v>
       </c>
       <c r="I514" t="s">
-        <v>1987</v>
+        <v>2017</v>
       </c>
       <c r="J514" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K514" t="s">
         <v>2651</v>
@@ -30782,25 +30792,22 @@
         <v>1273</v>
       </c>
       <c r="C515" t="s">
-        <v>1641</v>
-      </c>
-      <c r="D515" t="s">
-        <v>1763</v>
+        <v>1549</v>
       </c>
       <c r="F515" s="2">
-        <v>45812</v>
+        <v>45898</v>
       </c>
       <c r="G515" t="s">
         <v>1914</v>
       </c>
       <c r="H515" t="s">
-        <v>1921</v>
+        <v>1966</v>
       </c>
       <c r="I515" t="s">
-        <v>2074</v>
+        <v>1987</v>
       </c>
       <c r="J515" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K515" t="s">
         <v>2652</v>
@@ -30817,19 +30824,22 @@
         <v>1274</v>
       </c>
       <c r="C516" t="s">
-        <v>1730</v>
+        <v>1641</v>
+      </c>
+      <c r="D516" t="s">
+        <v>1763</v>
       </c>
       <c r="F516" s="2">
-        <v>45923</v>
+        <v>45812</v>
       </c>
       <c r="G516" t="s">
         <v>1914</v>
       </c>
       <c r="H516" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="I516" t="s">
-        <v>2118</v>
+        <v>2074</v>
       </c>
       <c r="J516" t="s">
         <v>2140</v>
@@ -30849,19 +30859,19 @@
         <v>1275</v>
       </c>
       <c r="C517" t="s">
-        <v>1799</v>
+        <v>1730</v>
       </c>
       <c r="F517" s="2">
-        <v>45994</v>
+        <v>45923</v>
       </c>
       <c r="G517" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H517" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="I517" t="s">
-        <v>2037</v>
+        <v>2118</v>
       </c>
       <c r="J517" t="s">
         <v>2140</v>
@@ -30881,19 +30891,19 @@
         <v>1276</v>
       </c>
       <c r="C518" t="s">
-        <v>1713</v>
+        <v>1799</v>
       </c>
       <c r="F518" s="2">
-        <v>46090</v>
+        <v>45994</v>
       </c>
       <c r="G518" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H518" t="s">
         <v>1922</v>
       </c>
       <c r="I518" t="s">
-        <v>2048</v>
+        <v>2037</v>
       </c>
       <c r="J518" t="s">
         <v>2140</v>
@@ -30913,19 +30923,19 @@
         <v>1277</v>
       </c>
       <c r="C519" t="s">
-        <v>1800</v>
+        <v>1713</v>
       </c>
       <c r="F519" s="2">
-        <v>46188</v>
+        <v>46090</v>
       </c>
       <c r="G519" t="s">
         <v>1914</v>
       </c>
       <c r="H519" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I519" t="s">
-        <v>2018</v>
+        <v>2048</v>
       </c>
       <c r="J519" t="s">
         <v>2140</v>
@@ -30945,19 +30955,19 @@
         <v>1278</v>
       </c>
       <c r="C520" t="s">
-        <v>1567</v>
+        <v>1800</v>
       </c>
       <c r="F520" s="2">
-        <v>45996</v>
+        <v>46188</v>
       </c>
       <c r="G520" t="s">
         <v>1914</v>
       </c>
       <c r="H520" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I520" t="s">
-        <v>2119</v>
+        <v>2018</v>
       </c>
       <c r="J520" t="s">
         <v>2140</v>
@@ -30977,19 +30987,19 @@
         <v>1279</v>
       </c>
       <c r="C521" t="s">
-        <v>1801</v>
+        <v>1567</v>
       </c>
       <c r="F521" s="2">
-        <v>45673</v>
+        <v>45996</v>
       </c>
       <c r="G521" t="s">
         <v>1914</v>
       </c>
       <c r="H521" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I521" t="s">
-        <v>2010</v>
+        <v>2119</v>
       </c>
       <c r="J521" t="s">
         <v>2140</v>
@@ -31009,19 +31019,19 @@
         <v>1280</v>
       </c>
       <c r="C522" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="F522" s="2">
-        <v>45919</v>
+        <v>45673</v>
       </c>
       <c r="G522" t="s">
         <v>1914</v>
       </c>
       <c r="H522" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I522" t="s">
-        <v>1994</v>
+        <v>2010</v>
       </c>
       <c r="J522" t="s">
         <v>2140</v>
@@ -31041,19 +31051,19 @@
         <v>1281</v>
       </c>
       <c r="C523" t="s">
-        <v>1692</v>
+        <v>1802</v>
       </c>
       <c r="F523" s="2">
-        <v>45946</v>
+        <v>45919</v>
       </c>
       <c r="G523" t="s">
         <v>1914</v>
       </c>
       <c r="H523" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I523" t="s">
-        <v>1986</v>
+        <v>1994</v>
       </c>
       <c r="J523" t="s">
         <v>2140</v>
@@ -31073,10 +31083,10 @@
         <v>1282</v>
       </c>
       <c r="C524" t="s">
-        <v>1602</v>
+        <v>1692</v>
       </c>
       <c r="F524" s="2">
-        <v>45838</v>
+        <v>45946</v>
       </c>
       <c r="G524" t="s">
         <v>1914</v>
@@ -31085,7 +31095,7 @@
         <v>1921</v>
       </c>
       <c r="I524" t="s">
-        <v>2097</v>
+        <v>1986</v>
       </c>
       <c r="J524" t="s">
         <v>2140</v>
@@ -31105,25 +31115,19 @@
         <v>1283</v>
       </c>
       <c r="C525" t="s">
-        <v>1803</v>
-      </c>
-      <c r="D525" t="s">
-        <v>1686</v>
-      </c>
-      <c r="E525" t="s">
-        <v>1686</v>
+        <v>1602</v>
       </c>
       <c r="F525" s="2">
-        <v>45994</v>
+        <v>45838</v>
       </c>
       <c r="G525" t="s">
         <v>1914</v>
       </c>
       <c r="H525" t="s">
-        <v>1940</v>
+        <v>1921</v>
       </c>
       <c r="I525" t="s">
-        <v>1974</v>
+        <v>2097</v>
       </c>
       <c r="J525" t="s">
         <v>2140</v>
@@ -31143,25 +31147,25 @@
         <v>1284</v>
       </c>
       <c r="C526" t="s">
-        <v>1526</v>
+        <v>1803</v>
       </c>
       <c r="D526" t="s">
-        <v>1511</v>
+        <v>1686</v>
       </c>
       <c r="E526" t="s">
-        <v>1911</v>
+        <v>1686</v>
       </c>
       <c r="F526" s="2">
-        <v>45772</v>
+        <v>45994</v>
       </c>
       <c r="G526" t="s">
         <v>1914</v>
       </c>
       <c r="H526" t="s">
-        <v>1950</v>
+        <v>1940</v>
       </c>
       <c r="I526" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="J526" t="s">
         <v>2140</v>
@@ -31181,19 +31185,25 @@
         <v>1285</v>
       </c>
       <c r="C527" t="s">
-        <v>1804</v>
+        <v>1526</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E527" t="s">
+        <v>1911</v>
       </c>
       <c r="F527" s="2">
-        <v>45989</v>
+        <v>45772</v>
       </c>
       <c r="G527" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H527" t="s">
-        <v>1924</v>
+        <v>1950</v>
       </c>
       <c r="I527" t="s">
-        <v>2120</v>
+        <v>1976</v>
       </c>
       <c r="J527" t="s">
         <v>2140</v>
@@ -31213,22 +31223,19 @@
         <v>1286</v>
       </c>
       <c r="C528" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D528" t="s">
-        <v>1881</v>
+        <v>1804</v>
       </c>
       <c r="F528" s="2">
-        <v>46147</v>
+        <v>45989</v>
       </c>
       <c r="G528" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H528" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="I528" t="s">
-        <v>1980</v>
+        <v>2120</v>
       </c>
       <c r="J528" t="s">
         <v>2140</v>
@@ -31248,19 +31255,22 @@
         <v>1287</v>
       </c>
       <c r="C529" t="s">
-        <v>1605</v>
+        <v>1518</v>
+      </c>
+      <c r="D529" t="s">
+        <v>1881</v>
       </c>
       <c r="F529" s="2">
-        <v>46184</v>
+        <v>46147</v>
       </c>
       <c r="G529" t="s">
         <v>1914</v>
       </c>
       <c r="H529" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="I529" t="s">
-        <v>2016</v>
+        <v>1980</v>
       </c>
       <c r="J529" t="s">
         <v>2140</v>
@@ -31280,19 +31290,19 @@
         <v>1288</v>
       </c>
       <c r="C530" t="s">
-        <v>1688</v>
+        <v>1605</v>
       </c>
       <c r="F530" s="2">
-        <v>46049</v>
+        <v>46184</v>
       </c>
       <c r="G530" t="s">
         <v>1914</v>
       </c>
       <c r="H530" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I530" t="s">
-        <v>1978</v>
+        <v>2016</v>
       </c>
       <c r="J530" t="s">
         <v>2140</v>
@@ -31312,25 +31322,19 @@
         <v>1289</v>
       </c>
       <c r="C531" t="s">
-        <v>1805</v>
-      </c>
-      <c r="D531" t="s">
-        <v>1887</v>
-      </c>
-      <c r="E531" t="s">
-        <v>1887</v>
+        <v>1688</v>
       </c>
       <c r="F531" s="2">
-        <v>46227</v>
+        <v>46049</v>
       </c>
       <c r="G531" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H531" t="s">
-        <v>1939</v>
+        <v>1921</v>
       </c>
       <c r="I531" t="s">
-        <v>1999</v>
+        <v>1978</v>
       </c>
       <c r="J531" t="s">
         <v>2140</v>
@@ -31350,25 +31354,25 @@
         <v>1290</v>
       </c>
       <c r="C532" t="s">
-        <v>1632</v>
+        <v>1805</v>
       </c>
       <c r="D532" t="s">
-        <v>1566</v>
+        <v>1887</v>
       </c>
       <c r="E532" t="s">
-        <v>1824</v>
+        <v>1887</v>
       </c>
       <c r="F532" s="2">
-        <v>45924</v>
+        <v>46227</v>
       </c>
       <c r="G532" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H532" t="s">
-        <v>1921</v>
+        <v>1939</v>
       </c>
       <c r="I532" t="s">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="J532" t="s">
         <v>2140</v>
@@ -31388,10 +31392,16 @@
         <v>1291</v>
       </c>
       <c r="C533" t="s">
-        <v>1636</v>
+        <v>1632</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E533" t="s">
+        <v>1824</v>
       </c>
       <c r="F533" s="2">
-        <v>45891</v>
+        <v>45924</v>
       </c>
       <c r="G533" t="s">
         <v>1914</v>
@@ -31400,7 +31410,7 @@
         <v>1921</v>
       </c>
       <c r="I533" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="J533" t="s">
         <v>2140</v>
@@ -31420,19 +31430,19 @@
         <v>1292</v>
       </c>
       <c r="C534" t="s">
-        <v>1692</v>
+        <v>1636</v>
       </c>
       <c r="F534" s="2">
-        <v>45812</v>
+        <v>45891</v>
       </c>
       <c r="G534" t="s">
         <v>1914</v>
       </c>
       <c r="H534" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I534" t="s">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="J534" t="s">
         <v>2140</v>
@@ -31452,28 +31462,22 @@
         <v>1293</v>
       </c>
       <c r="C535" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D535" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E535" t="s">
-        <v>1657</v>
+        <v>1692</v>
       </c>
       <c r="F535" s="2">
-        <v>46048</v>
+        <v>45812</v>
       </c>
       <c r="G535" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H535" t="s">
-        <v>1967</v>
+        <v>1922</v>
       </c>
       <c r="I535" t="s">
-        <v>2121</v>
+        <v>2009</v>
       </c>
       <c r="J535" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K535" t="s">
         <v>2672</v>
@@ -31490,25 +31494,25 @@
         <v>1294</v>
       </c>
       <c r="C536" t="s">
-        <v>1601</v>
+        <v>1559</v>
       </c>
       <c r="D536" t="s">
-        <v>1739</v>
+        <v>1657</v>
       </c>
       <c r="E536" t="s">
-        <v>1545</v>
+        <v>1657</v>
       </c>
       <c r="F536" s="2">
-        <v>45908</v>
+        <v>46048</v>
       </c>
       <c r="G536" t="s">
         <v>1915</v>
       </c>
       <c r="H536" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="I536" t="s">
-        <v>2049</v>
+        <v>2121</v>
       </c>
       <c r="J536" t="s">
         <v>2141</v>
@@ -31528,22 +31532,28 @@
         <v>1295</v>
       </c>
       <c r="C537" t="s">
-        <v>1737</v>
+        <v>1601</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E537" t="s">
+        <v>1545</v>
       </c>
       <c r="F537" s="2">
-        <v>46113</v>
+        <v>45908</v>
       </c>
       <c r="G537" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H537" t="s">
-        <v>1921</v>
+        <v>1968</v>
       </c>
       <c r="I537" t="s">
-        <v>2007</v>
+        <v>2049</v>
       </c>
       <c r="J537" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K537" t="s">
         <v>2674</v>
@@ -31560,19 +31570,19 @@
         <v>1296</v>
       </c>
       <c r="C538" t="s">
-        <v>1757</v>
+        <v>1737</v>
       </c>
       <c r="F538" s="2">
-        <v>45693</v>
+        <v>46113</v>
       </c>
       <c r="G538" t="s">
         <v>1914</v>
       </c>
       <c r="H538" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I538" t="s">
-        <v>1976</v>
+        <v>2007</v>
       </c>
       <c r="J538" t="s">
         <v>2140</v>
@@ -31592,22 +31602,22 @@
         <v>1297</v>
       </c>
       <c r="C539" t="s">
-        <v>1806</v>
+        <v>1757</v>
       </c>
       <c r="F539" s="2">
-        <v>45735</v>
+        <v>45693</v>
       </c>
       <c r="G539" t="s">
         <v>1914</v>
       </c>
       <c r="H539" t="s">
-        <v>1936</v>
+        <v>1922</v>
       </c>
       <c r="I539" t="s">
-        <v>2122</v>
+        <v>1976</v>
       </c>
       <c r="J539" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K539" t="s">
         <v>2676</v>
@@ -31624,22 +31634,22 @@
         <v>1298</v>
       </c>
       <c r="C540" t="s">
-        <v>1795</v>
+        <v>1806</v>
       </c>
       <c r="F540" s="2">
-        <v>46189</v>
+        <v>45735</v>
       </c>
       <c r="G540" t="s">
         <v>1914</v>
       </c>
       <c r="H540" t="s">
-        <v>1921</v>
+        <v>1936</v>
       </c>
       <c r="I540" t="s">
-        <v>2005</v>
+        <v>2122</v>
       </c>
       <c r="J540" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K540" t="s">
         <v>2677</v>
@@ -31656,25 +31666,19 @@
         <v>1299</v>
       </c>
       <c r="C541" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D541" t="s">
-        <v>1828</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1828</v>
+        <v>1795</v>
       </c>
       <c r="F541" s="2">
-        <v>46118</v>
+        <v>46189</v>
       </c>
       <c r="G541" t="s">
         <v>1914</v>
       </c>
       <c r="H541" t="s">
-        <v>1941</v>
+        <v>1921</v>
       </c>
       <c r="I541" t="s">
-        <v>2028</v>
+        <v>2005</v>
       </c>
       <c r="J541" t="s">
         <v>2140</v>
@@ -31694,19 +31698,25 @@
         <v>1300</v>
       </c>
       <c r="C542" t="s">
-        <v>1764</v>
+        <v>1535</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E542" t="s">
+        <v>1828</v>
       </c>
       <c r="F542" s="2">
-        <v>45812</v>
+        <v>46118</v>
       </c>
       <c r="G542" t="s">
         <v>1914</v>
       </c>
       <c r="H542" t="s">
-        <v>1922</v>
+        <v>1941</v>
       </c>
       <c r="I542" t="s">
-        <v>2123</v>
+        <v>2028</v>
       </c>
       <c r="J542" t="s">
         <v>2140</v>
@@ -31726,22 +31736,22 @@
         <v>1301</v>
       </c>
       <c r="C543" t="s">
-        <v>1530</v>
+        <v>1764</v>
       </c>
       <c r="F543" s="2">
-        <v>46204</v>
+        <v>45812</v>
       </c>
       <c r="G543" t="s">
         <v>1914</v>
       </c>
       <c r="H543" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I543" t="s">
-        <v>2009</v>
+        <v>2123</v>
       </c>
       <c r="J543" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K543" t="s">
         <v>2680</v>
@@ -31758,25 +31768,22 @@
         <v>1302</v>
       </c>
       <c r="C544" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1676</v>
+        <v>1530</v>
       </c>
       <c r="F544" s="2">
-        <v>45709</v>
+        <v>46204</v>
       </c>
       <c r="G544" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H544" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="I544" t="s">
-        <v>2071</v>
+        <v>2009</v>
       </c>
       <c r="J544" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K544" t="s">
         <v>2681</v>
@@ -31793,19 +31800,22 @@
         <v>1303</v>
       </c>
       <c r="C545" t="s">
-        <v>1604</v>
+        <v>1661</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1676</v>
       </c>
       <c r="F545" s="2">
-        <v>46148</v>
+        <v>45709</v>
       </c>
       <c r="G545" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="H545" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="I545" t="s">
-        <v>2010</v>
+        <v>2071</v>
       </c>
       <c r="J545" t="s">
         <v>2140</v>
@@ -31825,22 +31835,19 @@
         <v>1304</v>
       </c>
       <c r="C546" t="s">
-        <v>1807</v>
-      </c>
-      <c r="D546" t="s">
-        <v>1513</v>
+        <v>1604</v>
       </c>
       <c r="F546" s="2">
-        <v>46211</v>
+        <v>46148</v>
       </c>
       <c r="G546" t="s">
         <v>1914</v>
       </c>
       <c r="H546" t="s">
-        <v>1930</v>
+        <v>1921</v>
       </c>
       <c r="I546" t="s">
-        <v>2124</v>
+        <v>2010</v>
       </c>
       <c r="J546" t="s">
         <v>2140</v>
@@ -31860,19 +31867,22 @@
         <v>1305</v>
       </c>
       <c r="C547" t="s">
-        <v>1749</v>
+        <v>1807</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1513</v>
       </c>
       <c r="F547" s="2">
-        <v>46044</v>
+        <v>46211</v>
       </c>
       <c r="G547" t="s">
         <v>1914</v>
       </c>
       <c r="H547" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="I547" t="s">
-        <v>2027</v>
+        <v>2124</v>
       </c>
       <c r="J547" t="s">
         <v>2140</v>
@@ -31892,19 +31902,19 @@
         <v>1306</v>
       </c>
       <c r="C548" t="s">
-        <v>1519</v>
+        <v>1749</v>
       </c>
       <c r="F548" s="2">
-        <v>45994</v>
+        <v>46044</v>
       </c>
       <c r="G548" t="s">
         <v>1914</v>
       </c>
       <c r="H548" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="I548" t="s">
-        <v>2011</v>
+        <v>2027</v>
       </c>
       <c r="J548" t="s">
         <v>2140</v>
@@ -31924,28 +31934,22 @@
         <v>1307</v>
       </c>
       <c r="C549" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1701</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1705</v>
+        <v>1519</v>
       </c>
       <c r="F549" s="2">
-        <v>46034</v>
+        <v>45994</v>
       </c>
       <c r="G549" t="s">
         <v>1914</v>
       </c>
       <c r="H549" t="s">
-        <v>1927</v>
+        <v>1919</v>
       </c>
       <c r="I549" t="s">
-        <v>1990</v>
+        <v>2011</v>
       </c>
       <c r="J549" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K549" t="s">
         <v>2686</v>
@@ -31962,25 +31966,25 @@
         <v>1308</v>
       </c>
       <c r="C550" t="s">
-        <v>1642</v>
+        <v>1808</v>
       </c>
       <c r="D550" t="s">
-        <v>1764</v>
+        <v>1701</v>
       </c>
       <c r="E550" t="s">
-        <v>1764</v>
+        <v>1705</v>
       </c>
       <c r="F550" s="2">
-        <v>45811</v>
+        <v>46034</v>
       </c>
       <c r="G550" t="s">
         <v>1914</v>
       </c>
       <c r="H550" t="s">
-        <v>1941</v>
+        <v>1927</v>
       </c>
       <c r="I550" t="s">
-        <v>2095</v>
+        <v>1990</v>
       </c>
       <c r="J550" t="s">
         <v>2141</v>
@@ -32000,19 +32004,25 @@
         <v>1309</v>
       </c>
       <c r="C551" t="s">
-        <v>1541</v>
+        <v>1642</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E551" t="s">
+        <v>1764</v>
       </c>
       <c r="F551" s="2">
-        <v>46167</v>
+        <v>45811</v>
       </c>
       <c r="G551" t="s">
         <v>1914</v>
       </c>
       <c r="H551" t="s">
-        <v>1921</v>
+        <v>1941</v>
       </c>
       <c r="I551" t="s">
-        <v>1986</v>
+        <v>2095</v>
       </c>
       <c r="J551" t="s">
         <v>2141</v>
@@ -32032,22 +32042,22 @@
         <v>1310</v>
       </c>
       <c r="C552" t="s">
-        <v>1676</v>
+        <v>1541</v>
       </c>
       <c r="F552" s="2">
-        <v>45680</v>
+        <v>46167</v>
       </c>
       <c r="G552" t="s">
         <v>1914</v>
       </c>
       <c r="H552" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I552" t="s">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="J552" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K552" t="s">
         <v>2689</v>
@@ -32064,10 +32074,10 @@
         <v>1311</v>
       </c>
       <c r="C553" t="s">
-        <v>1743</v>
+        <v>1676</v>
       </c>
       <c r="F553" s="2">
-        <v>45754</v>
+        <v>45680</v>
       </c>
       <c r="G553" t="s">
         <v>1914</v>
@@ -32076,7 +32086,7 @@
         <v>1922</v>
       </c>
       <c r="I553" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="J553" t="s">
         <v>2140</v>
@@ -32096,19 +32106,19 @@
         <v>1312</v>
       </c>
       <c r="C554" t="s">
-        <v>1561</v>
+        <v>1743</v>
       </c>
       <c r="F554" s="2">
-        <v>46160</v>
+        <v>45754</v>
       </c>
       <c r="G554" t="s">
         <v>1914</v>
       </c>
       <c r="H554" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I554" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="J554" t="s">
         <v>2140</v>
@@ -32128,22 +32138,22 @@
         <v>1313</v>
       </c>
       <c r="C555" t="s">
-        <v>1735</v>
+        <v>1561</v>
       </c>
       <c r="F555" s="2">
-        <v>45854</v>
+        <v>46160</v>
       </c>
       <c r="G555" t="s">
         <v>1914</v>
       </c>
       <c r="H555" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I555" t="s">
-        <v>1978</v>
+        <v>2016</v>
       </c>
       <c r="J555" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K555" t="s">
         <v>2692</v>
@@ -32160,25 +32170,22 @@
         <v>1314</v>
       </c>
       <c r="C556" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1888</v>
+        <v>1735</v>
       </c>
       <c r="F556" s="2">
-        <v>45782</v>
+        <v>45854</v>
       </c>
       <c r="G556" t="s">
         <v>1914</v>
       </c>
       <c r="H556" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="I556" t="s">
-        <v>2029</v>
+        <v>1978</v>
       </c>
       <c r="J556" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K556" t="s">
         <v>2693</v>
@@ -32195,10 +32202,13 @@
         <v>1315</v>
       </c>
       <c r="C557" t="s">
-        <v>1514</v>
+        <v>1765</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1888</v>
       </c>
       <c r="F557" s="2">
-        <v>46010</v>
+        <v>45782</v>
       </c>
       <c r="G557" t="s">
         <v>1914</v>
@@ -32207,7 +32217,7 @@
         <v>1924</v>
       </c>
       <c r="I557" t="s">
-        <v>2039</v>
+        <v>2029</v>
       </c>
       <c r="J557" t="s">
         <v>2140</v>
@@ -32227,10 +32237,10 @@
         <v>1316</v>
       </c>
       <c r="C558" t="s">
-        <v>1642</v>
+        <v>1514</v>
       </c>
       <c r="F558" s="2">
-        <v>45812</v>
+        <v>46010</v>
       </c>
       <c r="G558" t="s">
         <v>1914</v>
@@ -32239,7 +32249,7 @@
         <v>1924</v>
       </c>
       <c r="I558" t="s">
-        <v>2095</v>
+        <v>2039</v>
       </c>
       <c r="J558" t="s">
         <v>2140</v>
@@ -32259,28 +32269,22 @@
         <v>1317</v>
       </c>
       <c r="C559" t="s">
-        <v>1674</v>
-      </c>
-      <c r="D559" t="s">
-        <v>1603</v>
-      </c>
-      <c r="E559" t="s">
-        <v>1603</v>
+        <v>1642</v>
       </c>
       <c r="F559" s="2">
-        <v>45884</v>
+        <v>45812</v>
       </c>
       <c r="G559" t="s">
         <v>1914</v>
       </c>
       <c r="H559" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I559" t="s">
-        <v>2060</v>
+        <v>2095</v>
       </c>
       <c r="J559" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K559" t="s">
         <v>2696</v>
@@ -32297,22 +32301,28 @@
         <v>1318</v>
       </c>
       <c r="C560" t="s">
-        <v>1802</v>
+        <v>1674</v>
+      </c>
+      <c r="D560" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E560" t="s">
+        <v>1603</v>
       </c>
       <c r="F560" s="2">
-        <v>45995</v>
+        <v>45884</v>
       </c>
       <c r="G560" t="s">
         <v>1914</v>
       </c>
       <c r="H560" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I560" t="s">
-        <v>2007</v>
+        <v>2060</v>
       </c>
       <c r="J560" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K560" t="s">
         <v>2697</v>
@@ -32329,25 +32339,19 @@
         <v>1319</v>
       </c>
       <c r="C561" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D561" t="s">
-        <v>1675</v>
-      </c>
-      <c r="E561" t="s">
-        <v>1675</v>
+        <v>1802</v>
       </c>
       <c r="F561" s="2">
-        <v>46167</v>
+        <v>45995</v>
       </c>
       <c r="G561" t="s">
         <v>1914</v>
       </c>
       <c r="H561" t="s">
-        <v>1930</v>
+        <v>1921</v>
       </c>
       <c r="I561" t="s">
-        <v>2123</v>
+        <v>2007</v>
       </c>
       <c r="J561" t="s">
         <v>2140</v>
@@ -32367,22 +32371,28 @@
         <v>1320</v>
       </c>
       <c r="C562" t="s">
-        <v>1708</v>
+        <v>1611</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E562" t="s">
+        <v>1675</v>
       </c>
       <c r="F562" s="2">
-        <v>45704</v>
+        <v>46167</v>
       </c>
       <c r="G562" t="s">
         <v>1914</v>
       </c>
       <c r="H562" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="I562" t="s">
-        <v>1977</v>
+        <v>2123</v>
       </c>
       <c r="J562" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K562" t="s">
         <v>2699</v>
@@ -32399,28 +32409,22 @@
         <v>1321</v>
       </c>
       <c r="C563" t="s">
-        <v>1727</v>
-      </c>
-      <c r="D563" t="s">
-        <v>1889</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1889</v>
+        <v>1708</v>
       </c>
       <c r="F563" s="2">
-        <v>46181</v>
+        <v>45704</v>
       </c>
       <c r="G563" t="s">
         <v>1914</v>
       </c>
       <c r="H563" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I563" t="s">
-        <v>2046</v>
+        <v>1977</v>
       </c>
       <c r="J563" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K563" t="s">
         <v>2700</v>
@@ -32437,19 +32441,25 @@
         <v>1322</v>
       </c>
       <c r="C564" t="s">
-        <v>1792</v>
+        <v>1727</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E564" t="s">
+        <v>1889</v>
       </c>
       <c r="F564" s="2">
-        <v>46204</v>
+        <v>46181</v>
       </c>
       <c r="G564" t="s">
         <v>1914</v>
       </c>
       <c r="H564" t="s">
-        <v>1940</v>
+        <v>1921</v>
       </c>
       <c r="I564" t="s">
-        <v>2027</v>
+        <v>2046</v>
       </c>
       <c r="J564" t="s">
         <v>2140</v>
@@ -32469,19 +32479,19 @@
         <v>1323</v>
       </c>
       <c r="C565" t="s">
-        <v>1730</v>
+        <v>1792</v>
       </c>
       <c r="F565" s="2">
-        <v>45853</v>
+        <v>46204</v>
       </c>
       <c r="G565" t="s">
         <v>1914</v>
       </c>
       <c r="H565" t="s">
-        <v>1924</v>
+        <v>1940</v>
       </c>
       <c r="I565" t="s">
-        <v>2074</v>
+        <v>2027</v>
       </c>
       <c r="J565" t="s">
         <v>2140</v>
@@ -32501,19 +32511,19 @@
         <v>1324</v>
       </c>
       <c r="C566" t="s">
-        <v>1516</v>
+        <v>1730</v>
       </c>
       <c r="F566" s="2">
-        <v>45705</v>
+        <v>45853</v>
       </c>
       <c r="G566" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H566" t="s">
         <v>1924</v>
       </c>
       <c r="I566" t="s">
-        <v>2125</v>
+        <v>2074</v>
       </c>
       <c r="J566" t="s">
         <v>2140</v>
@@ -32533,19 +32543,19 @@
         <v>1325</v>
       </c>
       <c r="C567" t="s">
-        <v>1667</v>
+        <v>1516</v>
       </c>
       <c r="F567" s="2">
-        <v>45862</v>
+        <v>45705</v>
       </c>
       <c r="G567" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="H567" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I567" t="s">
-        <v>2009</v>
+        <v>2125</v>
       </c>
       <c r="J567" t="s">
         <v>2140</v>
@@ -32565,25 +32575,19 @@
         <v>1326</v>
       </c>
       <c r="C568" t="s">
-        <v>1517</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1864</v>
-      </c>
-      <c r="E568" t="s">
-        <v>1842</v>
+        <v>1667</v>
       </c>
       <c r="F568" s="2">
-        <v>45992</v>
+        <v>45862</v>
       </c>
       <c r="G568" t="s">
         <v>1914</v>
       </c>
       <c r="H568" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="I568" t="s">
-        <v>1981</v>
+        <v>2009</v>
       </c>
       <c r="J568" t="s">
         <v>2140</v>
@@ -32603,19 +32607,25 @@
         <v>1327</v>
       </c>
       <c r="C569" t="s">
-        <v>1809</v>
+        <v>1517</v>
+      </c>
+      <c r="D569" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E569" t="s">
+        <v>1842</v>
       </c>
       <c r="F569" s="2">
-        <v>46010</v>
+        <v>45992</v>
       </c>
       <c r="G569" t="s">
         <v>1914</v>
       </c>
       <c r="H569" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
       <c r="I569" t="s">
-        <v>2021</v>
+        <v>1981</v>
       </c>
       <c r="J569" t="s">
         <v>2140</v>
@@ -32635,22 +32645,19 @@
         <v>1328</v>
       </c>
       <c r="C570" t="s">
-        <v>1810</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1599</v>
+        <v>1809</v>
       </c>
       <c r="F570" s="2">
-        <v>45972</v>
+        <v>46010</v>
       </c>
       <c r="G570" t="s">
         <v>1914</v>
       </c>
       <c r="H570" t="s">
-        <v>1943</v>
+        <v>1921</v>
       </c>
       <c r="I570" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="J570" t="s">
         <v>2140</v>
@@ -32670,19 +32677,22 @@
         <v>1329</v>
       </c>
       <c r="C571" t="s">
-        <v>1803</v>
+        <v>1810</v>
+      </c>
+      <c r="D571" t="s">
+        <v>1599</v>
       </c>
       <c r="F571" s="2">
-        <v>45849</v>
+        <v>45972</v>
       </c>
       <c r="G571" t="s">
         <v>1914</v>
       </c>
       <c r="H571" t="s">
-        <v>1922</v>
+        <v>1943</v>
       </c>
       <c r="I571" t="s">
-        <v>1974</v>
+        <v>2018</v>
       </c>
       <c r="J571" t="s">
         <v>2140</v>
@@ -32702,10 +32712,10 @@
         <v>1330</v>
       </c>
       <c r="C572" t="s">
-        <v>1568</v>
+        <v>1803</v>
       </c>
       <c r="F572" s="2">
-        <v>45965</v>
+        <v>45849</v>
       </c>
       <c r="G572" t="s">
         <v>1914</v>
@@ -32714,10 +32724,10 @@
         <v>1922</v>
       </c>
       <c r="I572" t="s">
-        <v>2097</v>
+        <v>1974</v>
       </c>
       <c r="J572" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K572" t="s">
         <v>2709</v>
@@ -32734,10 +32744,10 @@
         <v>1331</v>
       </c>
       <c r="C573" t="s">
-        <v>1792</v>
+        <v>1568</v>
       </c>
       <c r="F573" s="2">
-        <v>46224</v>
+        <v>45965</v>
       </c>
       <c r="G573" t="s">
         <v>1914</v>
@@ -32746,10 +32756,10 @@
         <v>1922</v>
       </c>
       <c r="I573" t="s">
-        <v>2007</v>
+        <v>2097</v>
       </c>
       <c r="J573" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K573" t="s">
         <v>2710</v>
@@ -32766,19 +32776,19 @@
         <v>1332</v>
       </c>
       <c r="C574" t="s">
-        <v>1524</v>
+        <v>1792</v>
       </c>
       <c r="F574" s="2">
-        <v>45811</v>
+        <v>46224</v>
       </c>
       <c r="G574" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H574" t="s">
-        <v>1938</v>
+        <v>1922</v>
       </c>
       <c r="I574" t="s">
-        <v>1978</v>
+        <v>2007</v>
       </c>
       <c r="J574" t="s">
         <v>2140</v>
@@ -32798,19 +32808,19 @@
         <v>1333</v>
       </c>
       <c r="C575" t="s">
-        <v>1811</v>
+        <v>1524</v>
       </c>
       <c r="F575" s="2">
         <v>45811</v>
       </c>
       <c r="G575" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H575" t="s">
-        <v>1922</v>
+        <v>1938</v>
       </c>
       <c r="I575" t="s">
-        <v>2060</v>
+        <v>1978</v>
       </c>
       <c r="J575" t="s">
         <v>2140</v>
@@ -32830,25 +32840,19 @@
         <v>1334</v>
       </c>
       <c r="C576" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D576" t="s">
-        <v>1863</v>
-      </c>
-      <c r="E576" t="s">
-        <v>1903</v>
+        <v>1777</v>
       </c>
       <c r="F576" s="2">
-        <v>45734</v>
+        <v>46232</v>
       </c>
       <c r="G576" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H576" t="s">
-        <v>1948</v>
+        <v>1921</v>
       </c>
       <c r="I576" t="s">
-        <v>2068</v>
+        <v>2032</v>
       </c>
       <c r="J576" t="s">
         <v>2140</v>
@@ -32868,25 +32872,19 @@
         <v>1335</v>
       </c>
       <c r="C577" t="s">
-        <v>1621</v>
-      </c>
-      <c r="D577" t="s">
-        <v>1890</v>
-      </c>
-      <c r="E577" t="s">
-        <v>1902</v>
+        <v>1811</v>
       </c>
       <c r="F577" s="2">
-        <v>45838</v>
+        <v>45811</v>
       </c>
       <c r="G577" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H577" t="s">
-        <v>1931</v>
+        <v>1922</v>
       </c>
       <c r="I577" t="s">
-        <v>2126</v>
+        <v>2060</v>
       </c>
       <c r="J577" t="s">
         <v>2140</v>
@@ -32906,22 +32904,28 @@
         <v>1336</v>
       </c>
       <c r="C578" t="s">
-        <v>1812</v>
+        <v>1664</v>
+      </c>
+      <c r="D578" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E578" t="s">
+        <v>1903</v>
       </c>
       <c r="F578" s="2">
-        <v>45684</v>
+        <v>45734</v>
       </c>
       <c r="G578" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="H578" t="s">
-        <v>1918</v>
+        <v>1948</v>
       </c>
       <c r="I578" t="s">
-        <v>2019</v>
+        <v>2068</v>
       </c>
       <c r="J578" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K578" t="s">
         <v>2715</v>
@@ -32938,19 +32942,25 @@
         <v>1337</v>
       </c>
       <c r="C579" t="s">
-        <v>1813</v>
+        <v>1621</v>
+      </c>
+      <c r="D579" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E579" t="s">
+        <v>1902</v>
       </c>
       <c r="F579" s="2">
-        <v>46092</v>
+        <v>45838</v>
       </c>
       <c r="G579" t="s">
         <v>1914</v>
       </c>
       <c r="H579" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="I579" t="s">
-        <v>2035</v>
+        <v>2126</v>
       </c>
       <c r="J579" t="s">
         <v>2140</v>
@@ -32970,25 +32980,19 @@
         <v>1338</v>
       </c>
       <c r="C580" t="s">
-        <v>1814</v>
-      </c>
-      <c r="D580" t="s">
-        <v>1891</v>
-      </c>
-      <c r="E580" t="s">
-        <v>1560</v>
+        <v>1812</v>
       </c>
       <c r="F580" s="2">
-        <v>45693</v>
+        <v>45684</v>
       </c>
       <c r="G580" t="s">
         <v>1914</v>
       </c>
       <c r="H580" t="s">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="I580" t="s">
-        <v>1994</v>
+        <v>2019</v>
       </c>
       <c r="J580" t="s">
         <v>2141</v>
@@ -33008,19 +33012,19 @@
         <v>1339</v>
       </c>
       <c r="C581" t="s">
-        <v>1705</v>
+        <v>1813</v>
       </c>
       <c r="F581" s="2">
-        <v>45994</v>
+        <v>46092</v>
       </c>
       <c r="G581" t="s">
         <v>1914</v>
       </c>
       <c r="H581" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="I581" t="s">
-        <v>2055</v>
+        <v>2035</v>
       </c>
       <c r="J581" t="s">
         <v>2140</v>
@@ -33040,25 +33044,25 @@
         <v>1340</v>
       </c>
       <c r="C582" t="s">
-        <v>1646</v>
+        <v>1814</v>
       </c>
       <c r="D582" t="s">
-        <v>1639</v>
+        <v>1891</v>
       </c>
       <c r="E582" t="s">
-        <v>1549</v>
+        <v>1560</v>
       </c>
       <c r="F582" s="2">
-        <v>45923</v>
+        <v>45693</v>
       </c>
       <c r="G582" t="s">
         <v>1914</v>
       </c>
       <c r="H582" t="s">
-        <v>1969</v>
+        <v>1922</v>
       </c>
       <c r="I582" t="s">
-        <v>2118</v>
+        <v>1994</v>
       </c>
       <c r="J582" t="s">
         <v>2141</v>
@@ -33078,19 +33082,19 @@
         <v>1341</v>
       </c>
       <c r="C583" t="s">
-        <v>1815</v>
+        <v>1705</v>
       </c>
       <c r="F583" s="2">
-        <v>46216</v>
+        <v>45994</v>
       </c>
       <c r="G583" t="s">
         <v>1914</v>
       </c>
       <c r="H583" t="s">
-        <v>1934</v>
+        <v>1922</v>
       </c>
       <c r="I583" t="s">
-        <v>2020</v>
+        <v>2055</v>
       </c>
       <c r="J583" t="s">
         <v>2140</v>
@@ -33110,22 +33114,28 @@
         <v>1342</v>
       </c>
       <c r="C584" t="s">
-        <v>1630</v>
+        <v>1646</v>
+      </c>
+      <c r="D584" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E584" t="s">
+        <v>1549</v>
       </c>
       <c r="F584" s="2">
-        <v>45712</v>
+        <v>45923</v>
       </c>
       <c r="G584" t="s">
         <v>1914</v>
       </c>
       <c r="H584" t="s">
-        <v>1919</v>
+        <v>1969</v>
       </c>
       <c r="I584" t="s">
-        <v>2014</v>
+        <v>2118</v>
       </c>
       <c r="J584" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K584" t="s">
         <v>2721</v>
@@ -33142,25 +33152,19 @@
         <v>1343</v>
       </c>
       <c r="C585" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D585" t="s">
-        <v>1803</v>
-      </c>
-      <c r="E585" t="s">
-        <v>1700</v>
+        <v>1815</v>
       </c>
       <c r="F585" s="2">
-        <v>45848</v>
+        <v>46216</v>
       </c>
       <c r="G585" t="s">
         <v>1914</v>
       </c>
       <c r="H585" t="s">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="I585" t="s">
-        <v>2002</v>
+        <v>2020</v>
       </c>
       <c r="J585" t="s">
         <v>2140</v>
@@ -33180,22 +33184,22 @@
         <v>1344</v>
       </c>
       <c r="C586" t="s">
-        <v>1811</v>
+        <v>1630</v>
       </c>
       <c r="F586" s="2">
-        <v>45722</v>
+        <v>45712</v>
       </c>
       <c r="G586" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H586" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I586" t="s">
-        <v>2127</v>
+        <v>2014</v>
       </c>
       <c r="J586" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K586" t="s">
         <v>2723</v>
@@ -33212,19 +33216,25 @@
         <v>1345</v>
       </c>
       <c r="C587" t="s">
-        <v>1816</v>
+        <v>1542</v>
+      </c>
+      <c r="D587" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E587" t="s">
+        <v>1700</v>
       </c>
       <c r="F587" s="2">
-        <v>46204</v>
+        <v>45848</v>
       </c>
       <c r="G587" t="s">
         <v>1914</v>
       </c>
       <c r="H587" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
       <c r="I587" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="J587" t="s">
         <v>2140</v>
@@ -33244,22 +33254,22 @@
         <v>1346</v>
       </c>
       <c r="C588" t="s">
-        <v>1692</v>
+        <v>1811</v>
       </c>
       <c r="F588" s="2">
-        <v>45891</v>
+        <v>45722</v>
       </c>
       <c r="G588" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H588" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I588" t="s">
-        <v>2009</v>
+        <v>2127</v>
       </c>
       <c r="J588" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K588" t="s">
         <v>2725</v>
@@ -33276,19 +33286,19 @@
         <v>1347</v>
       </c>
       <c r="C589" t="s">
-        <v>1542</v>
+        <v>1816</v>
       </c>
       <c r="F589" s="2">
-        <v>45846</v>
+        <v>46204</v>
       </c>
       <c r="G589" t="s">
         <v>1914</v>
       </c>
       <c r="H589" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I589" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="J589" t="s">
         <v>2140</v>
@@ -33308,19 +33318,19 @@
         <v>1348</v>
       </c>
       <c r="C590" t="s">
-        <v>1641</v>
+        <v>1692</v>
       </c>
       <c r="F590" s="2">
-        <v>45846</v>
+        <v>45891</v>
       </c>
       <c r="G590" t="s">
         <v>1914</v>
       </c>
       <c r="H590" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="I590" t="s">
-        <v>1980</v>
+        <v>2009</v>
       </c>
       <c r="J590" t="s">
         <v>2140</v>
@@ -33340,10 +33350,10 @@
         <v>1349</v>
       </c>
       <c r="C591" t="s">
-        <v>1606</v>
+        <v>1542</v>
       </c>
       <c r="F591" s="2">
-        <v>46175</v>
+        <v>45846</v>
       </c>
       <c r="G591" t="s">
         <v>1914</v>
@@ -33352,7 +33362,7 @@
         <v>1924</v>
       </c>
       <c r="I591" t="s">
-        <v>2128</v>
+        <v>2002</v>
       </c>
       <c r="J591" t="s">
         <v>2140</v>
@@ -33372,19 +33382,19 @@
         <v>1350</v>
       </c>
       <c r="C592" t="s">
-        <v>1779</v>
+        <v>1641</v>
       </c>
       <c r="F592" s="2">
-        <v>45994</v>
+        <v>45846</v>
       </c>
       <c r="G592" t="s">
         <v>1914</v>
       </c>
       <c r="H592" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I592" t="s">
-        <v>2011</v>
+        <v>1980</v>
       </c>
       <c r="J592" t="s">
         <v>2140</v>
@@ -33404,22 +33414,19 @@
         <v>1351</v>
       </c>
       <c r="C593" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D593" t="s">
-        <v>1551</v>
+        <v>1606</v>
       </c>
       <c r="F593" s="2">
-        <v>45946</v>
+        <v>46175</v>
       </c>
       <c r="G593" t="s">
         <v>1914</v>
       </c>
       <c r="H593" t="s">
-        <v>1941</v>
+        <v>1924</v>
       </c>
       <c r="I593" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="J593" t="s">
         <v>2140</v>
@@ -33439,25 +33446,22 @@
         <v>1352</v>
       </c>
       <c r="C594" t="s">
-        <v>1546</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1712</v>
+        <v>1779</v>
       </c>
       <c r="F594" s="2">
-        <v>46162</v>
+        <v>45994</v>
       </c>
       <c r="G594" t="s">
         <v>1914</v>
       </c>
       <c r="H594" t="s">
-        <v>1941</v>
+        <v>1922</v>
       </c>
       <c r="I594" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="J594" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K594" t="s">
         <v>2731</v>
@@ -33474,25 +33478,22 @@
         <v>1353</v>
       </c>
       <c r="C595" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="D595" t="s">
-        <v>1701</v>
-      </c>
-      <c r="E595" t="s">
-        <v>1701</v>
+        <v>1551</v>
       </c>
       <c r="F595" s="2">
-        <v>45950</v>
+        <v>45946</v>
       </c>
       <c r="G595" t="s">
         <v>1914</v>
       </c>
       <c r="H595" t="s">
-        <v>1931</v>
+        <v>1941</v>
       </c>
       <c r="I595" t="s">
-        <v>1976</v>
+        <v>2129</v>
       </c>
       <c r="J595" t="s">
         <v>2140</v>
@@ -33512,22 +33513,25 @@
         <v>1354</v>
       </c>
       <c r="C596" t="s">
-        <v>1819</v>
+        <v>1546</v>
+      </c>
+      <c r="D596" t="s">
+        <v>1712</v>
       </c>
       <c r="F596" s="2">
-        <v>45679</v>
+        <v>46162</v>
       </c>
       <c r="G596" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H596" t="s">
-        <v>1924</v>
+        <v>1941</v>
       </c>
       <c r="I596" t="s">
-        <v>1974</v>
+        <v>2008</v>
       </c>
       <c r="J596" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K596" t="s">
         <v>2733</v>
@@ -33544,25 +33548,25 @@
         <v>1355</v>
       </c>
       <c r="C597" t="s">
-        <v>1662</v>
+        <v>1818</v>
       </c>
       <c r="D597" t="s">
-        <v>1772</v>
+        <v>1701</v>
       </c>
       <c r="E597" t="s">
-        <v>1824</v>
+        <v>1701</v>
       </c>
       <c r="F597" s="2">
-        <v>45915</v>
+        <v>45950</v>
       </c>
       <c r="G597" t="s">
         <v>1914</v>
       </c>
       <c r="H597" t="s">
-        <v>1953</v>
+        <v>1931</v>
       </c>
       <c r="I597" t="s">
-        <v>2049</v>
+        <v>1976</v>
       </c>
       <c r="J597" t="s">
         <v>2140</v>
@@ -33582,19 +33586,19 @@
         <v>1356</v>
       </c>
       <c r="C598" t="s">
-        <v>1586</v>
+        <v>1819</v>
       </c>
       <c r="F598" s="2">
-        <v>45754</v>
+        <v>45679</v>
       </c>
       <c r="G598" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H598" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="I598" t="s">
-        <v>2009</v>
+        <v>1974</v>
       </c>
       <c r="J598" t="s">
         <v>2140</v>
@@ -33614,19 +33618,25 @@
         <v>1357</v>
       </c>
       <c r="C599" t="s">
-        <v>1730</v>
+        <v>1662</v>
+      </c>
+      <c r="D599" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E599" t="s">
+        <v>1824</v>
       </c>
       <c r="F599" s="2">
-        <v>45835</v>
+        <v>45915</v>
       </c>
       <c r="G599" t="s">
         <v>1914</v>
       </c>
       <c r="H599" t="s">
-        <v>1924</v>
+        <v>1953</v>
       </c>
       <c r="I599" t="s">
-        <v>1985</v>
+        <v>2049</v>
       </c>
       <c r="J599" t="s">
         <v>2140</v>
@@ -33646,19 +33656,19 @@
         <v>1358</v>
       </c>
       <c r="C600" t="s">
-        <v>1512</v>
+        <v>1586</v>
       </c>
       <c r="F600" s="2">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="G600" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="H600" t="s">
-        <v>1970</v>
+        <v>1922</v>
       </c>
       <c r="I600" t="s">
-        <v>2107</v>
+        <v>2009</v>
       </c>
       <c r="J600" t="s">
         <v>2140</v>
@@ -33678,25 +33688,19 @@
         <v>1359</v>
       </c>
       <c r="C601" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D601" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E601" t="s">
-        <v>1509</v>
+        <v>1730</v>
       </c>
       <c r="F601" s="2">
-        <v>46219</v>
+        <v>45835</v>
       </c>
       <c r="G601" t="s">
         <v>1914</v>
       </c>
       <c r="H601" t="s">
-        <v>1931</v>
+        <v>1924</v>
       </c>
       <c r="I601" t="s">
-        <v>1995</v>
+        <v>1985</v>
       </c>
       <c r="J601" t="s">
         <v>2140</v>
@@ -33716,19 +33720,19 @@
         <v>1360</v>
       </c>
       <c r="C602" t="s">
-        <v>1730</v>
+        <v>1512</v>
       </c>
       <c r="F602" s="2">
-        <v>45853</v>
+        <v>45751</v>
       </c>
       <c r="G602" t="s">
         <v>1914</v>
       </c>
       <c r="H602" t="s">
-        <v>1944</v>
+        <v>1970</v>
       </c>
       <c r="I602" t="s">
-        <v>2074</v>
+        <v>2107</v>
       </c>
       <c r="J602" t="s">
         <v>2140</v>
@@ -33748,19 +33752,25 @@
         <v>1361</v>
       </c>
       <c r="C603" t="s">
-        <v>1820</v>
+        <v>1605</v>
+      </c>
+      <c r="D603" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E603" t="s">
+        <v>1509</v>
       </c>
       <c r="F603" s="2">
-        <v>46196</v>
+        <v>46219</v>
       </c>
       <c r="G603" t="s">
         <v>1914</v>
       </c>
       <c r="H603" t="s">
-        <v>1921</v>
+        <v>1931</v>
       </c>
       <c r="I603" t="s">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="J603" t="s">
         <v>2140</v>
@@ -33780,19 +33790,19 @@
         <v>1362</v>
       </c>
       <c r="C604" t="s">
-        <v>1635</v>
+        <v>1730</v>
       </c>
       <c r="F604" s="2">
-        <v>45911</v>
+        <v>45853</v>
       </c>
       <c r="G604" t="s">
         <v>1914</v>
       </c>
       <c r="H604" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="I604" t="s">
-        <v>2018</v>
+        <v>2074</v>
       </c>
       <c r="J604" t="s">
         <v>2140</v>
@@ -33812,25 +33822,19 @@
         <v>1363</v>
       </c>
       <c r="C605" t="s">
-        <v>1685</v>
-      </c>
-      <c r="D605" t="s">
-        <v>1574</v>
-      </c>
-      <c r="E605" t="s">
-        <v>1574</v>
+        <v>1820</v>
       </c>
       <c r="F605" s="2">
-        <v>45996</v>
+        <v>46196</v>
       </c>
       <c r="G605" t="s">
         <v>1914</v>
       </c>
       <c r="H605" t="s">
-        <v>1936</v>
+        <v>1921</v>
       </c>
       <c r="I605" t="s">
-        <v>1985</v>
+        <v>2007</v>
       </c>
       <c r="J605" t="s">
         <v>2140</v>
@@ -33850,19 +33854,19 @@
         <v>1364</v>
       </c>
       <c r="C606" t="s">
-        <v>1712</v>
+        <v>1635</v>
       </c>
       <c r="F606" s="2">
-        <v>46003</v>
+        <v>45911</v>
       </c>
       <c r="G606" t="s">
         <v>1914</v>
       </c>
       <c r="H606" t="s">
-        <v>1919</v>
+        <v>1941</v>
       </c>
       <c r="I606" t="s">
-        <v>2051</v>
+        <v>2018</v>
       </c>
       <c r="J606" t="s">
         <v>2140</v>
@@ -33882,22 +33886,22 @@
         <v>1365</v>
       </c>
       <c r="C607" t="s">
-        <v>1733</v>
+        <v>1685</v>
       </c>
       <c r="D607" t="s">
-        <v>1667</v>
+        <v>1574</v>
       </c>
       <c r="E607" t="s">
-        <v>1667</v>
+        <v>1574</v>
       </c>
       <c r="F607" s="2">
-        <v>45937</v>
+        <v>45996</v>
       </c>
       <c r="G607" t="s">
         <v>1914</v>
       </c>
       <c r="H607" t="s">
-        <v>1954</v>
+        <v>1936</v>
       </c>
       <c r="I607" t="s">
         <v>1985</v>
@@ -33920,19 +33924,19 @@
         <v>1366</v>
       </c>
       <c r="C608" t="s">
-        <v>1741</v>
+        <v>1712</v>
       </c>
       <c r="F608" s="2">
-        <v>46204</v>
+        <v>46003</v>
       </c>
       <c r="G608" t="s">
         <v>1914</v>
       </c>
       <c r="H608" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I608" t="s">
-        <v>2000</v>
+        <v>2051</v>
       </c>
       <c r="J608" t="s">
         <v>2140</v>
@@ -33952,19 +33956,25 @@
         <v>1367</v>
       </c>
       <c r="C609" t="s">
-        <v>1727</v>
+        <v>1733</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E609" t="s">
+        <v>1667</v>
       </c>
       <c r="F609" s="2">
-        <v>46168</v>
+        <v>45937</v>
       </c>
       <c r="G609" t="s">
         <v>1914</v>
       </c>
       <c r="H609" t="s">
-        <v>1934</v>
+        <v>1954</v>
       </c>
       <c r="I609" t="s">
-        <v>1978</v>
+        <v>1985</v>
       </c>
       <c r="J609" t="s">
         <v>2140</v>
@@ -33984,19 +33994,19 @@
         <v>1368</v>
       </c>
       <c r="C610" t="s">
-        <v>1548</v>
+        <v>1741</v>
       </c>
       <c r="F610" s="2">
-        <v>45723</v>
+        <v>46204</v>
       </c>
       <c r="G610" t="s">
         <v>1914</v>
       </c>
       <c r="H610" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="I610" t="s">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="J610" t="s">
         <v>2140</v>
@@ -34016,19 +34026,19 @@
         <v>1369</v>
       </c>
       <c r="C611" t="s">
-        <v>1821</v>
+        <v>1727</v>
       </c>
       <c r="F611" s="2">
-        <v>45824</v>
+        <v>46168</v>
       </c>
       <c r="G611" t="s">
         <v>1914</v>
       </c>
       <c r="H611" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="I611" t="s">
-        <v>2130</v>
+        <v>1978</v>
       </c>
       <c r="J611" t="s">
         <v>2140</v>
@@ -34048,22 +34058,19 @@
         <v>1370</v>
       </c>
       <c r="C612" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D612" t="s">
-        <v>1892</v>
+        <v>1821</v>
       </c>
       <c r="F612" s="2">
-        <v>46050</v>
+        <v>45824</v>
       </c>
       <c r="G612" t="s">
         <v>1914</v>
       </c>
       <c r="H612" t="s">
-        <v>1919</v>
+        <v>1924</v>
       </c>
       <c r="I612" t="s">
-        <v>2033</v>
+        <v>2130</v>
       </c>
       <c r="J612" t="s">
         <v>2140</v>
@@ -34083,19 +34090,22 @@
         <v>1371</v>
       </c>
       <c r="C613" t="s">
-        <v>1640</v>
+        <v>1657</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1892</v>
       </c>
       <c r="F613" s="2">
-        <v>45908</v>
+        <v>46050</v>
       </c>
       <c r="G613" t="s">
         <v>1914</v>
       </c>
       <c r="H613" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="I613" t="s">
-        <v>1974</v>
+        <v>2033</v>
       </c>
       <c r="J613" t="s">
         <v>2140</v>
@@ -34115,19 +34125,19 @@
         <v>1372</v>
       </c>
       <c r="C614" t="s">
-        <v>1536</v>
+        <v>1640</v>
       </c>
       <c r="F614" s="2">
-        <v>46175</v>
+        <v>45908</v>
       </c>
       <c r="G614" t="s">
         <v>1914</v>
       </c>
       <c r="H614" t="s">
-        <v>1963</v>
+        <v>1922</v>
       </c>
       <c r="I614" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="J614" t="s">
         <v>2140</v>
@@ -34147,28 +34157,22 @@
         <v>1373</v>
       </c>
       <c r="C615" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D615" t="s">
-        <v>1893</v>
-      </c>
-      <c r="E615" t="s">
-        <v>1893</v>
+        <v>1536</v>
       </c>
       <c r="F615" s="2">
-        <v>46217</v>
+        <v>46175</v>
       </c>
       <c r="G615" t="s">
         <v>1914</v>
       </c>
       <c r="H615" t="s">
-        <v>1936</v>
+        <v>1963</v>
       </c>
       <c r="I615" t="s">
-        <v>1985</v>
+        <v>1977</v>
       </c>
       <c r="J615" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K615" t="s">
         <v>2752</v>
@@ -34185,22 +34189,28 @@
         <v>1374</v>
       </c>
       <c r="C616" t="s">
-        <v>1779</v>
+        <v>1509</v>
+      </c>
+      <c r="D616" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E616" t="s">
+        <v>1893</v>
       </c>
       <c r="F616" s="2">
-        <v>46093</v>
+        <v>46217</v>
       </c>
       <c r="G616" t="s">
         <v>1914</v>
       </c>
       <c r="H616" t="s">
-        <v>1921</v>
+        <v>1936</v>
       </c>
       <c r="I616" t="s">
-        <v>2032</v>
+        <v>1985</v>
       </c>
       <c r="J616" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K616" t="s">
         <v>2753</v>
@@ -34217,28 +34227,22 @@
         <v>1375</v>
       </c>
       <c r="C617" t="s">
-        <v>1774</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1691</v>
-      </c>
-      <c r="E617" t="s">
-        <v>1763</v>
+        <v>1779</v>
       </c>
       <c r="F617" s="2">
-        <v>45750</v>
+        <v>46093</v>
       </c>
       <c r="G617" t="s">
         <v>1914</v>
       </c>
       <c r="H617" t="s">
-        <v>1930</v>
+        <v>1921</v>
       </c>
       <c r="I617" t="s">
-        <v>2118</v>
+        <v>2032</v>
       </c>
       <c r="J617" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="K617" t="s">
         <v>2754</v>
@@ -34255,22 +34259,28 @@
         <v>1376</v>
       </c>
       <c r="C618" t="s">
-        <v>1528</v>
+        <v>1774</v>
+      </c>
+      <c r="D618" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E618" t="s">
+        <v>1763</v>
       </c>
       <c r="F618" s="2">
-        <v>45925</v>
+        <v>45750</v>
       </c>
       <c r="G618" t="s">
         <v>1914</v>
       </c>
       <c r="H618" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="I618" t="s">
-        <v>1992</v>
+        <v>2118</v>
       </c>
       <c r="J618" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="K618" t="s">
         <v>2755</v>
@@ -37873,10 +37883,10 @@
         <v>1484</v>
       </c>
       <c r="C726" t="s">
-        <v>1609</v>
+        <v>1589</v>
       </c>
       <c r="F726" s="2">
-        <v>45818</v>
+        <v>46232</v>
       </c>
       <c r="G726" t="s">
         <v>1914</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7124" uniqueCount="3637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7126" uniqueCount="3637">
   <si>
     <t>PROCEDIMENTO_SEI</t>
   </si>
@@ -1600,9 +1600,6 @@
     <t>20.22.0001.0007823.2025-55</t>
   </si>
   <si>
-    <t>20.22.0001.0043118.2025-18</t>
-  </si>
-  <si>
     <t>20.22.0001.0056255.2025-48</t>
   </si>
   <si>
@@ -1936,6 +1933,9 @@
     <t>20.22.0001.0067524.2025-74</t>
   </si>
   <si>
+    <t>20.22.0001.0049964.2026-55</t>
+  </si>
+  <si>
     <t>20.22.0001.0076373.2025-62</t>
   </si>
   <si>
@@ -3847,9 +3847,6 @@
     <t>2025.0108</t>
   </si>
   <si>
-    <t>2025.0755</t>
-  </si>
-  <si>
     <t>2025.1006</t>
   </si>
   <si>
@@ -4183,6 +4180,9 @@
     <t>2025.1230</t>
   </si>
   <si>
+    <t>2026.0838</t>
+  </si>
+  <si>
     <t>2025.1382</t>
   </si>
   <si>
@@ -6376,31 +6376,31 @@
     <t>PROMOTORIA DE JUSTIÇA DE FAMÍLIA DE RESENDE</t>
   </si>
   <si>
+    <t>1ª PROMOTORIA DE JUSTIÇA DE SEROPÉDICA</t>
+  </si>
+  <si>
+    <t>1ª PROMOTORIA DE JUSTIÇA CÍVEL DE NOVA IGUAÇU - MESQUITA</t>
+  </si>
+  <si>
+    <t>7ª PROMOTORIA DE JUSTIÇA DE FAZENDA PÚBLICA DA CAPITAL</t>
+  </si>
+  <si>
+    <t>2ª PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DE DEFESA DO MEIO AMBIENTE E DO PATRIMÔNIO CULTURAL DA CAPITAL</t>
+  </si>
+  <si>
+    <t>1ª PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DO NÚCLEO CAMPOS DOS GOYTACAZES</t>
+  </si>
+  <si>
+    <t>PROMOTORIA DE JUSTIÇA DE FAMÍLIA, DA INFÂNCIA E DA JUVENTUDE DE TRÊS RIOS</t>
+  </si>
+  <si>
+    <t>4ª PROMOTORIA DE JUSTIÇA DA PESSOA IDOSA DA CAPITAL</t>
+  </si>
+  <si>
+    <t>PROMOTORIA DE JUSTIÇA DA INFÂNCIA E DA JUVENTUDE DE TERESÓPOLIS</t>
+  </si>
+  <si>
     <t>PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DA PESSOA COM DEFICIÊNCIA DA CAPITAL</t>
-  </si>
-  <si>
-    <t>1ª PROMOTORIA DE JUSTIÇA DE SEROPÉDICA</t>
-  </si>
-  <si>
-    <t>1ª PROMOTORIA DE JUSTIÇA CÍVEL DE NOVA IGUAÇU - MESQUITA</t>
-  </si>
-  <si>
-    <t>7ª PROMOTORIA DE JUSTIÇA DE FAZENDA PÚBLICA DA CAPITAL</t>
-  </si>
-  <si>
-    <t>2ª PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DE DEFESA DO MEIO AMBIENTE E DO PATRIMÔNIO CULTURAL DA CAPITAL</t>
-  </si>
-  <si>
-    <t>1ª PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DO NÚCLEO CAMPOS DOS GOYTACAZES</t>
-  </si>
-  <si>
-    <t>PROMOTORIA DE JUSTIÇA DE FAMÍLIA, DA INFÂNCIA E DA JUVENTUDE DE TRÊS RIOS</t>
-  </si>
-  <si>
-    <t>4ª PROMOTORIA DE JUSTIÇA DA PESSOA IDOSA DA CAPITAL</t>
-  </si>
-  <si>
-    <t>PROMOTORIA DE JUSTIÇA DA INFÂNCIA E DA JUVENTUDE DE TERESÓPOLIS</t>
   </si>
   <si>
     <t>8ª PROMOTORIA DE JUSTIÇA DE TUTELA COLETIVA DE DEFESA DA CIDADANIA DA CAPITAL</t>
@@ -9560,9 +9560,6 @@
     <t>Solicito os bons préstimos no sentido de informar se é possível confeccionar IT contábil, diante dos novos esclarecimentos trazidos pela SEAS, ou se ratifica sua manifestação anterior.</t>
   </si>
   <si>
-    <t>Solicito apoio técnico do órgão na análise das informações prestadas pela SMAS, nos documentos de índexes 03910226 e 04402949, à luz da determinação exarada pelo Tribunal de Contas do Município no Processo TCM nº 040.100934.2019, especificamente no que diz respeito ao serviços destinados às pessoas com deficiência, de modo que seja indicado se as determinações do TCM foram cumpridas pelo MRJ, apontando-se, caso negativo, quais as pendências e as possíveis formas de regularização. Solicita-se, ainda, seja esclarecido se é possível concluir pela observância da Lei 13.019/2014 nos instrumentos firmados pelo MRJ com as entidades que compõe a RHC. Frisa-se que a SAT segue acompanhada da documentação constante de fls. 18/200 do volume I e de fls. 201/288 do volume II, além do despacho do índex 02202433.</t>
-  </si>
-  <si>
     <t>Análise da economicidade e regularidade da contratação do serviço de hospedagem para pessoas em situação de rua durante a pandemia de COVID-19, considerando o
 contexto emergencial, para que responda os quesitos iniciais abaixo indicados:
 1 - Análise de Preço e Mercado
@@ -10292,6 +10289,9 @@
     <t>Encaminhe as últimas respostas da Secretaria Municipal de Assistência Social de Magé ao GATE para complementação à IT nº 398/2025 a fim de verificar se as irregularidades antes constatadas foram sanadas pelos Municípios.</t>
   </si>
   <si>
+    <t>Análise das manifestações dos réus de ids 286073242 e 289938002, em resposta à IT 329/2026 do GATE, especialmente quanto à proposta de formalização de negócio jurídico para realização de perícia (privada) acerca de suposto desvio de rio.</t>
+  </si>
+  <si>
     <t>A solicitação de análise técnica ao GATE justifica-se pela necessidade de apurar e quantificar o dano ao erário decorrente do uso indevido do terminal rodoviário de Itaguaí, conforme indícios constantes dos autos. A apuração demanda avaliação técnica especializada, a fim de identificar o valor econômico do prejuízo ao erário municipal.</t>
   </si>
   <si>
@@ -12546,9 +12546,6 @@
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4427641&amp;id_documento=4427642</t>
   </si>
   <si>
-    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=4886904&amp;id_documento=4886905</t>
-  </si>
-  <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5069914&amp;id_documento=5069915</t>
   </si>
   <si>
@@ -12880,6 +12877,9 @@
   </si>
   <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5227432&amp;id_documento=5227433</t>
+  </si>
+  <si>
+    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=6309470&amp;id_documento=6309471</t>
   </si>
   <si>
     <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=5352423&amp;id_documento=5352424</t>
@@ -30904,19 +30904,19 @@
         <v>1277</v>
       </c>
       <c r="C518" t="s">
-        <v>1732</v>
+        <v>1802</v>
       </c>
       <c r="F518" s="2">
-        <v>45923</v>
+        <v>45994</v>
       </c>
       <c r="G518" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H518" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="I518" t="s">
-        <v>2120</v>
+        <v>2039</v>
       </c>
       <c r="J518" t="s">
         <v>2142</v>
@@ -30936,19 +30936,19 @@
         <v>1278</v>
       </c>
       <c r="C519" t="s">
-        <v>1802</v>
+        <v>1715</v>
       </c>
       <c r="F519" s="2">
-        <v>45994</v>
+        <v>46090</v>
       </c>
       <c r="G519" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="H519" t="s">
         <v>1924</v>
       </c>
       <c r="I519" t="s">
-        <v>2039</v>
+        <v>2050</v>
       </c>
       <c r="J519" t="s">
         <v>2142</v>
@@ -30968,19 +30968,19 @@
         <v>1279</v>
       </c>
       <c r="C520" t="s">
-        <v>1715</v>
+        <v>1803</v>
       </c>
       <c r="F520" s="2">
-        <v>46090</v>
+        <v>46188</v>
       </c>
       <c r="G520" t="s">
         <v>1916</v>
       </c>
       <c r="H520" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I520" t="s">
-        <v>2050</v>
+        <v>2020</v>
       </c>
       <c r="J520" t="s">
         <v>2142</v>
@@ -31000,19 +31000,19 @@
         <v>1280</v>
       </c>
       <c r="C521" t="s">
-        <v>1803</v>
+        <v>1569</v>
       </c>
       <c r="F521" s="2">
-        <v>46188</v>
+        <v>45996</v>
       </c>
       <c r="G521" t="s">
         <v>1916</v>
       </c>
       <c r="H521" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="I521" t="s">
-        <v>2020</v>
+        <v>2120</v>
       </c>
       <c r="J521" t="s">
         <v>2142</v>
@@ -31032,19 +31032,19 @@
         <v>1281</v>
       </c>
       <c r="C522" t="s">
-        <v>1569</v>
+        <v>1804</v>
       </c>
       <c r="F522" s="2">
-        <v>45996</v>
+        <v>45673</v>
       </c>
       <c r="G522" t="s">
         <v>1916</v>
       </c>
       <c r="H522" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="I522" t="s">
-        <v>2121</v>
+        <v>2012</v>
       </c>
       <c r="J522" t="s">
         <v>2142</v>
@@ -31064,19 +31064,19 @@
         <v>1282</v>
       </c>
       <c r="C523" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="F523" s="2">
-        <v>45673</v>
+        <v>45919</v>
       </c>
       <c r="G523" t="s">
         <v>1916</v>
       </c>
       <c r="H523" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I523" t="s">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="J523" t="s">
         <v>2142</v>
@@ -31096,19 +31096,19 @@
         <v>1283</v>
       </c>
       <c r="C524" t="s">
-        <v>1805</v>
+        <v>1694</v>
       </c>
       <c r="F524" s="2">
-        <v>45919</v>
+        <v>45946</v>
       </c>
       <c r="G524" t="s">
         <v>1916</v>
       </c>
       <c r="H524" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I524" t="s">
-        <v>1996</v>
+        <v>1988</v>
       </c>
       <c r="J524" t="s">
         <v>2142</v>
@@ -31128,10 +31128,10 @@
         <v>1284</v>
       </c>
       <c r="C525" t="s">
-        <v>1694</v>
+        <v>1604</v>
       </c>
       <c r="F525" s="2">
-        <v>45946</v>
+        <v>45838</v>
       </c>
       <c r="G525" t="s">
         <v>1916</v>
@@ -31140,7 +31140,7 @@
         <v>1923</v>
       </c>
       <c r="I525" t="s">
-        <v>1988</v>
+        <v>2099</v>
       </c>
       <c r="J525" t="s">
         <v>2142</v>
@@ -31160,19 +31160,25 @@
         <v>1285</v>
       </c>
       <c r="C526" t="s">
-        <v>1604</v>
+        <v>1806</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E526" t="s">
+        <v>1688</v>
       </c>
       <c r="F526" s="2">
-        <v>45838</v>
+        <v>45994</v>
       </c>
       <c r="G526" t="s">
         <v>1916</v>
       </c>
       <c r="H526" t="s">
-        <v>1923</v>
+        <v>1942</v>
       </c>
       <c r="I526" t="s">
-        <v>2099</v>
+        <v>1976</v>
       </c>
       <c r="J526" t="s">
         <v>2142</v>
@@ -31192,25 +31198,25 @@
         <v>1286</v>
       </c>
       <c r="C527" t="s">
-        <v>1806</v>
+        <v>1528</v>
       </c>
       <c r="D527" t="s">
-        <v>1688</v>
+        <v>1513</v>
       </c>
       <c r="E527" t="s">
-        <v>1688</v>
+        <v>1913</v>
       </c>
       <c r="F527" s="2">
-        <v>45994</v>
+        <v>45772</v>
       </c>
       <c r="G527" t="s">
         <v>1916</v>
       </c>
       <c r="H527" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="I527" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="J527" t="s">
         <v>2142</v>
@@ -31230,25 +31236,19 @@
         <v>1287</v>
       </c>
       <c r="C528" t="s">
-        <v>1528</v>
-      </c>
-      <c r="D528" t="s">
-        <v>1513</v>
-      </c>
-      <c r="E528" t="s">
-        <v>1913</v>
+        <v>1807</v>
       </c>
       <c r="F528" s="2">
-        <v>45772</v>
+        <v>45989</v>
       </c>
       <c r="G528" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H528" t="s">
-        <v>1952</v>
+        <v>1926</v>
       </c>
       <c r="I528" t="s">
-        <v>1978</v>
+        <v>2121</v>
       </c>
       <c r="J528" t="s">
         <v>2142</v>
@@ -31268,19 +31268,22 @@
         <v>1288</v>
       </c>
       <c r="C529" t="s">
-        <v>1807</v>
+        <v>1520</v>
+      </c>
+      <c r="D529" t="s">
+        <v>1883</v>
       </c>
       <c r="F529" s="2">
-        <v>45989</v>
+        <v>46147</v>
       </c>
       <c r="G529" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H529" t="s">
-        <v>1926</v>
+        <v>1932</v>
       </c>
       <c r="I529" t="s">
-        <v>2122</v>
+        <v>1982</v>
       </c>
       <c r="J529" t="s">
         <v>2142</v>
@@ -31300,22 +31303,19 @@
         <v>1289</v>
       </c>
       <c r="C530" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D530" t="s">
-        <v>1883</v>
+        <v>1607</v>
       </c>
       <c r="F530" s="2">
-        <v>46147</v>
+        <v>46184</v>
       </c>
       <c r="G530" t="s">
         <v>1916</v>
       </c>
       <c r="H530" t="s">
-        <v>1932</v>
+        <v>1924</v>
       </c>
       <c r="I530" t="s">
-        <v>1982</v>
+        <v>2018</v>
       </c>
       <c r="J530" t="s">
         <v>2142</v>
@@ -31335,19 +31335,19 @@
         <v>1290</v>
       </c>
       <c r="C531" t="s">
-        <v>1607</v>
+        <v>1690</v>
       </c>
       <c r="F531" s="2">
-        <v>46184</v>
+        <v>46049</v>
       </c>
       <c r="G531" t="s">
         <v>1916</v>
       </c>
       <c r="H531" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I531" t="s">
-        <v>2018</v>
+        <v>1980</v>
       </c>
       <c r="J531" t="s">
         <v>2142</v>
@@ -31367,19 +31367,25 @@
         <v>1291</v>
       </c>
       <c r="C532" t="s">
-        <v>1690</v>
+        <v>1808</v>
+      </c>
+      <c r="D532" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E532" t="s">
+        <v>1889</v>
       </c>
       <c r="F532" s="2">
-        <v>46049</v>
+        <v>46227</v>
       </c>
       <c r="G532" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H532" t="s">
-        <v>1923</v>
+        <v>1941</v>
       </c>
       <c r="I532" t="s">
-        <v>1980</v>
+        <v>2001</v>
       </c>
       <c r="J532" t="s">
         <v>2142</v>
@@ -31399,25 +31405,25 @@
         <v>1292</v>
       </c>
       <c r="C533" t="s">
-        <v>1808</v>
+        <v>1634</v>
       </c>
       <c r="D533" t="s">
-        <v>1889</v>
+        <v>1568</v>
       </c>
       <c r="E533" t="s">
-        <v>1889</v>
+        <v>1826</v>
       </c>
       <c r="F533" s="2">
-        <v>46227</v>
+        <v>45924</v>
       </c>
       <c r="G533" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H533" t="s">
-        <v>1941</v>
+        <v>1923</v>
       </c>
       <c r="I533" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="J533" t="s">
         <v>2142</v>
@@ -31437,16 +31443,10 @@
         <v>1293</v>
       </c>
       <c r="C534" t="s">
-        <v>1634</v>
-      </c>
-      <c r="D534" t="s">
-        <v>1568</v>
-      </c>
-      <c r="E534" t="s">
-        <v>1826</v>
+        <v>1638</v>
       </c>
       <c r="F534" s="2">
-        <v>45924</v>
+        <v>45891</v>
       </c>
       <c r="G534" t="s">
         <v>1916</v>
@@ -31455,7 +31455,7 @@
         <v>1923</v>
       </c>
       <c r="I534" t="s">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="J534" t="s">
         <v>2142</v>
@@ -31475,19 +31475,19 @@
         <v>1294</v>
       </c>
       <c r="C535" t="s">
-        <v>1638</v>
+        <v>1694</v>
       </c>
       <c r="F535" s="2">
-        <v>45891</v>
+        <v>45812</v>
       </c>
       <c r="G535" t="s">
         <v>1916</v>
       </c>
       <c r="H535" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I535" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="J535" t="s">
         <v>2142</v>
@@ -31507,22 +31507,28 @@
         <v>1295</v>
       </c>
       <c r="C536" t="s">
-        <v>1694</v>
+        <v>1561</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E536" t="s">
+        <v>1659</v>
       </c>
       <c r="F536" s="2">
-        <v>45812</v>
+        <v>46048</v>
       </c>
       <c r="G536" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H536" t="s">
-        <v>1924</v>
+        <v>1969</v>
       </c>
       <c r="I536" t="s">
-        <v>2011</v>
+        <v>2122</v>
       </c>
       <c r="J536" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K536" t="s">
         <v>2675</v>
@@ -31539,25 +31545,25 @@
         <v>1296</v>
       </c>
       <c r="C537" t="s">
-        <v>1561</v>
+        <v>1603</v>
       </c>
       <c r="D537" t="s">
-        <v>1659</v>
+        <v>1741</v>
       </c>
       <c r="E537" t="s">
-        <v>1659</v>
+        <v>1547</v>
       </c>
       <c r="F537" s="2">
-        <v>46048</v>
+        <v>45908</v>
       </c>
       <c r="G537" t="s">
         <v>1917</v>
       </c>
       <c r="H537" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="I537" t="s">
-        <v>2123</v>
+        <v>2051</v>
       </c>
       <c r="J537" t="s">
         <v>2143</v>
@@ -31577,28 +31583,22 @@
         <v>1297</v>
       </c>
       <c r="C538" t="s">
-        <v>1603</v>
-      </c>
-      <c r="D538" t="s">
-        <v>1741</v>
-      </c>
-      <c r="E538" t="s">
-        <v>1547</v>
+        <v>1739</v>
       </c>
       <c r="F538" s="2">
-        <v>45908</v>
+        <v>46113</v>
       </c>
       <c r="G538" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H538" t="s">
-        <v>1970</v>
+        <v>1923</v>
       </c>
       <c r="I538" t="s">
-        <v>2051</v>
+        <v>2009</v>
       </c>
       <c r="J538" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K538" t="s">
         <v>2677</v>
@@ -31615,19 +31615,19 @@
         <v>1298</v>
       </c>
       <c r="C539" t="s">
-        <v>1739</v>
+        <v>1760</v>
       </c>
       <c r="F539" s="2">
-        <v>46113</v>
+        <v>45693</v>
       </c>
       <c r="G539" t="s">
         <v>1916</v>
       </c>
       <c r="H539" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I539" t="s">
-        <v>2009</v>
+        <v>1978</v>
       </c>
       <c r="J539" t="s">
         <v>2142</v>
@@ -31647,22 +31647,22 @@
         <v>1299</v>
       </c>
       <c r="C540" t="s">
-        <v>1760</v>
+        <v>1809</v>
       </c>
       <c r="F540" s="2">
-        <v>45693</v>
+        <v>45735</v>
       </c>
       <c r="G540" t="s">
         <v>1916</v>
       </c>
       <c r="H540" t="s">
-        <v>1924</v>
+        <v>1938</v>
       </c>
       <c r="I540" t="s">
-        <v>1978</v>
+        <v>2123</v>
       </c>
       <c r="J540" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K540" t="s">
         <v>2679</v>
@@ -31679,22 +31679,22 @@
         <v>1300</v>
       </c>
       <c r="C541" t="s">
-        <v>1809</v>
+        <v>1798</v>
       </c>
       <c r="F541" s="2">
-        <v>45735</v>
+        <v>46189</v>
       </c>
       <c r="G541" t="s">
         <v>1916</v>
       </c>
       <c r="H541" t="s">
-        <v>1938</v>
+        <v>1923</v>
       </c>
       <c r="I541" t="s">
-        <v>2124</v>
+        <v>2007</v>
       </c>
       <c r="J541" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K541" t="s">
         <v>2680</v>
@@ -31711,19 +31711,25 @@
         <v>1301</v>
       </c>
       <c r="C542" t="s">
-        <v>1798</v>
+        <v>1537</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E542" t="s">
+        <v>1830</v>
       </c>
       <c r="F542" s="2">
-        <v>46189</v>
+        <v>46118</v>
       </c>
       <c r="G542" t="s">
         <v>1916</v>
       </c>
       <c r="H542" t="s">
-        <v>1923</v>
+        <v>1943</v>
       </c>
       <c r="I542" t="s">
-        <v>2007</v>
+        <v>2030</v>
       </c>
       <c r="J542" t="s">
         <v>2142</v>
@@ -31743,25 +31749,19 @@
         <v>1302</v>
       </c>
       <c r="C543" t="s">
-        <v>1537</v>
-      </c>
-      <c r="D543" t="s">
-        <v>1830</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1830</v>
+        <v>1767</v>
       </c>
       <c r="F543" s="2">
-        <v>46118</v>
+        <v>45812</v>
       </c>
       <c r="G543" t="s">
         <v>1916</v>
       </c>
       <c r="H543" t="s">
-        <v>1943</v>
+        <v>1924</v>
       </c>
       <c r="I543" t="s">
-        <v>2030</v>
+        <v>2124</v>
       </c>
       <c r="J543" t="s">
         <v>2142</v>
@@ -31781,22 +31781,22 @@
         <v>1303</v>
       </c>
       <c r="C544" t="s">
-        <v>1767</v>
+        <v>1532</v>
       </c>
       <c r="F544" s="2">
-        <v>45812</v>
+        <v>46204</v>
       </c>
       <c r="G544" t="s">
         <v>1916</v>
       </c>
       <c r="H544" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I544" t="s">
-        <v>2125</v>
+        <v>2011</v>
       </c>
       <c r="J544" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K544" t="s">
         <v>2683</v>
@@ -31813,22 +31813,25 @@
         <v>1304</v>
       </c>
       <c r="C545" t="s">
-        <v>1532</v>
+        <v>1663</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1678</v>
       </c>
       <c r="F545" s="2">
-        <v>46204</v>
+        <v>45709</v>
       </c>
       <c r="G545" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="H545" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="I545" t="s">
-        <v>2011</v>
+        <v>2073</v>
       </c>
       <c r="J545" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K545" t="s">
         <v>2684</v>
@@ -31845,22 +31848,19 @@
         <v>1305</v>
       </c>
       <c r="C546" t="s">
-        <v>1663</v>
-      </c>
-      <c r="D546" t="s">
-        <v>1678</v>
+        <v>1606</v>
       </c>
       <c r="F546" s="2">
-        <v>45709</v>
+        <v>46148</v>
       </c>
       <c r="G546" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="H546" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="I546" t="s">
-        <v>2073</v>
+        <v>2012</v>
       </c>
       <c r="J546" t="s">
         <v>2142</v>
@@ -31880,19 +31880,22 @@
         <v>1306</v>
       </c>
       <c r="C547" t="s">
-        <v>1606</v>
+        <v>1810</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1515</v>
       </c>
       <c r="F547" s="2">
-        <v>46148</v>
+        <v>46211</v>
       </c>
       <c r="G547" t="s">
         <v>1916</v>
       </c>
       <c r="H547" t="s">
-        <v>1923</v>
+        <v>1932</v>
       </c>
       <c r="I547" t="s">
-        <v>2012</v>
+        <v>2125</v>
       </c>
       <c r="J547" t="s">
         <v>2142</v>
@@ -31912,22 +31915,19 @@
         <v>1307</v>
       </c>
       <c r="C548" t="s">
-        <v>1810</v>
-      </c>
-      <c r="D548" t="s">
-        <v>1515</v>
+        <v>1752</v>
       </c>
       <c r="F548" s="2">
-        <v>46211</v>
+        <v>46044</v>
       </c>
       <c r="G548" t="s">
         <v>1916</v>
       </c>
       <c r="H548" t="s">
-        <v>1932</v>
+        <v>1923</v>
       </c>
       <c r="I548" t="s">
-        <v>2126</v>
+        <v>2029</v>
       </c>
       <c r="J548" t="s">
         <v>2142</v>
@@ -31947,19 +31947,19 @@
         <v>1308</v>
       </c>
       <c r="C549" t="s">
-        <v>1752</v>
+        <v>1521</v>
       </c>
       <c r="F549" s="2">
-        <v>46044</v>
+        <v>45994</v>
       </c>
       <c r="G549" t="s">
         <v>1916</v>
       </c>
       <c r="H549" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="I549" t="s">
-        <v>2029</v>
+        <v>2013</v>
       </c>
       <c r="J549" t="s">
         <v>2142</v>
@@ -31979,22 +31979,28 @@
         <v>1309</v>
       </c>
       <c r="C550" t="s">
-        <v>1521</v>
+        <v>1811</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E550" t="s">
+        <v>1707</v>
       </c>
       <c r="F550" s="2">
-        <v>45994</v>
+        <v>46034</v>
       </c>
       <c r="G550" t="s">
         <v>1916</v>
       </c>
       <c r="H550" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
       <c r="I550" t="s">
-        <v>2013</v>
+        <v>1992</v>
       </c>
       <c r="J550" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K550" t="s">
         <v>2689</v>
@@ -32011,25 +32017,25 @@
         <v>1310</v>
       </c>
       <c r="C551" t="s">
-        <v>1811</v>
+        <v>1644</v>
       </c>
       <c r="D551" t="s">
-        <v>1703</v>
+        <v>1767</v>
       </c>
       <c r="E551" t="s">
-        <v>1707</v>
+        <v>1767</v>
       </c>
       <c r="F551" s="2">
-        <v>46034</v>
+        <v>45811</v>
       </c>
       <c r="G551" t="s">
         <v>1916</v>
       </c>
       <c r="H551" t="s">
-        <v>1929</v>
+        <v>1943</v>
       </c>
       <c r="I551" t="s">
-        <v>1992</v>
+        <v>2097</v>
       </c>
       <c r="J551" t="s">
         <v>2143</v>
@@ -32049,25 +32055,19 @@
         <v>1311</v>
       </c>
       <c r="C552" t="s">
-        <v>1644</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E552" t="s">
-        <v>1767</v>
+        <v>1543</v>
       </c>
       <c r="F552" s="2">
-        <v>45811</v>
+        <v>46167</v>
       </c>
       <c r="G552" t="s">
         <v>1916</v>
       </c>
       <c r="H552" t="s">
-        <v>1943</v>
+        <v>1923</v>
       </c>
       <c r="I552" t="s">
-        <v>2097</v>
+        <v>1988</v>
       </c>
       <c r="J552" t="s">
         <v>2143</v>
@@ -32087,22 +32087,22 @@
         <v>1312</v>
       </c>
       <c r="C553" t="s">
-        <v>1543</v>
+        <v>1678</v>
       </c>
       <c r="F553" s="2">
-        <v>46167</v>
+        <v>45680</v>
       </c>
       <c r="G553" t="s">
         <v>1916</v>
       </c>
       <c r="H553" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I553" t="s">
-        <v>1988</v>
+        <v>2021</v>
       </c>
       <c r="J553" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K553" t="s">
         <v>2692</v>
@@ -32119,10 +32119,10 @@
         <v>1313</v>
       </c>
       <c r="C554" t="s">
-        <v>1678</v>
+        <v>1746</v>
       </c>
       <c r="F554" s="2">
-        <v>45680</v>
+        <v>45754</v>
       </c>
       <c r="G554" t="s">
         <v>1916</v>
@@ -32131,7 +32131,7 @@
         <v>1924</v>
       </c>
       <c r="I554" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J554" t="s">
         <v>2142</v>
@@ -32151,19 +32151,19 @@
         <v>1314</v>
       </c>
       <c r="C555" t="s">
-        <v>1746</v>
+        <v>1563</v>
       </c>
       <c r="F555" s="2">
-        <v>45754</v>
+        <v>46160</v>
       </c>
       <c r="G555" t="s">
         <v>1916</v>
       </c>
       <c r="H555" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I555" t="s">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="J555" t="s">
         <v>2142</v>
@@ -32183,22 +32183,22 @@
         <v>1315</v>
       </c>
       <c r="C556" t="s">
-        <v>1563</v>
+        <v>1737</v>
       </c>
       <c r="F556" s="2">
-        <v>46160</v>
+        <v>45854</v>
       </c>
       <c r="G556" t="s">
         <v>1916</v>
       </c>
       <c r="H556" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I556" t="s">
-        <v>2018</v>
+        <v>1980</v>
       </c>
       <c r="J556" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K556" t="s">
         <v>2695</v>
@@ -32215,22 +32215,25 @@
         <v>1316</v>
       </c>
       <c r="C557" t="s">
-        <v>1737</v>
+        <v>1768</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1890</v>
       </c>
       <c r="F557" s="2">
-        <v>45854</v>
+        <v>45782</v>
       </c>
       <c r="G557" t="s">
         <v>1916</v>
       </c>
       <c r="H557" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="I557" t="s">
-        <v>1980</v>
+        <v>2031</v>
       </c>
       <c r="J557" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K557" t="s">
         <v>2696</v>
@@ -32247,13 +32250,10 @@
         <v>1317</v>
       </c>
       <c r="C558" t="s">
-        <v>1768</v>
-      </c>
-      <c r="D558" t="s">
-        <v>1890</v>
+        <v>1516</v>
       </c>
       <c r="F558" s="2">
-        <v>45782</v>
+        <v>46010</v>
       </c>
       <c r="G558" t="s">
         <v>1916</v>
@@ -32262,7 +32262,7 @@
         <v>1926</v>
       </c>
       <c r="I558" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="J558" t="s">
         <v>2142</v>
@@ -32282,10 +32282,10 @@
         <v>1318</v>
       </c>
       <c r="C559" t="s">
-        <v>1516</v>
+        <v>1644</v>
       </c>
       <c r="F559" s="2">
-        <v>46010</v>
+        <v>45812</v>
       </c>
       <c r="G559" t="s">
         <v>1916</v>
@@ -32294,7 +32294,7 @@
         <v>1926</v>
       </c>
       <c r="I559" t="s">
-        <v>2041</v>
+        <v>2097</v>
       </c>
       <c r="J559" t="s">
         <v>2142</v>
@@ -32314,22 +32314,28 @@
         <v>1319</v>
       </c>
       <c r="C560" t="s">
-        <v>1644</v>
+        <v>1676</v>
+      </c>
+      <c r="D560" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E560" t="s">
+        <v>1605</v>
       </c>
       <c r="F560" s="2">
-        <v>45812</v>
+        <v>45884</v>
       </c>
       <c r="G560" t="s">
         <v>1916</v>
       </c>
       <c r="H560" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="I560" t="s">
-        <v>2097</v>
+        <v>2062</v>
       </c>
       <c r="J560" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K560" t="s">
         <v>2699</v>
@@ -32346,28 +32352,22 @@
         <v>1320</v>
       </c>
       <c r="C561" t="s">
-        <v>1676</v>
-      </c>
-      <c r="D561" t="s">
-        <v>1605</v>
-      </c>
-      <c r="E561" t="s">
-        <v>1605</v>
+        <v>1805</v>
       </c>
       <c r="F561" s="2">
-        <v>45884</v>
+        <v>45995</v>
       </c>
       <c r="G561" t="s">
         <v>1916</v>
       </c>
       <c r="H561" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I561" t="s">
-        <v>2062</v>
+        <v>2009</v>
       </c>
       <c r="J561" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K561" t="s">
         <v>2700</v>
@@ -32384,19 +32384,25 @@
         <v>1321</v>
       </c>
       <c r="C562" t="s">
-        <v>1805</v>
+        <v>1613</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E562" t="s">
+        <v>1677</v>
       </c>
       <c r="F562" s="2">
-        <v>45995</v>
+        <v>46167</v>
       </c>
       <c r="G562" t="s">
         <v>1916</v>
       </c>
       <c r="H562" t="s">
-        <v>1923</v>
+        <v>1932</v>
       </c>
       <c r="I562" t="s">
-        <v>2009</v>
+        <v>2124</v>
       </c>
       <c r="J562" t="s">
         <v>2142</v>
@@ -32416,28 +32422,22 @@
         <v>1322</v>
       </c>
       <c r="C563" t="s">
-        <v>1613</v>
-      </c>
-      <c r="D563" t="s">
-        <v>1677</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1677</v>
+        <v>1710</v>
       </c>
       <c r="F563" s="2">
-        <v>46167</v>
+        <v>45704</v>
       </c>
       <c r="G563" t="s">
         <v>1916</v>
       </c>
       <c r="H563" t="s">
-        <v>1932</v>
+        <v>1924</v>
       </c>
       <c r="I563" t="s">
-        <v>2125</v>
+        <v>1979</v>
       </c>
       <c r="J563" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K563" t="s">
         <v>2702</v>
@@ -32454,22 +32454,28 @@
         <v>1323</v>
       </c>
       <c r="C564" t="s">
-        <v>1710</v>
+        <v>1729</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E564" t="s">
+        <v>1891</v>
       </c>
       <c r="F564" s="2">
-        <v>45704</v>
+        <v>46181</v>
       </c>
       <c r="G564" t="s">
         <v>1916</v>
       </c>
       <c r="H564" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I564" t="s">
-        <v>1979</v>
+        <v>2048</v>
       </c>
       <c r="J564" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K564" t="s">
         <v>2703</v>
@@ -32486,25 +32492,19 @@
         <v>1324</v>
       </c>
       <c r="C565" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D565" t="s">
-        <v>1891</v>
-      </c>
-      <c r="E565" t="s">
-        <v>1891</v>
+        <v>1795</v>
       </c>
       <c r="F565" s="2">
-        <v>46181</v>
+        <v>46204</v>
       </c>
       <c r="G565" t="s">
         <v>1916</v>
       </c>
       <c r="H565" t="s">
-        <v>1923</v>
+        <v>1942</v>
       </c>
       <c r="I565" t="s">
-        <v>2048</v>
+        <v>2029</v>
       </c>
       <c r="J565" t="s">
         <v>2142</v>
@@ -32524,19 +32524,19 @@
         <v>1325</v>
       </c>
       <c r="C566" t="s">
-        <v>1795</v>
+        <v>1732</v>
       </c>
       <c r="F566" s="2">
-        <v>46204</v>
+        <v>45853</v>
       </c>
       <c r="G566" t="s">
         <v>1916</v>
       </c>
       <c r="H566" t="s">
-        <v>1942</v>
+        <v>1926</v>
       </c>
       <c r="I566" t="s">
-        <v>2029</v>
+        <v>2076</v>
       </c>
       <c r="J566" t="s">
         <v>2142</v>
@@ -32556,19 +32556,19 @@
         <v>1326</v>
       </c>
       <c r="C567" t="s">
-        <v>1732</v>
+        <v>1518</v>
       </c>
       <c r="F567" s="2">
-        <v>45853</v>
+        <v>45705</v>
       </c>
       <c r="G567" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="H567" t="s">
         <v>1926</v>
       </c>
       <c r="I567" t="s">
-        <v>2076</v>
+        <v>2126</v>
       </c>
       <c r="J567" t="s">
         <v>2142</v>
@@ -32588,19 +32588,19 @@
         <v>1327</v>
       </c>
       <c r="C568" t="s">
-        <v>1518</v>
+        <v>1669</v>
       </c>
       <c r="F568" s="2">
-        <v>45705</v>
+        <v>45862</v>
       </c>
       <c r="G568" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="H568" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="I568" t="s">
-        <v>2127</v>
+        <v>2011</v>
       </c>
       <c r="J568" t="s">
         <v>2142</v>
@@ -32620,19 +32620,25 @@
         <v>1328</v>
       </c>
       <c r="C569" t="s">
-        <v>1669</v>
+        <v>1519</v>
+      </c>
+      <c r="D569" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E569" t="s">
+        <v>1844</v>
       </c>
       <c r="F569" s="2">
-        <v>45862</v>
+        <v>45992</v>
       </c>
       <c r="G569" t="s">
         <v>1916</v>
       </c>
       <c r="H569" t="s">
-        <v>1924</v>
+        <v>1930</v>
       </c>
       <c r="I569" t="s">
-        <v>2011</v>
+        <v>1983</v>
       </c>
       <c r="J569" t="s">
         <v>2142</v>
@@ -32652,25 +32658,19 @@
         <v>1329</v>
       </c>
       <c r="C570" t="s">
-        <v>1519</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E570" t="s">
-        <v>1844</v>
+        <v>1812</v>
       </c>
       <c r="F570" s="2">
-        <v>45992</v>
+        <v>46010</v>
       </c>
       <c r="G570" t="s">
         <v>1916</v>
       </c>
       <c r="H570" t="s">
-        <v>1930</v>
+        <v>1923</v>
       </c>
       <c r="I570" t="s">
-        <v>1983</v>
+        <v>2023</v>
       </c>
       <c r="J570" t="s">
         <v>2142</v>
@@ -32690,19 +32690,22 @@
         <v>1330</v>
       </c>
       <c r="C571" t="s">
-        <v>1812</v>
+        <v>1813</v>
+      </c>
+      <c r="D571" t="s">
+        <v>1601</v>
       </c>
       <c r="F571" s="2">
-        <v>46010</v>
+        <v>45972</v>
       </c>
       <c r="G571" t="s">
         <v>1916</v>
       </c>
       <c r="H571" t="s">
-        <v>1923</v>
+        <v>1945</v>
       </c>
       <c r="I571" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="J571" t="s">
         <v>2142</v>
@@ -32722,22 +32725,19 @@
         <v>1331</v>
       </c>
       <c r="C572" t="s">
-        <v>1813</v>
-      </c>
-      <c r="D572" t="s">
-        <v>1601</v>
+        <v>1806</v>
       </c>
       <c r="F572" s="2">
-        <v>45972</v>
+        <v>45849</v>
       </c>
       <c r="G572" t="s">
         <v>1916</v>
       </c>
       <c r="H572" t="s">
-        <v>1945</v>
+        <v>1924</v>
       </c>
       <c r="I572" t="s">
-        <v>2020</v>
+        <v>1976</v>
       </c>
       <c r="J572" t="s">
         <v>2142</v>
@@ -32757,10 +32757,10 @@
         <v>1332</v>
       </c>
       <c r="C573" t="s">
-        <v>1806</v>
+        <v>1570</v>
       </c>
       <c r="F573" s="2">
-        <v>45849</v>
+        <v>45965</v>
       </c>
       <c r="G573" t="s">
         <v>1916</v>
@@ -32769,10 +32769,10 @@
         <v>1924</v>
       </c>
       <c r="I573" t="s">
-        <v>1976</v>
+        <v>2099</v>
       </c>
       <c r="J573" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K573" t="s">
         <v>2712</v>
@@ -32789,10 +32789,10 @@
         <v>1333</v>
       </c>
       <c r="C574" t="s">
-        <v>1570</v>
+        <v>1795</v>
       </c>
       <c r="F574" s="2">
-        <v>45965</v>
+        <v>46224</v>
       </c>
       <c r="G574" t="s">
         <v>1916</v>
@@ -32801,10 +32801,10 @@
         <v>1924</v>
       </c>
       <c r="I574" t="s">
-        <v>2099</v>
+        <v>2009</v>
       </c>
       <c r="J574" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K574" t="s">
         <v>2713</v>
@@ -32821,19 +32821,19 @@
         <v>1334</v>
       </c>
       <c r="C575" t="s">
-        <v>1795</v>
+        <v>1526</v>
       </c>
       <c r="F575" s="2">
-        <v>46224</v>
+        <v>45811</v>
       </c>
       <c r="G575" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H575" t="s">
-        <v>1924</v>
+        <v>1940</v>
       </c>
       <c r="I575" t="s">
-        <v>2009</v>
+        <v>1980</v>
       </c>
       <c r="J575" t="s">
         <v>2142</v>
@@ -32853,19 +32853,19 @@
         <v>1335</v>
       </c>
       <c r="C576" t="s">
-        <v>1526</v>
+        <v>1780</v>
       </c>
       <c r="F576" s="2">
-        <v>45811</v>
+        <v>46232</v>
       </c>
       <c r="G576" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H576" t="s">
-        <v>1940</v>
+        <v>1923</v>
       </c>
       <c r="I576" t="s">
-        <v>1980</v>
+        <v>2034</v>
       </c>
       <c r="J576" t="s">
         <v>2142</v>
@@ -32885,19 +32885,19 @@
         <v>1336</v>
       </c>
       <c r="C577" t="s">
-        <v>1780</v>
+        <v>1814</v>
       </c>
       <c r="F577" s="2">
-        <v>46232</v>
+        <v>45811</v>
       </c>
       <c r="G577" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H577" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I577" t="s">
-        <v>2034</v>
+        <v>2062</v>
       </c>
       <c r="J577" t="s">
         <v>2142</v>
@@ -32917,19 +32917,25 @@
         <v>1337</v>
       </c>
       <c r="C578" t="s">
-        <v>1814</v>
+        <v>1666</v>
+      </c>
+      <c r="D578" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E578" t="s">
+        <v>1905</v>
       </c>
       <c r="F578" s="2">
-        <v>45811</v>
+        <v>45734</v>
       </c>
       <c r="G578" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H578" t="s">
-        <v>1924</v>
+        <v>1950</v>
       </c>
       <c r="I578" t="s">
-        <v>2062</v>
+        <v>2070</v>
       </c>
       <c r="J578" t="s">
         <v>2142</v>
@@ -32949,25 +32955,25 @@
         <v>1338</v>
       </c>
       <c r="C579" t="s">
-        <v>1666</v>
+        <v>1623</v>
       </c>
       <c r="D579" t="s">
-        <v>1865</v>
+        <v>1892</v>
       </c>
       <c r="E579" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="F579" s="2">
-        <v>45734</v>
+        <v>45838</v>
       </c>
       <c r="G579" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="H579" t="s">
-        <v>1950</v>
+        <v>1933</v>
       </c>
       <c r="I579" t="s">
-        <v>2070</v>
+        <v>2127</v>
       </c>
       <c r="J579" t="s">
         <v>2142</v>
@@ -32987,28 +32993,22 @@
         <v>1339</v>
       </c>
       <c r="C580" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D580" t="s">
-        <v>1892</v>
-      </c>
-      <c r="E580" t="s">
-        <v>1904</v>
+        <v>1815</v>
       </c>
       <c r="F580" s="2">
-        <v>45838</v>
+        <v>45684</v>
       </c>
       <c r="G580" t="s">
         <v>1916</v>
       </c>
       <c r="H580" t="s">
-        <v>1933</v>
+        <v>1920</v>
       </c>
       <c r="I580" t="s">
-        <v>2128</v>
+        <v>2021</v>
       </c>
       <c r="J580" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K580" t="s">
         <v>2719</v>
@@ -33025,22 +33025,22 @@
         <v>1340</v>
       </c>
       <c r="C581" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="F581" s="2">
-        <v>45684</v>
+        <v>46092</v>
       </c>
       <c r="G581" t="s">
         <v>1916</v>
       </c>
       <c r="H581" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="I581" t="s">
-        <v>2021</v>
+        <v>2037</v>
       </c>
       <c r="J581" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K581" t="s">
         <v>2720</v>
@@ -33057,22 +33057,28 @@
         <v>1341</v>
       </c>
       <c r="C582" t="s">
-        <v>1816</v>
+        <v>1817</v>
+      </c>
+      <c r="D582" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E582" t="s">
+        <v>1562</v>
       </c>
       <c r="F582" s="2">
-        <v>46092</v>
+        <v>45693</v>
       </c>
       <c r="G582" t="s">
         <v>1916</v>
       </c>
       <c r="H582" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I582" t="s">
-        <v>2037</v>
+        <v>1996</v>
       </c>
       <c r="J582" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K582" t="s">
         <v>2721</v>
@@ -33089,16 +33095,10 @@
         <v>1342</v>
       </c>
       <c r="C583" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D583" t="s">
-        <v>1893</v>
-      </c>
-      <c r="E583" t="s">
-        <v>1562</v>
+        <v>1707</v>
       </c>
       <c r="F583" s="2">
-        <v>45693</v>
+        <v>45994</v>
       </c>
       <c r="G583" t="s">
         <v>1916</v>
@@ -33107,10 +33107,10 @@
         <v>1924</v>
       </c>
       <c r="I583" t="s">
-        <v>1996</v>
+        <v>2057</v>
       </c>
       <c r="J583" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K583" t="s">
         <v>2722</v>
@@ -33127,22 +33127,28 @@
         <v>1343</v>
       </c>
       <c r="C584" t="s">
-        <v>1707</v>
+        <v>1648</v>
+      </c>
+      <c r="D584" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E584" t="s">
+        <v>1551</v>
       </c>
       <c r="F584" s="2">
-        <v>45994</v>
+        <v>45923</v>
       </c>
       <c r="G584" t="s">
         <v>1916</v>
       </c>
       <c r="H584" t="s">
-        <v>1924</v>
+        <v>1971</v>
       </c>
       <c r="I584" t="s">
-        <v>2057</v>
+        <v>2128</v>
       </c>
       <c r="J584" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K584" t="s">
         <v>2723</v>
@@ -33159,28 +33165,22 @@
         <v>1344</v>
       </c>
       <c r="C585" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D585" t="s">
-        <v>1641</v>
-      </c>
-      <c r="E585" t="s">
-        <v>1551</v>
+        <v>1818</v>
       </c>
       <c r="F585" s="2">
-        <v>45923</v>
+        <v>46216</v>
       </c>
       <c r="G585" t="s">
         <v>1916</v>
       </c>
       <c r="H585" t="s">
-        <v>1971</v>
+        <v>1936</v>
       </c>
       <c r="I585" t="s">
-        <v>2120</v>
+        <v>2022</v>
       </c>
       <c r="J585" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K585" t="s">
         <v>2724</v>
@@ -33197,19 +33197,19 @@
         <v>1345</v>
       </c>
       <c r="C586" t="s">
-        <v>1818</v>
+        <v>1632</v>
       </c>
       <c r="F586" s="2">
-        <v>46216</v>
+        <v>45712</v>
       </c>
       <c r="G586" t="s">
         <v>1916</v>
       </c>
       <c r="H586" t="s">
-        <v>1936</v>
+        <v>1921</v>
       </c>
       <c r="I586" t="s">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="J586" t="s">
         <v>2142</v>
@@ -33229,19 +33229,25 @@
         <v>1346</v>
       </c>
       <c r="C587" t="s">
-        <v>1632</v>
+        <v>1544</v>
+      </c>
+      <c r="D587" t="s">
+        <v>1806</v>
+      </c>
+      <c r="E587" t="s">
+        <v>1702</v>
       </c>
       <c r="F587" s="2">
-        <v>45712</v>
+        <v>45848</v>
       </c>
       <c r="G587" t="s">
         <v>1916</v>
       </c>
       <c r="H587" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="I587" t="s">
-        <v>2016</v>
+        <v>2004</v>
       </c>
       <c r="J587" t="s">
         <v>2142</v>
@@ -33261,28 +33267,22 @@
         <v>1347</v>
       </c>
       <c r="C588" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D588" t="s">
-        <v>1806</v>
-      </c>
-      <c r="E588" t="s">
-        <v>1702</v>
+        <v>1814</v>
       </c>
       <c r="F588" s="2">
-        <v>45848</v>
+        <v>45722</v>
       </c>
       <c r="G588" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H588" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="I588" t="s">
-        <v>2004</v>
+        <v>2129</v>
       </c>
       <c r="J588" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K588" t="s">
         <v>2727</v>
@@ -33299,22 +33299,22 @@
         <v>1348</v>
       </c>
       <c r="C589" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="F589" s="2">
-        <v>45722</v>
+        <v>46204</v>
       </c>
       <c r="G589" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="H589" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="I589" t="s">
-        <v>2129</v>
+        <v>2002</v>
       </c>
       <c r="J589" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K589" t="s">
         <v>2728</v>
@@ -33331,10 +33331,10 @@
         <v>1349</v>
       </c>
       <c r="C590" t="s">
-        <v>1819</v>
+        <v>1694</v>
       </c>
       <c r="F590" s="2">
-        <v>46204</v>
+        <v>45891</v>
       </c>
       <c r="G590" t="s">
         <v>1916</v>
@@ -33343,7 +33343,7 @@
         <v>1923</v>
       </c>
       <c r="I590" t="s">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="J590" t="s">
         <v>2142</v>
@@ -33363,19 +33363,19 @@
         <v>1350</v>
       </c>
       <c r="C591" t="s">
-        <v>1694</v>
+        <v>1544</v>
       </c>
       <c r="F591" s="2">
-        <v>45891</v>
+        <v>45846</v>
       </c>
       <c r="G591" t="s">
         <v>1916</v>
       </c>
       <c r="H591" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="I591" t="s">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="J591" t="s">
         <v>2142</v>
@@ -33395,7 +33395,7 @@
         <v>1351</v>
       </c>
       <c r="C592" t="s">
-        <v>1544</v>
+        <v>1643</v>
       </c>
       <c r="F592" s="2">
         <v>45846</v>
@@ -33404,10 +33404,10 @@
         <v>1916</v>
       </c>
       <c r="H592" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="I592" t="s">
-        <v>2004</v>
+        <v>1982</v>
       </c>
       <c r="J592" t="s">
         <v>2142</v>
@@ -33427,19 +33427,19 @@
         <v>1352</v>
       </c>
       <c r="C593" t="s">
-        <v>1643</v>
+        <v>1608</v>
       </c>
       <c r="F593" s="2">
-        <v>45846</v>
+        <v>46175</v>
       </c>
       <c r="G593" t="s">
         <v>1916</v>
       </c>
       <c r="H593" t="s">
-        <v>1921</v>
+        <v>1926</v>
       </c>
       <c r="I593" t="s">
-        <v>1982</v>
+        <v>2130</v>
       </c>
       <c r="J593" t="s">
         <v>2142</v>
@@ -33459,19 +33459,19 @@
         <v>1353</v>
       </c>
       <c r="C594" t="s">
-        <v>1608</v>
+        <v>1782</v>
       </c>
       <c r="F594" s="2">
-        <v>46175</v>
+        <v>45994</v>
       </c>
       <c r="G594" t="s">
         <v>1916</v>
       </c>
       <c r="H594" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="I594" t="s">
-        <v>2130</v>
+        <v>2013</v>
       </c>
       <c r="J594" t="s">
         <v>2142</v>
@@ -33491,19 +33491,22 @@
         <v>1354</v>
       </c>
       <c r="C595" t="s">
-        <v>1782</v>
+        <v>1820</v>
+      </c>
+      <c r="D595" t="s">
+        <v>1553</v>
       </c>
       <c r="F595" s="2">
-        <v>45994</v>
+        <v>45946</v>
       </c>
       <c r="G595" t="s">
         <v>1916</v>
       </c>
       <c r="H595" t="s">
-        <v>1924</v>
+        <v>1943</v>
       </c>
       <c r="I595" t="s">
-        <v>2013</v>
+        <v>2131</v>
       </c>
       <c r="J595" t="s">
         <v>2142</v>
@@ -33523,13 +33526,13 @@
         <v>1355</v>
       </c>
       <c r="C596" t="s">
-        <v>1820</v>
+        <v>1548</v>
       </c>
       <c r="D596" t="s">
-        <v>1553</v>
+        <v>1714</v>
       </c>
       <c r="F596" s="2">
-        <v>45946</v>
+        <v>46162</v>
       </c>
       <c r="G596" t="s">
         <v>1916</v>
@@ -33538,10 +33541,10 @@
         <v>1943</v>
       </c>
       <c r="I596" t="s">
-        <v>2131</v>
+        <v>2010</v>
       </c>
       <c r="J596" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K596" t="s">
         <v>2735</v>
@@ -33558,25 +33561,28 @@
         <v>1356</v>
       </c>
       <c r="C597" t="s">
-        <v>1548</v>
+        <v>1821</v>
       </c>
       <c r="D597" t="s">
-        <v>1714</v>
+        <v>1703</v>
+      </c>
+      <c r="E597" t="s">
+        <v>1703</v>
       </c>
       <c r="F597" s="2">
-        <v>46162</v>
+        <v>45950</v>
       </c>
       <c r="G597" t="s">
         <v>1916</v>
       </c>
       <c r="H597" t="s">
-        <v>1943</v>
+        <v>1933</v>
       </c>
       <c r="I597" t="s">
-        <v>2010</v>
+        <v>1978</v>
       </c>
       <c r="J597" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K597" t="s">
         <v>2736</v>
@@ -33593,25 +33599,19 @@
         <v>1357</v>
       </c>
       <c r="C598" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D598" t="s">
-        <v>1703</v>
-      </c>
-      <c r="E598" t="s">
-        <v>1703</v>
+        <v>1822</v>
       </c>
       <c r="F598" s="2">
-        <v>45950</v>
+        <v>45679</v>
       </c>
       <c r="G598" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="H598" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
       <c r="I598" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="J598" t="s">
         <v>2142</v>
@@ -33631,19 +33631,25 @@
         <v>1358</v>
       </c>
       <c r="C599" t="s">
-        <v>1822</v>
+        <v>1664</v>
+      </c>
+      <c r="D599" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E599" t="s">
+        <v>1826</v>
       </c>
       <c r="F599" s="2">
-        <v>45679</v>
+        <v>45915</v>
       </c>
       <c r="G599" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="H599" t="s">
-        <v>1926</v>
+        <v>1955</v>
       </c>
       <c r="I599" t="s">
-        <v>1976</v>
+        <v>2051</v>
       </c>
       <c r="J599" t="s">
         <v>2142</v>
@@ -33663,25 +33669,19 @@
         <v>1359</v>
       </c>
       <c r="C600" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D600" t="s">
-        <v>1775</v>
-      </c>
-      <c r="E600" t="s">
-        <v>1826</v>
+        <v>1588</v>
       </c>
       <c r="F600" s="2">
-        <v>45915</v>
+        <v>45754</v>
       </c>
       <c r="G600" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H600" t="s">
-        <v>1955</v>
+        <v>1924</v>
       </c>
       <c r="I600" t="s">
-        <v>2051</v>
+        <v>2011</v>
       </c>
       <c r="J600" t="s">
         <v>2142</v>
@@ -33701,19 +33701,19 @@
         <v>1360</v>
       </c>
       <c r="C601" t="s">
-        <v>1588</v>
+        <v>1732</v>
       </c>
       <c r="F601" s="2">
-        <v>45754</v>
+        <v>45835</v>
       </c>
       <c r="G601" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="H601" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="I601" t="s">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="J601" t="s">
         <v>2142</v>
@@ -33733,19 +33733,19 @@
         <v>1361</v>
       </c>
       <c r="C602" t="s">
-        <v>1732</v>
+        <v>1514</v>
       </c>
       <c r="F602" s="2">
-        <v>45835</v>
+        <v>45751</v>
       </c>
       <c r="G602" t="s">
         <v>1916</v>
       </c>
       <c r="H602" t="s">
-        <v>1926</v>
+        <v>1972</v>
       </c>
       <c r="I602" t="s">
-        <v>1987</v>
+        <v>2109</v>
       </c>
       <c r="J602" t="s">
         <v>2142</v>
@@ -33765,19 +33765,25 @@
         <v>1362</v>
       </c>
       <c r="C603" t="s">
-        <v>1514</v>
+        <v>1607</v>
+      </c>
+      <c r="D603" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E603" t="s">
+        <v>1511</v>
       </c>
       <c r="F603" s="2">
-        <v>45751</v>
+        <v>46219</v>
       </c>
       <c r="G603" t="s">
         <v>1916</v>
       </c>
       <c r="H603" t="s">
-        <v>1972</v>
+        <v>1933</v>
       </c>
       <c r="I603" t="s">
-        <v>2109</v>
+        <v>1997</v>
       </c>
       <c r="J603" t="s">
         <v>2142</v>
@@ -33797,25 +33803,19 @@
         <v>1363</v>
       </c>
       <c r="C604" t="s">
-        <v>1607</v>
-      </c>
-      <c r="D604" t="s">
-        <v>1627</v>
-      </c>
-      <c r="E604" t="s">
-        <v>1511</v>
+        <v>1732</v>
       </c>
       <c r="F604" s="2">
-        <v>46219</v>
+        <v>45853</v>
       </c>
       <c r="G604" t="s">
         <v>1916</v>
       </c>
       <c r="H604" t="s">
-        <v>1933</v>
+        <v>1946</v>
       </c>
       <c r="I604" t="s">
-        <v>1997</v>
+        <v>2076</v>
       </c>
       <c r="J604" t="s">
         <v>2142</v>
@@ -33835,19 +33835,19 @@
         <v>1364</v>
       </c>
       <c r="C605" t="s">
-        <v>1732</v>
+        <v>1743</v>
       </c>
       <c r="F605" s="2">
-        <v>45853</v>
+        <v>46196</v>
       </c>
       <c r="G605" t="s">
         <v>1916</v>
       </c>
       <c r="H605" t="s">
-        <v>1946</v>
+        <v>1923</v>
       </c>
       <c r="I605" t="s">
-        <v>2076</v>
+        <v>2009</v>
       </c>
       <c r="J605" t="s">
         <v>2142</v>
@@ -33867,19 +33867,19 @@
         <v>1365</v>
       </c>
       <c r="C606" t="s">
-        <v>1743</v>
+        <v>1637</v>
       </c>
       <c r="F606" s="2">
-        <v>46196</v>
+        <v>45911</v>
       </c>
       <c r="G606" t="s">
         <v>1916</v>
       </c>
       <c r="H606" t="s">
-        <v>1923</v>
+        <v>1943</v>
       </c>
       <c r="I606" t="s">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="J606" t="s">
         <v>2142</v>
@@ -33899,19 +33899,25 @@
         <v>1366</v>
       </c>
       <c r="C607" t="s">
-        <v>1637</v>
+        <v>1687</v>
+      </c>
+      <c r="D607" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E607" t="s">
+        <v>1576</v>
       </c>
       <c r="F607" s="2">
-        <v>45911</v>
+        <v>45996</v>
       </c>
       <c r="G607" t="s">
         <v>1916</v>
       </c>
       <c r="H607" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="I607" t="s">
-        <v>2020</v>
+        <v>1987</v>
       </c>
       <c r="J607" t="s">
         <v>2142</v>
@@ -33931,25 +33937,19 @@
         <v>1367</v>
       </c>
       <c r="C608" t="s">
-        <v>1687</v>
-      </c>
-      <c r="D608" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E608" t="s">
-        <v>1576</v>
+        <v>1714</v>
       </c>
       <c r="F608" s="2">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="G608" t="s">
         <v>1916</v>
       </c>
       <c r="H608" t="s">
-        <v>1938</v>
+        <v>1921</v>
       </c>
       <c r="I608" t="s">
-        <v>1987</v>
+        <v>2053</v>
       </c>
       <c r="J608" t="s">
         <v>2142</v>
@@ -33969,19 +33969,25 @@
         <v>1368</v>
       </c>
       <c r="C609" t="s">
-        <v>1714</v>
+        <v>1735</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E609" t="s">
+        <v>1669</v>
       </c>
       <c r="F609" s="2">
-        <v>46003</v>
+        <v>45937</v>
       </c>
       <c r="G609" t="s">
         <v>1916</v>
       </c>
       <c r="H609" t="s">
-        <v>1921</v>
+        <v>1956</v>
       </c>
       <c r="I609" t="s">
-        <v>2053</v>
+        <v>1987</v>
       </c>
       <c r="J609" t="s">
         <v>2142</v>
@@ -34001,25 +34007,19 @@
         <v>1369</v>
       </c>
       <c r="C610" t="s">
-        <v>1735</v>
-      </c>
-      <c r="D610" t="s">
-        <v>1669</v>
-      </c>
-      <c r="E610" t="s">
-        <v>1669</v>
+        <v>1744</v>
       </c>
       <c r="F610" s="2">
-        <v>45937</v>
+        <v>46204</v>
       </c>
       <c r="G610" t="s">
         <v>1916</v>
       </c>
       <c r="H610" t="s">
-        <v>1956</v>
+        <v>1924</v>
       </c>
       <c r="I610" t="s">
-        <v>1987</v>
+        <v>2002</v>
       </c>
       <c r="J610" t="s">
         <v>2142</v>
@@ -34039,19 +34039,19 @@
         <v>1370</v>
       </c>
       <c r="C611" t="s">
-        <v>1744</v>
+        <v>1729</v>
       </c>
       <c r="F611" s="2">
-        <v>46204</v>
+        <v>46168</v>
       </c>
       <c r="G611" t="s">
         <v>1916</v>
       </c>
       <c r="H611" t="s">
-        <v>1924</v>
+        <v>1936</v>
       </c>
       <c r="I611" t="s">
-        <v>2002</v>
+        <v>1980</v>
       </c>
       <c r="J611" t="s">
         <v>2142</v>
@@ -34071,19 +34071,19 @@
         <v>1371</v>
       </c>
       <c r="C612" t="s">
-        <v>1729</v>
+        <v>1823</v>
       </c>
       <c r="F612" s="2">
-        <v>46168</v>
+        <v>45824</v>
       </c>
       <c r="G612" t="s">
         <v>1916</v>
       </c>
       <c r="H612" t="s">
-        <v>1936</v>
+        <v>1926</v>
       </c>
       <c r="I612" t="s">
-        <v>1980</v>
+        <v>2132</v>
       </c>
       <c r="J612" t="s">
         <v>2142</v>
@@ -34103,19 +34103,22 @@
         <v>1372</v>
       </c>
       <c r="C613" t="s">
-        <v>1823</v>
+        <v>1659</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1894</v>
       </c>
       <c r="F613" s="2">
-        <v>45824</v>
+        <v>46050</v>
       </c>
       <c r="G613" t="s">
         <v>1916</v>
       </c>
       <c r="H613" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="I613" t="s">
-        <v>2132</v>
+        <v>2035</v>
       </c>
       <c r="J613" t="s">
         <v>2142</v>
@@ -34135,22 +34138,19 @@
         <v>1373</v>
       </c>
       <c r="C614" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D614" t="s">
-        <v>1894</v>
+        <v>1642</v>
       </c>
       <c r="F614" s="2">
-        <v>46050</v>
+        <v>45908</v>
       </c>
       <c r="G614" t="s">
         <v>1916</v>
       </c>
       <c r="H614" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="I614" t="s">
-        <v>2035</v>
+        <v>1976</v>
       </c>
       <c r="J614" t="s">
         <v>2142</v>
@@ -34170,19 +34170,19 @@
         <v>1374</v>
       </c>
       <c r="C615" t="s">
-        <v>1642</v>
+        <v>1538</v>
       </c>
       <c r="F615" s="2">
-        <v>45908</v>
+        <v>46175</v>
       </c>
       <c r="G615" t="s">
         <v>1916</v>
       </c>
       <c r="H615" t="s">
-        <v>1924</v>
+        <v>1965</v>
       </c>
       <c r="I615" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="J615" t="s">
         <v>2142</v>
@@ -34202,22 +34202,28 @@
         <v>1375</v>
       </c>
       <c r="C616" t="s">
-        <v>1538</v>
+        <v>1511</v>
+      </c>
+      <c r="D616" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E616" t="s">
+        <v>1895</v>
       </c>
       <c r="F616" s="2">
-        <v>46175</v>
+        <v>46217</v>
       </c>
       <c r="G616" t="s">
         <v>1916</v>
       </c>
       <c r="H616" t="s">
-        <v>1965</v>
+        <v>1938</v>
       </c>
       <c r="I616" t="s">
-        <v>1979</v>
+        <v>1987</v>
       </c>
       <c r="J616" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K616" t="s">
         <v>2755</v>
@@ -34234,28 +34240,22 @@
         <v>1376</v>
       </c>
       <c r="C617" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1895</v>
-      </c>
-      <c r="E617" t="s">
-        <v>1895</v>
+        <v>1782</v>
       </c>
       <c r="F617" s="2">
-        <v>46217</v>
+        <v>46093</v>
       </c>
       <c r="G617" t="s">
         <v>1916</v>
       </c>
       <c r="H617" t="s">
-        <v>1938</v>
+        <v>1923</v>
       </c>
       <c r="I617" t="s">
-        <v>1987</v>
+        <v>2034</v>
       </c>
       <c r="J617" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K617" t="s">
         <v>2756</v>
@@ -34272,22 +34272,28 @@
         <v>1377</v>
       </c>
       <c r="C618" t="s">
-        <v>1782</v>
+        <v>1777</v>
+      </c>
+      <c r="D618" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E618" t="s">
+        <v>1766</v>
       </c>
       <c r="F618" s="2">
-        <v>46093</v>
+        <v>45750</v>
       </c>
       <c r="G618" t="s">
         <v>1916</v>
       </c>
       <c r="H618" t="s">
-        <v>1923</v>
+        <v>1932</v>
       </c>
       <c r="I618" t="s">
-        <v>2034</v>
+        <v>2128</v>
       </c>
       <c r="J618" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K618" t="s">
         <v>2757</v>
@@ -34304,28 +34310,22 @@
         <v>1378</v>
       </c>
       <c r="C619" t="s">
-        <v>1777</v>
-      </c>
-      <c r="D619" t="s">
-        <v>1693</v>
-      </c>
-      <c r="E619" t="s">
-        <v>1766</v>
+        <v>1824</v>
       </c>
       <c r="F619" s="2">
-        <v>45750</v>
+        <v>45946</v>
       </c>
       <c r="G619" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H619" t="s">
-        <v>1932</v>
+        <v>1926</v>
       </c>
       <c r="I619" t="s">
-        <v>2120</v>
+        <v>1980</v>
       </c>
       <c r="J619" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K619" t="s">
         <v>2758</v>
@@ -34342,19 +34342,19 @@
         <v>1379</v>
       </c>
       <c r="C620" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="F620" s="2">
-        <v>45946</v>
+        <v>45751</v>
       </c>
       <c r="G620" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H620" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="I620" t="s">
-        <v>1980</v>
+        <v>2043</v>
       </c>
       <c r="J620" t="s">
         <v>2142</v>
@@ -34374,22 +34374,28 @@
         <v>1380</v>
       </c>
       <c r="C621" t="s">
-        <v>1825</v>
+        <v>1692</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E621" t="s">
+        <v>1863</v>
       </c>
       <c r="F621" s="2">
-        <v>45751</v>
+        <v>46176</v>
       </c>
       <c r="G621" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H621" t="s">
         <v>1923</v>
       </c>
       <c r="I621" t="s">
-        <v>2043</v>
+        <v>2129</v>
       </c>
       <c r="J621" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K621" t="s">
         <v>2760</v>
@@ -34406,28 +34412,22 @@
         <v>1381</v>
       </c>
       <c r="C622" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D622" t="s">
-        <v>1896</v>
-      </c>
-      <c r="E622" t="s">
-        <v>1863</v>
+        <v>1697</v>
       </c>
       <c r="F622" s="2">
-        <v>46176</v>
+        <v>45938</v>
       </c>
       <c r="G622" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="H622" t="s">
         <v>1923</v>
       </c>
       <c r="I622" t="s">
-        <v>2129</v>
+        <v>1980</v>
       </c>
       <c r="J622" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="K622" t="s">
         <v>2761</v>
@@ -34444,19 +34444,19 @@
         <v>1382</v>
       </c>
       <c r="C623" t="s">
-        <v>1697</v>
+        <v>1556</v>
       </c>
       <c r="F623" s="2">
-        <v>45938</v>
+        <v>46118</v>
       </c>
       <c r="G623" t="s">
         <v>1916</v>
       </c>
       <c r="H623" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="I623" t="s">
-        <v>1980</v>
+        <v>2019</v>
       </c>
       <c r="J623" t="s">
         <v>2142</v>
@@ -34476,19 +34476,19 @@
         <v>1383</v>
       </c>
       <c r="C624" t="s">
-        <v>1556</v>
+        <v>1748</v>
       </c>
       <c r="F624" s="2">
-        <v>46118</v>
+        <v>45994</v>
       </c>
       <c r="G624" t="s">
         <v>1916</v>
       </c>
       <c r="H624" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="I624" t="s">
-        <v>2019</v>
+        <v>2034</v>
       </c>
       <c r="J624" t="s">
         <v>2142</v>
@@ -34508,19 +34508,25 @@
         <v>1384</v>
       </c>
       <c r="C625" t="s">
-        <v>1748</v>
+        <v>1680</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E625" t="s">
+        <v>1524</v>
       </c>
       <c r="F625" s="2">
-        <v>45994</v>
+        <v>45859</v>
       </c>
       <c r="G625" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H625" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="I625" t="s">
-        <v>2034</v>
+        <v>1980</v>
       </c>
       <c r="J625" t="s">
         <v>2142</v>
@@ -34540,25 +34546,19 @@
         <v>1385</v>
       </c>
       <c r="C626" t="s">
-        <v>1680</v>
-      </c>
-      <c r="D626" t="s">
-        <v>1605</v>
-      </c>
-      <c r="E626" t="s">
-        <v>1524</v>
+        <v>1826</v>
       </c>
       <c r="F626" s="2">
-        <v>45859</v>
+        <v>46049</v>
       </c>
       <c r="G626" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H626" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="I626" t="s">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="J626" t="s">
         <v>2142</v>
@@ -34578,19 +34578,19 @@
         <v>1386</v>
       </c>
       <c r="C627" t="s">
-        <v>1826</v>
+        <v>1739</v>
       </c>
       <c r="F627" s="2">
-        <v>46049</v>
+        <v>46118</v>
       </c>
       <c r="G627" t="s">
         <v>1916</v>
       </c>
       <c r="H627" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="I627" t="s">
-        <v>1976</v>
+        <v>2029</v>
       </c>
       <c r="J627" t="s">
         <v>2142</v>
@@ -34610,22 +34610,22 @@
         <v>1387</v>
       </c>
       <c r="C628" t="s">
-        <v>1739</v>
+        <v>1578</v>
       </c>
       <c r="F628" s="2">
-        <v>46118</v>
+        <v>45923</v>
       </c>
       <c r="G628" t="s">
         <v>1916</v>
       </c>
       <c r="H628" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="I628" t="s">
-        <v>2029</v>
+        <v>2057</v>
       </c>
       <c r="J628" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="K628" t="s">
         <v>2767</v>
@@ -34642,19 +34642,25 @@
         <v>1388</v>
       </c>
       <c r="C629" t="s">
-        <v>1578</v>
+        <v>1808</v>
+      </c>
+      <c r="D629" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E629" t="s">
+        <v>1889</v>
       </c>
       <c r="F629" s="2">
-        <v>45923</v>
+        <v>46234</v>
       </c>
       <c r="G629" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H629" t="s">
-        <v>1925</v>
+        <v>1961</v>
       </c>
       <c r="I629" t="s">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="J629" t="s">
         <v>2143</v>
@@ -34750,7 +34756,7 @@
         <v>1926</v>
       </c>
       <c r="I632" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="J632" t="s">
         <v>2143</v>
@@ -36216,7 +36222,7 @@
         <v>1925</v>
       </c>
       <c r="I675" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
       <c r="J675" t="s">
         <v>2143</v>
@@ -36248,7 +36254,7 @@
         <v>1975</v>
       </c>
       <c r="I676" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="J676" t="s">
         <v>2142</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -35138,7 +35138,7 @@
         <v>1916</v>
       </c>
       <c r="H643" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="I643" t="s">
         <v>2081</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -28783,7 +28783,7 @@
         <v>1914</v>
       </c>
       <c r="H454" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="I454" t="s">
         <v>2021</v>
